--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\EPSURIS Internship (Vicon)\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9591BB-4F2F-426C-8D4D-28AEE94C6451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F595C417-1755-420E-8DE6-9B7FFA50463C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
     <sheet name="Log" sheetId="1" r:id="rId2"/>
     <sheet name="Daily Summary" sheetId="2" r:id="rId3"/>
     <sheet name="Visualisations" sheetId="3" r:id="rId4"/>
+    <sheet name="DevScriptErrors" sheetId="5" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,8 +39,112 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Daniel Newby</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{212B7CA1-1D60-441F-B72D-2455352A7338}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Daniel Newby:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+From 28/07/2026 bumping experiment, recorded above cameras. Cameras without a value were unaffected by disturbances in the room.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{C01FFB04-8F84-491C-BB2E-65383C0F8D44}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Daniel Newby:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+persistently slow to auto-stop when calibrating</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{17C8BC38-A956-4D7F-998B-6CD76E9EE7EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Daniel Newby:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+persistently slow to auto-stop when calibrating</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
   <si>
     <t>Starting Time</t>
   </si>
@@ -357,6 +465,94 @@
   <si>
     <t>Earlier recordings are not as granular &amp; have irregular time steps</t>
   </si>
+  <si>
+    <t>Recording with camera temperature tracking script from this day</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(tested script against non-active system configs) - on selecting VCS on init, 1 cam active, temp not shown. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mix of auto &amp; manual logs!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>note</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - polling errors with camera temp script (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>window not selected!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Camera by ID</t>
+  </si>
+  <si>
+    <t>This is a dev troubleshooting record for the camera temperature script, checking which cameras are dropped from readings</t>
+  </si>
+  <si>
+    <t>Cameras Missing from Temperature Script Log</t>
+  </si>
+  <si>
+    <t>(04/08 is first day recording these errors)</t>
+  </si>
 </sst>
 </file>
 
@@ -367,7 +563,7 @@
     <numFmt numFmtId="165" formatCode="hh:mm:ss;@"/>
     <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,8 +679,97 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -527,8 +812,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -608,12 +911,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -678,10 +1027,75 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,14 +1112,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -875,6 +1289,9 @@
                 <c:pt idx="8">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -910,6 +1327,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -989,6 +1409,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2770,6 +3193,133 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Instructions"/>
+      <sheetName val="Lists"/>
+      <sheetName val="Camera Labelling"/>
+      <sheetName val="Log"/>
+      <sheetName val="Daily Summary"/>
+      <sheetName val="Camera Error Trend"/>
+      <sheetName val="Camera Performance Trends"/>
+      <sheetName val="High Error Cameras"/>
+      <sheetName val="Problem Cameras"/>
+      <sheetName val="Error Log"/>
+      <sheetName val="Error Summary"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>#1 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>#2 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>#3 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>#4 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>#5 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>#6 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>#7 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>#8 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>#9 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>#10 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>#11 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>#12 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>#13 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>#14 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>#15 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>#16 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>#17 (Vero v2.2)</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>#18 (Vero v2.2)</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3147,16 +3697,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
       <c r="I1" s="19" t="s">
         <v>18</v>
       </c>
@@ -4968,59 +5518,107 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>46238</v>
+      </c>
       <c r="C71" s="9">
         <f>_xlfn.XLOOKUP(Log!A71, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D71" s="9">
+        <v>0.43125000000000002</v>
+      </c>
+      <c r="E71" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H71" s="2" t="str">
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F71" s="7">
+        <v>29</v>
+      </c>
+      <c r="G71" s="2">
+        <v>31</v>
+      </c>
+      <c r="H71" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>46238</v>
+      </c>
       <c r="C72" s="9">
         <f>_xlfn.XLOOKUP(Log!A72, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E72" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D72" s="9">
+        <v>0.43263888888888891</v>
+      </c>
+      <c r="E72" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H72" s="2" t="str">
+        <v>3.9999999999999858</v>
+      </c>
+      <c r="F72" s="7">
+        <v>35</v>
+      </c>
+      <c r="G72" s="2">
+        <v>38</v>
+      </c>
+      <c r="H72" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>46238</v>
+      </c>
       <c r="C73" s="9">
         <f>_xlfn.XLOOKUP(Log!A73, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D73" s="9">
+        <v>0.43611111111111112</v>
+      </c>
+      <c r="E73" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H73" s="2" t="str">
+        <v>8.999999999999968</v>
+      </c>
+      <c r="F73" s="7">
+        <v>41</v>
+      </c>
+      <c r="G73" s="2">
+        <v>44</v>
+      </c>
+      <c r="H73" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>46238</v>
+      </c>
       <c r="C74" s="9">
         <f>_xlfn.XLOOKUP(Log!A74, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E74" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D74" s="9">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="E74" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H74" s="2" t="str">
+        <v>16.99999999999994</v>
+      </c>
+      <c r="F74" s="7">
+        <v>49</v>
+      </c>
+      <c r="G74" s="2">
+        <v>51</v>
+      </c>
+      <c r="H74" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
@@ -11562,14 +12160,14 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="A3:H9999">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$B3&lt;&gt;""</formula>
+  <conditionalFormatting sqref="D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45 A2:C1048576">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:XFD32 A2:C1048576 D33:L40 A1 I1:XFD1 O33:XFD40 D41:XFD44 D45:H45 J45:XFD45 D2:I2 K2:XFD2 D46:XFD1048576">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
+  <conditionalFormatting sqref="A3:H9999">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$B3&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11788,6 +12386,9 @@
         <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
         <v>21.583333333333243</v>
       </c>
+      <c r="F10" s="28" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -11807,12 +12408,25 @@
         <v>21.216666666666654</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46238</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.42986111111111114</v>
+      </c>
       <c r="E12" s="25" t="str">
         <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>–</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -12454,7 +13068,7 @@
       </c>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="26" t="s">
         <v>43</v>
       </c>
     </row>
@@ -12464,7 +13078,7 @@
       </c>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="K24" s="27" t="s">
+      <c r="K24" s="26" t="s">
         <v>39</v>
       </c>
     </row>
@@ -12487,4 +13101,198 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D01A83-1FDF-45BF-A1E3-B5167A4A0F21}">
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" style="43" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="41"/>
+    <col min="3" max="20" width="6.77734375" style="42" customWidth="1"/>
+    <col min="21" max="21" width="2.77734375" style="38" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="39"/>
+    <col min="23" max="25" width="10.77734375" style="38" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="31" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="V1" s="32"/>
+    </row>
+    <row r="2" spans="1:25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="47"/>
+      <c r="V2" s="33"/>
+    </row>
+    <row r="3" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="36" t="str" cm="1">
+        <f t="array" ref="C3:T3">LEFT(TRANSPOSE([1]Lists!A2:A19), 3)</f>
+        <v xml:space="preserve">#1 </v>
+      </c>
+      <c r="D3" s="36" t="str">
+        <v xml:space="preserve">#2 </v>
+      </c>
+      <c r="E3" s="36" t="str">
+        <v xml:space="preserve">#3 </v>
+      </c>
+      <c r="F3" s="36" t="str">
+        <v xml:space="preserve">#4 </v>
+      </c>
+      <c r="G3" s="36" t="str">
+        <v xml:space="preserve">#5 </v>
+      </c>
+      <c r="H3" s="36" t="str">
+        <v xml:space="preserve">#6 </v>
+      </c>
+      <c r="I3" s="36" t="str">
+        <v xml:space="preserve">#7 </v>
+      </c>
+      <c r="J3" s="37" t="str">
+        <v xml:space="preserve">#8 </v>
+      </c>
+      <c r="K3" s="36" t="str">
+        <v xml:space="preserve">#9 </v>
+      </c>
+      <c r="L3" s="36" t="str">
+        <v>#10</v>
+      </c>
+      <c r="M3" s="36" t="str">
+        <v>#11</v>
+      </c>
+      <c r="N3" s="36" t="str">
+        <v>#12</v>
+      </c>
+      <c r="O3" s="37" t="str">
+        <v>#13</v>
+      </c>
+      <c r="P3" s="36" t="str">
+        <v>#14</v>
+      </c>
+      <c r="Q3" s="36" t="str">
+        <v>#15</v>
+      </c>
+      <c r="R3" s="36" t="str">
+        <v>#16</v>
+      </c>
+      <c r="S3" s="36" t="str">
+        <v>#17</v>
+      </c>
+      <c r="T3" s="36" t="str">
+        <v>#18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="40">
+        <v>46238</v>
+      </c>
+      <c r="C4" s="44">
+        <v>3</v>
+      </c>
+      <c r="D4" s="44">
+        <v>3</v>
+      </c>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44">
+        <v>1</v>
+      </c>
+      <c r="S4" s="44">
+        <v>1</v>
+      </c>
+      <c r="T4" s="44">
+        <v>2</v>
+      </c>
+      <c r="V4" s="48"/>
+      <c r="W4" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="40"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="50"/>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="49"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V6" s="48"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="49"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V7" s="48"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\EPSURIS Internship (Vicon)\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F595C417-1755-420E-8DE6-9B7FFA50463C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9030D01B-764E-4BC0-A0CE-D8E29AA06B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -69,60 +69,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{C01FFB04-8F84-491C-BB2E-65383C0F8D44}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Daniel Newby:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-persistently slow to auto-stop when calibrating</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{17C8BC38-A956-4D7F-998B-6CD76E9EE7EB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Daniel Newby:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-persistently slow to auto-stop when calibrating</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -144,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
   <si>
     <t>Starting Time</t>
   </si>
@@ -469,6 +421,21 @@
     <t>Recording with camera temperature tracking script from this day</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Camera by ID</t>
+  </si>
+  <si>
+    <t>This is a dev troubleshooting record for the camera temperature script, checking which cameras are dropped from readings</t>
+  </si>
+  <si>
+    <t>Cameras Missing from Temperature Script Log</t>
+  </si>
+  <si>
+    <t>(04/08 is first day recording these errors)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">(tested script against non-active system configs) - on selecting VCS on init, 1 cam active, temp not shown. </t>
     </r>
@@ -535,23 +502,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)</t>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>time to ready wasn't faster than yesterday despite higher starting temp</t>
     </r>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Camera by ID</t>
-  </si>
-  <si>
-    <t>This is a dev troubleshooting record for the camera temperature script, checking which cameras are dropped from readings</t>
-  </si>
-  <si>
-    <t>Cameras Missing from Temperature Script Log</t>
-  </si>
-  <si>
-    <t>(04/08 is first day recording these errors)</t>
+    <t>startup time may be off by 30 seconds, recorded after start</t>
   </si>
 </sst>
 </file>
@@ -826,7 +794,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -962,7 +930,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1028,9 +996,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1058,9 +1023,6 @@
     <xf numFmtId="0" fontId="22" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1076,6 +1038,19 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1084,17 +1059,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1127,6 +1091,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFBDD7EE"/>
       <color rgb="FF1F4E78"/>
       <color rgb="FFC65911"/>
     </mruColors>
@@ -1292,6 +1257,9 @@
                 <c:pt idx="9">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1329,6 +1297,9 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>24.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1413,6 +1384,9 @@
                 <c:pt idx="9">
                   <c:v>46238</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46239</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1450,10 +1424,10 @@
                   <c:v>21.216666666666654</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>21.066666666666627</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>19.600000000000026</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -3201,7 +3175,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Instructions"/>
-      <sheetName val="Lists"/>
+      <sheetName val="Data-Lists"/>
       <sheetName val="Camera Labelling"/>
       <sheetName val="Log"/>
       <sheetName val="Daily Summary"/>
@@ -3697,16 +3671,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
       <c r="I1" s="19" t="s">
         <v>18</v>
       </c>
@@ -5622,370 +5596,682 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>46238</v>
+      </c>
       <c r="C75" s="9">
         <f>_xlfn.XLOOKUP(Log!A75, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E75" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D75" s="9">
+        <v>0.43334490740740739</v>
+      </c>
+      <c r="E75" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H75" s="2" t="str">
+        <v>5.0166666666665982</v>
+      </c>
+      <c r="F75" s="7">
+        <v>38</v>
+      </c>
+      <c r="G75" s="2">
+        <v>39</v>
+      </c>
+      <c r="H75" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>46238</v>
+      </c>
       <c r="C76" s="9">
         <f>_xlfn.XLOOKUP(Log!A76, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D76" s="9">
+        <v>0.43752314814814813</v>
+      </c>
+      <c r="E76" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H76" s="2" t="str">
+        <v>11.033333333333273</v>
+      </c>
+      <c r="F76" s="7">
+        <v>44</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45</v>
+      </c>
+      <c r="H76" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>46238</v>
+      </c>
       <c r="C77" s="9">
         <f>_xlfn.XLOOKUP(Log!A77, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D77" s="9">
+        <v>0.43892361111111111</v>
+      </c>
+      <c r="E77" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H77" s="2" t="str">
+        <v>13.049999999999962</v>
+      </c>
+      <c r="F77" s="7">
+        <v>47</v>
+      </c>
+      <c r="G77" s="2">
+        <v>48</v>
+      </c>
+      <c r="H77" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>46238</v>
+      </c>
       <c r="C78" s="9">
         <f>_xlfn.XLOOKUP(Log!A78, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E78" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D78" s="9">
+        <v>0.4403125</v>
+      </c>
+      <c r="E78" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H78" s="2" t="str">
+        <v>15.049999999999955</v>
+      </c>
+      <c r="F78" s="7">
+        <v>47</v>
+      </c>
+      <c r="G78" s="2">
+        <v>49</v>
+      </c>
+      <c r="H78" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>46238</v>
+      </c>
       <c r="C79" s="9">
         <f>_xlfn.XLOOKUP(Log!A79, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D79" s="9">
+        <v>0.44310185185185186</v>
+      </c>
+      <c r="E79" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H79" s="2" t="str">
+        <v>19.066666666666634</v>
+      </c>
+      <c r="F79" s="7">
+        <v>49</v>
+      </c>
+      <c r="G79" s="2">
+        <v>52</v>
+      </c>
+      <c r="H79" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>46238</v>
+      </c>
       <c r="C80" s="9">
         <f>_xlfn.XLOOKUP(Log!A80, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D80" s="9">
+        <v>0.44449074074074074</v>
+      </c>
+      <c r="E80" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H80" s="2" t="str">
+        <v>21.066666666666627</v>
+      </c>
+      <c r="F80" s="7">
+        <v>51</v>
+      </c>
+      <c r="G80" s="2">
+        <v>52</v>
+      </c>
+      <c r="H80" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>46238</v>
+      </c>
       <c r="C81" s="9">
         <f>_xlfn.XLOOKUP(Log!A81, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E81" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D81" s="9">
+        <v>0.44589120370370372</v>
+      </c>
+      <c r="E81" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H81" s="2" t="str">
+        <v>23.083333333333318</v>
+      </c>
+      <c r="F81" s="7">
+        <v>52</v>
+      </c>
+      <c r="G81" s="2">
+        <v>55</v>
+      </c>
+      <c r="H81" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>46238</v>
+      </c>
       <c r="C82" s="9">
         <f>_xlfn.XLOOKUP(Log!A82, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E82" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D82" s="9">
+        <v>0.4472800925925926</v>
+      </c>
+      <c r="E82" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H82" s="2" t="str">
+        <v>25.083333333333311</v>
+      </c>
+      <c r="F82" s="7">
+        <v>52</v>
+      </c>
+      <c r="G82" s="2">
+        <v>55</v>
+      </c>
+      <c r="H82" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>46238</v>
+      </c>
       <c r="C83" s="9">
         <f>_xlfn.XLOOKUP(Log!A83, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D83" s="9">
+        <v>0.44866898148148149</v>
+      </c>
+      <c r="E83" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H83" s="2" t="str">
+        <v>27.083333333333304</v>
+      </c>
+      <c r="F83" s="7">
+        <v>54</v>
+      </c>
+      <c r="G83" s="2">
+        <v>55</v>
+      </c>
+      <c r="H83" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>46238</v>
+      </c>
       <c r="C84" s="9">
         <f>_xlfn.XLOOKUP(Log!A84, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D84" s="9">
+        <v>0.45005787037037037</v>
+      </c>
+      <c r="E84" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H84" s="2" t="str">
+        <v>29.083333333333297</v>
+      </c>
+      <c r="F84" s="7">
+        <v>54</v>
+      </c>
+      <c r="G84" s="2">
+        <v>55</v>
+      </c>
+      <c r="H84" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>46238</v>
+      </c>
       <c r="C85" s="9">
         <f>_xlfn.XLOOKUP(Log!A85, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E85" s="6" t="str">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D85" s="9">
+        <v>0.45145833333333335</v>
+      </c>
+      <c r="E85" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H85" s="2" t="str">
+        <v>31.099999999999987</v>
+      </c>
+      <c r="F85" s="7">
+        <v>55</v>
+      </c>
+      <c r="G85" s="2">
+        <v>58</v>
+      </c>
+      <c r="H85" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>46239</v>
+      </c>
       <c r="C86" s="9">
         <f>_xlfn.XLOOKUP(Log!A86, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D86" s="9">
+        <v>0.48472222222222222</v>
+      </c>
+      <c r="E86" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H86" s="2" t="str">
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F86" s="7">
+        <v>30</v>
+      </c>
+      <c r="G86" s="2">
+        <v>31</v>
+      </c>
+      <c r="H86" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>46239</v>
+      </c>
       <c r="C87" s="9">
         <f>_xlfn.XLOOKUP(Log!A87, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E87" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D87" s="9">
+        <v>0.48716435185185186</v>
+      </c>
+      <c r="E87" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H87" s="2" t="str">
+        <v>5.5166666666666764</v>
+      </c>
+      <c r="F87" s="7">
+        <v>38</v>
+      </c>
+      <c r="G87" s="2">
+        <v>39</v>
+      </c>
+      <c r="H87" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>46239</v>
+      </c>
       <c r="C88" s="9">
         <f>_xlfn.XLOOKUP(Log!A88, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D88" s="9">
+        <v>0.48856481481481484</v>
+      </c>
+      <c r="E88" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H88" s="2" t="str">
+        <v>7.5333333333333652</v>
+      </c>
+      <c r="F88" s="7">
+        <v>41</v>
+      </c>
+      <c r="G88" s="2">
+        <v>42</v>
+      </c>
+      <c r="H88" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>46239</v>
+      </c>
       <c r="C89" s="9">
         <f>_xlfn.XLOOKUP(Log!A89, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D89" s="9">
+        <v>0.48995370370370372</v>
+      </c>
+      <c r="E89" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H89" s="2" t="str">
+        <v>9.5333333333333581</v>
+      </c>
+      <c r="F89" s="7">
+        <v>42</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45</v>
+      </c>
+      <c r="H89" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>46239</v>
+      </c>
       <c r="C90" s="9">
         <f>_xlfn.XLOOKUP(Log!A90, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D90" s="9">
+        <v>0.49135416666666665</v>
+      </c>
+      <c r="E90" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H90" s="2" t="str">
+        <v>11.549999999999967</v>
+      </c>
+      <c r="F90" s="7">
+        <v>44</v>
+      </c>
+      <c r="G90" s="2">
+        <v>47</v>
+      </c>
+      <c r="H90" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>46239</v>
+      </c>
       <c r="C91" s="9">
         <f>_xlfn.XLOOKUP(Log!A91, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D91" s="9">
+        <v>0.49275462962962963</v>
+      </c>
+      <c r="E91" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H91" s="2" t="str">
+        <v>13.566666666666656</v>
+      </c>
+      <c r="F91" s="7">
+        <v>47</v>
+      </c>
+      <c r="G91" s="2">
+        <v>48</v>
+      </c>
+      <c r="H91" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>46239</v>
+      </c>
       <c r="C92" s="9">
         <f>_xlfn.XLOOKUP(Log!A92, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E92" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D92" s="9">
+        <v>0.4941550925925926</v>
+      </c>
+      <c r="E92" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H92" s="2" t="str">
+        <v>15.583333333333345</v>
+      </c>
+      <c r="F92" s="7">
+        <v>48</v>
+      </c>
+      <c r="G92" s="2">
+        <v>49</v>
+      </c>
+      <c r="H92" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>46239</v>
+      </c>
       <c r="C93" s="9">
         <f>_xlfn.XLOOKUP(Log!A93, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D93" s="9">
+        <v>0.49554398148148149</v>
+      </c>
+      <c r="E93" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H93" s="2" t="str">
+        <v>17.583333333333336</v>
+      </c>
+      <c r="F93" s="7">
+        <v>49</v>
+      </c>
+      <c r="G93" s="2">
+        <v>51</v>
+      </c>
+      <c r="H93" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="3:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>46239</v>
+      </c>
       <c r="C94" s="9">
         <f>_xlfn.XLOOKUP(Log!A94, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D94" s="9">
+        <v>0.49694444444444447</v>
+      </c>
+      <c r="E94" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H94" s="2" t="str">
+        <v>19.600000000000026</v>
+      </c>
+      <c r="F94" s="7">
+        <v>51</v>
+      </c>
+      <c r="G94" s="2">
+        <v>52</v>
+      </c>
+      <c r="H94" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>46239</v>
+      </c>
       <c r="C95" s="9">
         <f>_xlfn.XLOOKUP(Log!A95, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D95" s="9">
+        <v>0.49833333333333335</v>
+      </c>
+      <c r="E95" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H95" s="2" t="str">
+        <v>21.600000000000019</v>
+      </c>
+      <c r="F95" s="7">
+        <v>51</v>
+      </c>
+      <c r="G95" s="2">
+        <v>54</v>
+      </c>
+      <c r="H95" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>46239</v>
+      </c>
       <c r="C96" s="9">
         <f>_xlfn.XLOOKUP(Log!A96, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D96" s="9">
+        <v>0.49972222222222223</v>
+      </c>
+      <c r="E96" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H96" s="2" t="str">
+        <v>23.600000000000012</v>
+      </c>
+      <c r="F96" s="7">
+        <v>52</v>
+      </c>
+      <c r="G96" s="2">
+        <v>55</v>
+      </c>
+      <c r="H96" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>46239</v>
+      </c>
       <c r="C97" s="9">
         <f>_xlfn.XLOOKUP(Log!A97, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D97" s="9">
+        <v>0.50111111111111106</v>
+      </c>
+      <c r="E97" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H97" s="2" t="str">
+        <v>25.599999999999923</v>
+      </c>
+      <c r="F97" s="7">
+        <v>54</v>
+      </c>
+      <c r="G97" s="2">
+        <v>55</v>
+      </c>
+      <c r="H97" s="2">
         <f t="shared" ref="H97:H160" si="5">IF(AND(G97&lt;&gt;"",F97&lt;&gt;""),G97-F97,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>46239</v>
+      </c>
       <c r="C98" s="9">
         <f>_xlfn.XLOOKUP(Log!A98, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D98" s="9">
+        <v>0.5025115740740741</v>
+      </c>
+      <c r="E98" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H98" s="2" t="str">
+        <v>27.616666666666696</v>
+      </c>
+      <c r="F98" s="7">
+        <v>54</v>
+      </c>
+      <c r="G98" s="2">
+        <v>57</v>
+      </c>
+      <c r="H98" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>46239</v>
+      </c>
       <c r="C99" s="9">
         <f>_xlfn.XLOOKUP(Log!A99, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D99" s="9">
+        <v>0.50391203703703702</v>
+      </c>
+      <c r="E99" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H99" s="2" t="str">
+        <v>29.633333333333304</v>
+      </c>
+      <c r="F99" s="7">
+        <v>55</v>
+      </c>
+      <c r="G99" s="2">
+        <v>57</v>
+      </c>
+      <c r="H99" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="3:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>46239</v>
+      </c>
       <c r="C100" s="9">
         <f>_xlfn.XLOOKUP(Log!A100, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E100" s="6" t="str">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D100" s="9">
+        <v>0.5053009259259259</v>
+      </c>
+      <c r="E100" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H100" s="2" t="str">
+        <v>31.633333333333297</v>
+      </c>
+      <c r="F100" s="7">
+        <v>55</v>
+      </c>
+      <c r="G100" s="2">
+        <v>58</v>
+      </c>
+      <c r="H100" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C101" s="9">
         <f>_xlfn.XLOOKUP(Log!A101, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -5999,7 +6285,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C102" s="9">
         <f>_xlfn.XLOOKUP(Log!A102, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6013,7 +6299,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C103" s="9">
         <f>_xlfn.XLOOKUP(Log!A103, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6027,7 +6313,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C104" s="9">
         <f>_xlfn.XLOOKUP(Log!A104, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6041,7 +6327,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C105" s="9">
         <f>_xlfn.XLOOKUP(Log!A105, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6055,7 +6341,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C106" s="9">
         <f>_xlfn.XLOOKUP(Log!A106, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6069,7 +6355,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C107" s="9">
         <f>_xlfn.XLOOKUP(Log!A107, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6083,7 +6369,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C108" s="9">
         <f>_xlfn.XLOOKUP(Log!A108, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6097,7 +6383,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C109" s="9">
         <f>_xlfn.XLOOKUP(Log!A109, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6111,7 +6397,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C110" s="9">
         <f>_xlfn.XLOOKUP(Log!A110, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6125,7 +6411,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C111" s="9">
         <f>_xlfn.XLOOKUP(Log!A111, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6139,7 +6425,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C112" s="9">
         <f>_xlfn.XLOOKUP(Log!A112, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -12160,7 +12446,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45 A2:C1048576">
+  <conditionalFormatting sqref="A2:C1048576 D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
@@ -12386,7 +12672,7 @@
         <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
         <v>21.583333333333243</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="27" t="s">
         <v>44</v>
       </c>
     </row>
@@ -12408,7 +12694,7 @@
         <v>21.216666666666654</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46238</v>
       </c>
@@ -12421,20 +12707,33 @@
       <c r="D12" s="8">
         <v>0.42986111111111114</v>
       </c>
-      <c r="E12" s="25" t="str">
+      <c r="E12" s="25">
         <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>–</v>
+        <v>21.066666666666627</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="E13" s="25" t="str">
+      <c r="A13" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46239</v>
+      </c>
+      <c r="C13" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="E13" s="25">
         <f>IF(AND(D13&lt;&gt;"", C13&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>19.600000000000026</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -13108,185 +13407,191 @@
   <dimension ref="A1:Y7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" style="43" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="41"/>
-    <col min="3" max="20" width="6.77734375" style="42" customWidth="1"/>
-    <col min="21" max="21" width="2.77734375" style="38" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="39"/>
-    <col min="23" max="25" width="10.77734375" style="38" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="38"/>
+    <col min="1" max="1" width="25.77734375" style="41" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="39"/>
+    <col min="3" max="20" width="6.77734375" style="40" customWidth="1"/>
+    <col min="21" max="21" width="2.77734375" style="36" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="37"/>
+    <col min="23" max="25" width="10.77734375" style="36" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="31" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:25" s="30" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="V1" s="31"/>
+    </row>
+    <row r="2" spans="1:25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="V1" s="32"/>
-    </row>
-    <row r="2" spans="1:25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="50"/>
+      <c r="V2" s="32"/>
+    </row>
+    <row r="3" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="35" t="str" cm="1">
+        <f t="array" ref="C3:T3">LEFT(TRANSPOSE('[1]Data-Lists'!A2:A19), 3)</f>
+        <v xml:space="preserve">#1 </v>
+      </c>
+      <c r="D3" s="35" t="str">
+        <v xml:space="preserve">#2 </v>
+      </c>
+      <c r="E3" s="35" t="str">
+        <v xml:space="preserve">#3 </v>
+      </c>
+      <c r="F3" s="35" t="str">
+        <v xml:space="preserve">#4 </v>
+      </c>
+      <c r="G3" s="35" t="str">
+        <v xml:space="preserve">#5 </v>
+      </c>
+      <c r="H3" s="35" t="str">
+        <v xml:space="preserve">#6 </v>
+      </c>
+      <c r="I3" s="46" t="str">
+        <v xml:space="preserve">#7 </v>
+      </c>
+      <c r="J3" s="46" t="str">
+        <v xml:space="preserve">#8 </v>
+      </c>
+      <c r="K3" s="35" t="str">
+        <v xml:space="preserve">#9 </v>
+      </c>
+      <c r="L3" s="35" t="str">
+        <v>#10</v>
+      </c>
+      <c r="M3" s="35" t="str">
+        <v>#11</v>
+      </c>
+      <c r="N3" s="35" t="str">
+        <v>#12</v>
+      </c>
+      <c r="O3" s="46" t="str">
+        <v>#13</v>
+      </c>
+      <c r="P3" s="35" t="str">
+        <v>#14</v>
+      </c>
+      <c r="Q3" s="35" t="str">
+        <v>#15</v>
+      </c>
+      <c r="R3" s="35" t="str">
+        <v>#16</v>
+      </c>
+      <c r="S3" s="35" t="str">
+        <v>#17</v>
+      </c>
+      <c r="T3" s="35" t="str">
+        <v>#18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" s="38">
+        <v>46238</v>
+      </c>
+      <c r="C4" s="42">
+        <v>5</v>
+      </c>
+      <c r="D4" s="42">
+        <v>5</v>
+      </c>
+      <c r="E4" s="42">
+        <v>2</v>
+      </c>
+      <c r="F4" s="42">
+        <v>2</v>
+      </c>
+      <c r="G4" s="42">
+        <v>2</v>
+      </c>
+      <c r="H4" s="42">
+        <v>2</v>
+      </c>
+      <c r="I4" s="42">
+        <v>2</v>
+      </c>
+      <c r="J4" s="42">
+        <v>2</v>
+      </c>
+      <c r="K4" s="42">
+        <v>2</v>
+      </c>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42">
+        <v>1</v>
+      </c>
+      <c r="S4" s="42">
+        <v>1</v>
+      </c>
+      <c r="T4" s="42">
+        <v>2</v>
+      </c>
+      <c r="W4" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="47"/>
-      <c r="V2" s="33"/>
-    </row>
-    <row r="3" spans="1:25" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="36" t="str" cm="1">
-        <f t="array" ref="C3:T3">LEFT(TRANSPOSE([1]Lists!A2:A19), 3)</f>
-        <v xml:space="preserve">#1 </v>
-      </c>
-      <c r="D3" s="36" t="str">
-        <v xml:space="preserve">#2 </v>
-      </c>
-      <c r="E3" s="36" t="str">
-        <v xml:space="preserve">#3 </v>
-      </c>
-      <c r="F3" s="36" t="str">
-        <v xml:space="preserve">#4 </v>
-      </c>
-      <c r="G3" s="36" t="str">
-        <v xml:space="preserve">#5 </v>
-      </c>
-      <c r="H3" s="36" t="str">
-        <v xml:space="preserve">#6 </v>
-      </c>
-      <c r="I3" s="36" t="str">
-        <v xml:space="preserve">#7 </v>
-      </c>
-      <c r="J3" s="37" t="str">
-        <v xml:space="preserve">#8 </v>
-      </c>
-      <c r="K3" s="36" t="str">
-        <v xml:space="preserve">#9 </v>
-      </c>
-      <c r="L3" s="36" t="str">
-        <v>#10</v>
-      </c>
-      <c r="M3" s="36" t="str">
-        <v>#11</v>
-      </c>
-      <c r="N3" s="36" t="str">
-        <v>#12</v>
-      </c>
-      <c r="O3" s="37" t="str">
-        <v>#13</v>
-      </c>
-      <c r="P3" s="36" t="str">
-        <v>#14</v>
-      </c>
-      <c r="Q3" s="36" t="str">
-        <v>#15</v>
-      </c>
-      <c r="R3" s="36" t="str">
-        <v>#16</v>
-      </c>
-      <c r="S3" s="36" t="str">
-        <v>#17</v>
-      </c>
-      <c r="T3" s="36" t="str">
-        <v>#18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="40">
-        <v>46238</v>
-      </c>
-      <c r="C4" s="44">
-        <v>3</v>
-      </c>
-      <c r="D4" s="44">
-        <v>3</v>
-      </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44">
-        <v>1</v>
-      </c>
-      <c r="S4" s="44">
-        <v>1</v>
-      </c>
-      <c r="T4" s="44">
-        <v>2</v>
-      </c>
-      <c r="V4" s="48"/>
-      <c r="W4" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="49"/>
+      <c r="A5" s="38"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V6" s="48"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="49"/>
+      <c r="X6" s="43"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V7" s="48"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="49"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\EPSURIS Internship (Vicon)\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9030D01B-764E-4BC0-A0CE-D8E29AA06B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683BE9AF-6F55-491E-9784-81250A6FE53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -1260,6 +1260,9 @@
                 <c:pt idx="10">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1301,6 +1304,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1387,6 +1393,9 @@
                 <c:pt idx="10">
                   <c:v>46239</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1430,7 +1439,7 @@
                   <c:v>19.600000000000026</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>20.133333333333336</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -3174,17 +3183,18 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Instructions"/>
+      <sheetName val="WIP"/>
       <sheetName val="Data-Lists"/>
-      <sheetName val="Camera Labelling"/>
-      <sheetName val="Log"/>
-      <sheetName val="Daily Summary"/>
+      <sheetName val="Labelling"/>
+      <sheetName val="Daily Log"/>
+      <sheetName val="Secondary Log"/>
+      <sheetName val="Daily Recap"/>
+      <sheetName val="Trial Recap"/>
+      <sheetName val="Error Recap"/>
       <sheetName val="Camera Error Trend"/>
       <sheetName val="Camera Performance Trends"/>
       <sheetName val="High Error Cameras"/>
       <sheetName val="Problem Cameras"/>
-      <sheetName val="Error Log"/>
-      <sheetName val="Error Summary"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -3289,6 +3299,7 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6272,230 +6283,422 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>46240</v>
+      </c>
       <c r="C101" s="9">
         <f>_xlfn.XLOOKUP(Log!A101, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D101" s="9">
+        <v>0.44027777777777777</v>
+      </c>
+      <c r="E101" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H101" s="2" t="str">
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F101" s="7">
+        <v>32</v>
+      </c>
+      <c r="G101" s="2">
+        <v>33</v>
+      </c>
+      <c r="H101" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>46240</v>
+      </c>
       <c r="C102" s="9">
         <f>_xlfn.XLOOKUP(Log!A102, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E102" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D102" s="9">
+        <v>0.44170138888888888</v>
+      </c>
+      <c r="E102" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H102" s="2" t="str">
+        <v>4.0499999999999936</v>
+      </c>
+      <c r="F102" s="7">
+        <v>35</v>
+      </c>
+      <c r="G102" s="2">
+        <v>36</v>
+      </c>
+      <c r="H102" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>46240</v>
+      </c>
       <c r="C103" s="9">
         <f>_xlfn.XLOOKUP(Log!A103, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D103" s="9">
+        <v>0.44310185185185186</v>
+      </c>
+      <c r="E103" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H103" s="2" t="str">
+        <v>6.0666666666666824</v>
+      </c>
+      <c r="F103" s="7">
+        <v>38</v>
+      </c>
+      <c r="G103" s="2">
+        <v>41</v>
+      </c>
+      <c r="H103" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>46240</v>
+      </c>
       <c r="C104" s="9">
         <f>_xlfn.XLOOKUP(Log!A104, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E104" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D104" s="9">
+        <v>0.44450231481481484</v>
+      </c>
+      <c r="E104" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H104" s="2" t="str">
+        <v>8.0833333333333712</v>
+      </c>
+      <c r="F104" s="7">
+        <v>41</v>
+      </c>
+      <c r="G104" s="2">
+        <v>44</v>
+      </c>
+      <c r="H104" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>46240</v>
+      </c>
       <c r="C105" s="9">
         <f>_xlfn.XLOOKUP(Log!A105, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D105" s="9">
+        <v>0.44590277777777776</v>
+      </c>
+      <c r="E105" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H105" s="2" t="str">
+        <v>10.09999999999998</v>
+      </c>
+      <c r="F105" s="7">
+        <v>44</v>
+      </c>
+      <c r="G105" s="2">
+        <v>45</v>
+      </c>
+      <c r="H105" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>46240</v>
+      </c>
       <c r="C106" s="9">
         <f>_xlfn.XLOOKUP(Log!A106, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E106" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D106" s="9">
+        <v>0.44729166666666664</v>
+      </c>
+      <c r="E106" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H106" s="2" t="str">
+        <v>12.099999999999973</v>
+      </c>
+      <c r="F106" s="7">
+        <v>44</v>
+      </c>
+      <c r="G106" s="2">
+        <v>47</v>
+      </c>
+      <c r="H106" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>46240</v>
+      </c>
       <c r="C107" s="9">
         <f>_xlfn.XLOOKUP(Log!A107, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E107" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D107" s="9">
+        <v>0.44868055555555558</v>
+      </c>
+      <c r="E107" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H107" s="2" t="str">
+        <v>14.100000000000046</v>
+      </c>
+      <c r="F107" s="7">
+        <v>47</v>
+      </c>
+      <c r="G107" s="2">
+        <v>49</v>
+      </c>
+      <c r="H107" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>46240</v>
+      </c>
       <c r="C108" s="9">
         <f>_xlfn.XLOOKUP(Log!A108, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E108" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D108" s="9">
+        <v>0.45008101851851851</v>
+      </c>
+      <c r="E108" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H108" s="2" t="str">
+        <v>16.116666666666653</v>
+      </c>
+      <c r="F108" s="7">
+        <v>48</v>
+      </c>
+      <c r="G108" s="2">
+        <v>51</v>
+      </c>
+      <c r="H108" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>46240</v>
+      </c>
       <c r="C109" s="9">
         <f>_xlfn.XLOOKUP(Log!A109, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E109" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D109" s="9">
+        <v>0.45148148148148148</v>
+      </c>
+      <c r="E109" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H109" s="2" t="str">
+        <v>18.133333333333344</v>
+      </c>
+      <c r="F109" s="7">
+        <v>49</v>
+      </c>
+      <c r="G109" s="2">
+        <v>52</v>
+      </c>
+      <c r="H109" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>46240</v>
+      </c>
       <c r="C110" s="9">
         <f>_xlfn.XLOOKUP(Log!A110, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D110" s="9">
+        <v>0.45287037037037037</v>
+      </c>
+      <c r="E110" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H110" s="2" t="str">
+        <v>20.133333333333336</v>
+      </c>
+      <c r="F110" s="7">
+        <v>51</v>
+      </c>
+      <c r="G110" s="2">
+        <v>52</v>
+      </c>
+      <c r="H110" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>46240</v>
+      </c>
       <c r="C111" s="9">
         <f>_xlfn.XLOOKUP(Log!A111, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E111" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D111" s="9">
+        <v>0.45425925925925925</v>
+      </c>
+      <c r="E111" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H111" s="2" t="str">
+        <v>22.133333333333329</v>
+      </c>
+      <c r="F111" s="7">
+        <v>51</v>
+      </c>
+      <c r="G111" s="2">
+        <v>54</v>
+      </c>
+      <c r="H111" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>46240</v>
+      </c>
       <c r="C112" s="9">
         <f>_xlfn.XLOOKUP(Log!A112, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E112" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D112" s="9">
+        <v>0.45565972222222223</v>
+      </c>
+      <c r="E112" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H112" s="2" t="str">
+        <v>24.15000000000002</v>
+      </c>
+      <c r="F112" s="7">
+        <v>52</v>
+      </c>
+      <c r="G112" s="2">
+        <v>55</v>
+      </c>
+      <c r="H112" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>46240</v>
+      </c>
       <c r="C113" s="9">
         <f>_xlfn.XLOOKUP(Log!A113, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E113" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D113" s="9">
+        <v>0.45704861111111111</v>
+      </c>
+      <c r="E113" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H113" s="2" t="str">
+        <v>26.150000000000013</v>
+      </c>
+      <c r="F113" s="7">
+        <v>54</v>
+      </c>
+      <c r="G113" s="2">
+        <v>55</v>
+      </c>
+      <c r="H113" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>46240</v>
+      </c>
       <c r="C114" s="9">
         <f>_xlfn.XLOOKUP(Log!A114, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E114" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D114" s="9">
+        <v>0.4584375</v>
+      </c>
+      <c r="E114" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H114" s="2" t="str">
+        <v>28.150000000000006</v>
+      </c>
+      <c r="F114" s="7">
+        <v>54</v>
+      </c>
+      <c r="G114" s="2">
+        <v>57</v>
+      </c>
+      <c r="H114" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>46240</v>
+      </c>
       <c r="C115" s="9">
         <f>_xlfn.XLOOKUP(Log!A115, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E115" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D115" s="9">
+        <v>0.45983796296296298</v>
+      </c>
+      <c r="E115" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H115" s="2" t="str">
+        <v>30.166666666666693</v>
+      </c>
+      <c r="F115" s="7">
+        <v>55</v>
+      </c>
+      <c r="G115" s="2">
+        <v>58</v>
+      </c>
+      <c r="H115" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>46240</v>
+      </c>
       <c r="C116" s="9">
         <f>_xlfn.XLOOKUP(Log!A116, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E116" s="6" t="str">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D116" s="9">
+        <v>0.46122685185185186</v>
+      </c>
+      <c r="E116" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H116" s="2" t="str">
+        <v>32.166666666666686</v>
+      </c>
+      <c r="F116" s="7">
+        <v>55</v>
+      </c>
+      <c r="G116" s="2">
+        <v>58</v>
+      </c>
+      <c r="H116" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C117" s="9">
         <f>_xlfn.XLOOKUP(Log!A117, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6509,7 +6712,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C118" s="9">
         <f>_xlfn.XLOOKUP(Log!A118, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6523,7 +6726,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C119" s="9">
         <f>_xlfn.XLOOKUP(Log!A119, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6537,7 +6740,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C120" s="9">
         <f>_xlfn.XLOOKUP(Log!A120, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6551,7 +6754,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C121" s="9">
         <f>_xlfn.XLOOKUP(Log!A121, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6565,7 +6768,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C122" s="9">
         <f>_xlfn.XLOOKUP(Log!A122, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6579,7 +6782,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C123" s="9">
         <f>_xlfn.XLOOKUP(Log!A123, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6593,7 +6796,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C124" s="9">
         <f>_xlfn.XLOOKUP(Log!A124, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6607,7 +6810,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C125" s="9">
         <f>_xlfn.XLOOKUP(Log!A125, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6621,7 +6824,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C126" s="9">
         <f>_xlfn.XLOOKUP(Log!A126, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6635,7 +6838,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C127" s="9">
         <f>_xlfn.XLOOKUP(Log!A127, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -6649,7 +6852,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C128" s="9">
         <f>_xlfn.XLOOKUP(Log!A128, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -12446,7 +12649,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="A2:C1048576 D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45">
+  <conditionalFormatting sqref="D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45 A2:C1048576">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
@@ -12737,11 +12940,21 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="E14" s="25" t="str">
+      <c r="A14" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46240</v>
+      </c>
+      <c r="C14" s="2">
+        <v>24</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="E14" s="25">
         <f>IF(AND(D14&lt;&gt;"", C14&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>20.133333333333336</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\EPSURIS Internship (Vicon)\Public Files\Documentation Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683BE9AF-6F55-491E-9784-81250A6FE53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ED750D-F7ED-45AF-829D-E348694C3C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
     <sheet name="Log" sheetId="1" r:id="rId2"/>
     <sheet name="Daily Summary" sheetId="2" r:id="rId3"/>
     <sheet name="Visualisations" sheetId="3" r:id="rId4"/>
-    <sheet name="DevScriptErrors" sheetId="5" r:id="rId5"/>
+    <sheet name="DevScriptErrors" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId6"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>Starting Time</t>
   </si>
@@ -521,6 +521,38 @@
   <si>
     <t>startup time may be off by 30 seconds, recorded after start</t>
   </si>
+  <si>
+    <t>no longer tracking - bug fixed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Next chart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - camera temperature at time (avg. between low/high no error data) cross-referenced against starting temperature</t>
+    </r>
+  </si>
+  <si>
+    <t>Attempted to cool room prior to test but thermostat is locked to 23° range and does not cool room quickly - room temperature used</t>
+  </si>
+  <si>
+    <t>initial recording/camera startup time slightly delayed by interruption</t>
+  </si>
 </sst>
 </file>
 
@@ -531,7 +563,7 @@
     <numFmt numFmtId="165" formatCode="hh:mm:ss;@"/>
     <numFmt numFmtId="166" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -736,6 +768,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -930,7 +969,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1058,6 +1097,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1263,6 +1305,15 @@
                 <c:pt idx="11">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46242</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46245</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1307,6 +1358,15 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1396,6 +1456,15 @@
                 <c:pt idx="11">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46242</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46245</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1442,13 +1511,13 @@
                   <c:v>20.133333333333336</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>19.616666666666642</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>18.850000000000069</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>21.350000000000058</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -1924,7 +1993,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
-  <c:roundedCorners val="1"/>
+  <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
@@ -1935,519 +2004,41 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB"/>
-              <a:t>Camera temperature vs minutes since start</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="8.0346666666666663E-2"/>
-          <c:y val="2.1528333333333333E-2"/>
-          <c:w val="0.88248819444444448"/>
-          <c:h val="0.8724561111111111"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>25 Jul (high)</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Log!$E$3:$E$8</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>2.9999999999999893</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.999999999999968</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>19.000000000000092</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25.000000000000071</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40.000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>63.000000000000099</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Log!$G$3:$G$8</c:f>
-              <c:numCache>
-                <c:formatCode>0.0\°\ \(\C\)</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>61</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AAB1-499E-AC05-854E44FBC272}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>25 Jul (low)</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Log!$E$3:$E$8</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>2.9999999999999893</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.999999999999968</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>19.000000000000092</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25.000000000000071</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40.000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>63.000000000000099</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Log!$F$3:$F$8</c:f>
-              <c:numCache>
-                <c:formatCode>0.0\°\ \(\C\)</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AAB1-499E-AC05-854E44FBC272}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>27 Jul (high)</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Log!$E$9:$E$13</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>3.0000000000001492</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.000000000000124</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16.000000000000185</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24.000000000000234</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>43.000000000000171</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Log!$G$9:$G$13</c:f>
-              <c:numCache>
-                <c:formatCode>0.0\°\ \(\C\)</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AAB1-499E-AC05-854E44FBC272}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>27 Jul (low)</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Log!$E$9:$E$13</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>3.0000000000001492</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10.000000000000124</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16.000000000000185</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24.000000000000234</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>43.000000000000171</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Log!$F$9:$F$13</c:f>
-              <c:numCache>
-                <c:formatCode>0.0\°\ \(\C\)</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>57</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-AAB1-499E-AC05-854E44FBC272}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>28 Jul (high)</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Log!$E$14:$E$18</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>3.0000000000000693</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15.000000000000027</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>26.000000000000068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>34.000000000000121</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>45</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Log!$G$14:$G$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0\°\ \(\C\)</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>61</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-AAB1-499E-AC05-854E44FBC272}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:v>28 Jul (low)</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Log!$E$14:$E$18</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>3.0000000000000693</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15.000000000000027</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>26.000000000000068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>34.000000000000121</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>45</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Log!$F$14:$F$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0\°\ \(\C\)</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>57</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-AAB1-499E-AC05-854E44FBC272}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -2456,86 +2047,160 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="10"/>
-        <c:axId val="20"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="10"/>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="505666224"/>
+        <c:axId val="512736368"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="505666224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Minutes since start</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="20"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="512736368"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="20"/>
+        <c:axId val="512736368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Temperature (°C)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="0.0\°\ \(\C\)" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="505666224"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="1"/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -2545,6 +2210,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3100,6 +2805,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3140,26 +3361,29 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>259080</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7200000" cy="3600000"/>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE94728B-DDB7-4468-8EF4-F3B9EE38BF02}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F46A80B-2967-17AE-2CEC-2B53FF16C346}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3172,7 +3396,7 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3183,123 +3407,10 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="WIP"/>
-      <sheetName val="Data-Lists"/>
-      <sheetName val="Labelling"/>
-      <sheetName val="Daily Log"/>
-      <sheetName val="Secondary Log"/>
-      <sheetName val="Daily Recap"/>
-      <sheetName val="Trial Recap"/>
-      <sheetName val="Error Recap"/>
-      <sheetName val="Camera Error Trend"/>
-      <sheetName val="Camera Performance Trends"/>
-      <sheetName val="High Error Cameras"/>
-      <sheetName val="Problem Cameras"/>
+      <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>#1 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>#2 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>#3 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>#4 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>#5 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>#6 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>#7 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>#8 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>#9 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>#10 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>#11 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>#12 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>#13 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>#14 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>#15 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>#16 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>#17 (Vero v2.2)</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>#18 (Vero v2.2)</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
+      <sheetData sheetId="0" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6699,678 +6810,1254 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>46242</v>
+      </c>
       <c r="C117" s="9">
         <f>_xlfn.XLOOKUP(Log!A117, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E117" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D117" s="9">
+        <v>0.55972222222222223</v>
+      </c>
+      <c r="E117" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H117" s="2" t="str">
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F117" s="7">
+        <v>31</v>
+      </c>
+      <c r="G117" s="2">
+        <v>33</v>
+      </c>
+      <c r="H117" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>46242</v>
+      </c>
       <c r="C118" s="9">
         <f>_xlfn.XLOOKUP(Log!A118, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E118" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D118" s="9">
+        <v>0.56081018518518522</v>
+      </c>
+      <c r="E118" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H118" s="2" t="str">
+        <v>3.5666666666666913</v>
+      </c>
+      <c r="F118" s="7">
+        <v>33</v>
+      </c>
+      <c r="G118" s="2">
+        <v>35</v>
+      </c>
+      <c r="H118" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>46242</v>
+      </c>
       <c r="C119" s="9">
         <f>_xlfn.XLOOKUP(Log!A119, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E119" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D119" s="9">
+        <v>0.5621990740740741</v>
+      </c>
+      <c r="E119" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H119" s="2" t="str">
+        <v>5.5666666666666842</v>
+      </c>
+      <c r="F119" s="7">
+        <v>38</v>
+      </c>
+      <c r="G119" s="2">
+        <v>39</v>
+      </c>
+      <c r="H119" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>46242</v>
+      </c>
       <c r="C120" s="9">
         <f>_xlfn.XLOOKUP(Log!A120, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E120" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D120" s="9">
+        <v>0.56359953703703702</v>
+      </c>
+      <c r="E120" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H120" s="2" t="str">
+        <v>7.5833333333332931</v>
+      </c>
+      <c r="F120" s="7">
+        <v>39</v>
+      </c>
+      <c r="G120" s="2">
+        <v>42</v>
+      </c>
+      <c r="H120" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>46242</v>
+      </c>
       <c r="C121" s="9">
         <f>_xlfn.XLOOKUP(Log!A121, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E121" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D121" s="9">
+        <v>0.56498842592592591</v>
+      </c>
+      <c r="E121" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H121" s="2" t="str">
+        <v>9.583333333333286</v>
+      </c>
+      <c r="F121" s="7">
+        <v>42</v>
+      </c>
+      <c r="G121" s="2">
+        <v>45</v>
+      </c>
+      <c r="H121" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>46242</v>
+      </c>
       <c r="C122" s="9">
         <f>_xlfn.XLOOKUP(Log!A122, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E122" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D122" s="9">
+        <v>0.56637731481481479</v>
+      </c>
+      <c r="E122" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H122" s="2" t="str">
+        <v>11.583333333333279</v>
+      </c>
+      <c r="F122" s="7">
+        <v>44</v>
+      </c>
+      <c r="G122" s="2">
+        <v>47</v>
+      </c>
+      <c r="H122" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>46242</v>
+      </c>
       <c r="C123" s="9">
         <f>_xlfn.XLOOKUP(Log!A123, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E123" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D123" s="9">
+        <v>0.56777777777777783</v>
+      </c>
+      <c r="E123" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H123" s="2" t="str">
+        <v>13.600000000000048</v>
+      </c>
+      <c r="F123" s="7">
+        <v>45</v>
+      </c>
+      <c r="G123" s="2">
+        <v>49</v>
+      </c>
+      <c r="H123" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>46242</v>
+      </c>
       <c r="C124" s="9">
         <f>_xlfn.XLOOKUP(Log!A124, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E124" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D124" s="9">
+        <v>0.56916666666666671</v>
+      </c>
+      <c r="E124" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H124" s="2" t="str">
+        <v>15.600000000000041</v>
+      </c>
+      <c r="F124" s="7">
+        <v>48</v>
+      </c>
+      <c r="G124" s="2">
+        <v>49</v>
+      </c>
+      <c r="H124" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>46242</v>
+      </c>
       <c r="C125" s="9">
         <f>_xlfn.XLOOKUP(Log!A125, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E125" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D125" s="9">
+        <v>0.57056712962962963</v>
+      </c>
+      <c r="E125" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H125" s="2" t="str">
+        <v>17.616666666666649</v>
+      </c>
+      <c r="F125" s="7">
+        <v>48</v>
+      </c>
+      <c r="G125" s="2">
+        <v>52</v>
+      </c>
+      <c r="H125" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>46242</v>
+      </c>
       <c r="C126" s="9">
         <f>_xlfn.XLOOKUP(Log!A126, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E126" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D126" s="9">
+        <v>0.57195601851851852</v>
+      </c>
+      <c r="E126" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H126" s="2" t="str">
+        <v>19.616666666666642</v>
+      </c>
+      <c r="F126" s="7">
+        <v>51</v>
+      </c>
+      <c r="G126" s="2">
+        <v>52</v>
+      </c>
+      <c r="H126" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>46242</v>
+      </c>
       <c r="C127" s="9">
         <f>_xlfn.XLOOKUP(Log!A127, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E127" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D127" s="9">
+        <v>0.5733449074074074</v>
+      </c>
+      <c r="E127" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H127" s="2" t="str">
+        <v>21.616666666666635</v>
+      </c>
+      <c r="F127" s="7">
+        <v>51</v>
+      </c>
+      <c r="G127" s="2">
+        <v>54</v>
+      </c>
+      <c r="H127" s="2">
         <f t="shared" si="5"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>46242</v>
+      </c>
       <c r="C128" s="9">
         <f>_xlfn.XLOOKUP(Log!A128, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E128" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D128" s="9">
+        <v>0.57473379629629628</v>
+      </c>
+      <c r="E128" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H128" s="2" t="str">
+        <v>23.616666666666628</v>
+      </c>
+      <c r="F128" s="7">
+        <v>52</v>
+      </c>
+      <c r="G128" s="2">
+        <v>55</v>
+      </c>
+      <c r="H128" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>46242</v>
+      </c>
       <c r="C129" s="9">
         <f>_xlfn.XLOOKUP(Log!A129, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E129" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D129" s="9">
+        <v>0.57613425925925921</v>
+      </c>
+      <c r="E129" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H129" s="2" t="str">
+        <v>25.633333333333237</v>
+      </c>
+      <c r="F129" s="7">
+        <v>54</v>
+      </c>
+      <c r="G129" s="2">
+        <v>55</v>
+      </c>
+      <c r="H129" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>46242</v>
+      </c>
       <c r="C130" s="9">
         <f>_xlfn.XLOOKUP(Log!A130, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E130" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D130" s="9">
+        <v>0.5775231481481482</v>
+      </c>
+      <c r="E130" s="6">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H130" s="2" t="str">
+        <v>27.63333333333339</v>
+      </c>
+      <c r="F130" s="7">
+        <v>54</v>
+      </c>
+      <c r="G130" s="2">
+        <v>57</v>
+      </c>
+      <c r="H130" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>46242</v>
+      </c>
       <c r="C131" s="9">
         <f>_xlfn.XLOOKUP(Log!A131, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E131" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D131" s="9">
+        <v>0.57892361111111112</v>
+      </c>
+      <c r="E131" s="6">
         <f t="shared" ref="E131:E194" si="6">IF(AND($D131&lt;&gt;"", $C131&lt;&gt;""), ($D131-$C131)*1440, "")</f>
-        <v/>
-      </c>
-      <c r="H131" s="2" t="str">
+        <v>29.65</v>
+      </c>
+      <c r="F131" s="7">
+        <v>54</v>
+      </c>
+      <c r="G131" s="2">
+        <v>58</v>
+      </c>
+      <c r="H131" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>46242</v>
+      </c>
       <c r="C132" s="9">
         <f>_xlfn.XLOOKUP(Log!A132, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E132" s="6" t="str">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D132" s="9">
+        <v>0.58031250000000001</v>
+      </c>
+      <c r="E132" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H132" s="2" t="str">
+        <v>31.649999999999991</v>
+      </c>
+      <c r="F132" s="7">
+        <v>55</v>
+      </c>
+      <c r="G132" s="2">
+        <v>58</v>
+      </c>
+      <c r="H132" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>46244</v>
+      </c>
       <c r="C133" s="9">
         <f>_xlfn.XLOOKUP(Log!A133, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E133" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D133" s="9">
+        <v>0.44513888888888886</v>
+      </c>
+      <c r="E133" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H133" s="2" t="str">
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F133" s="7">
+        <v>28</v>
+      </c>
+      <c r="G133" s="2">
+        <v>30</v>
+      </c>
+      <c r="H133" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="3:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>46244</v>
+      </c>
       <c r="C134" s="9">
         <f>_xlfn.XLOOKUP(Log!A134, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E134" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D134" s="9">
+        <v>0.44570601851851854</v>
+      </c>
+      <c r="E134" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H134" s="2" t="str">
+        <v>2.8166666666667339</v>
+      </c>
+      <c r="F134" s="7">
+        <v>32</v>
+      </c>
+      <c r="G134" s="2">
+        <v>33</v>
+      </c>
+      <c r="H134" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>46244</v>
+      </c>
       <c r="C135" s="9">
         <f>_xlfn.XLOOKUP(Log!A135, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E135" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D135" s="9">
+        <v>0.44709490740740743</v>
+      </c>
+      <c r="E135" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H135" s="2" t="str">
+        <v>4.8166666666667268</v>
+      </c>
+      <c r="F135" s="7">
+        <v>38</v>
+      </c>
+      <c r="G135" s="2">
+        <v>39</v>
+      </c>
+      <c r="H135" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>46244</v>
+      </c>
       <c r="C136" s="9">
         <f>_xlfn.XLOOKUP(Log!A136, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E136" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D136" s="9">
+        <v>0.44848379629629631</v>
+      </c>
+      <c r="E136" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H136" s="2" t="str">
+        <v>6.8166666666667197</v>
+      </c>
+      <c r="F136" s="7">
+        <v>39</v>
+      </c>
+      <c r="G136" s="2">
+        <v>42</v>
+      </c>
+      <c r="H136" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>46244</v>
+      </c>
       <c r="C137" s="9">
         <f>_xlfn.XLOOKUP(Log!A137, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E137" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D137" s="9">
+        <v>0.44988425925925923</v>
+      </c>
+      <c r="E137" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H137" s="2" t="str">
+        <v>8.8333333333333286</v>
+      </c>
+      <c r="F137" s="7">
+        <v>41</v>
+      </c>
+      <c r="G137" s="2">
+        <v>45</v>
+      </c>
+      <c r="H137" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>46244</v>
+      </c>
       <c r="C138" s="9">
         <f>_xlfn.XLOOKUP(Log!A138, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E138" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D138" s="9">
+        <v>0.45127314814814817</v>
+      </c>
+      <c r="E138" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H138" s="2" t="str">
+        <v>10.833333333333401</v>
+      </c>
+      <c r="F138" s="7">
+        <v>44</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45</v>
+      </c>
+      <c r="H138" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>46244</v>
+      </c>
       <c r="C139" s="9">
         <f>_xlfn.XLOOKUP(Log!A139, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E139" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D139" s="9">
+        <v>0.45266203703703706</v>
+      </c>
+      <c r="E139" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H139" s="2" t="str">
+        <v>12.833333333333394</v>
+      </c>
+      <c r="F139" s="7">
+        <v>45</v>
+      </c>
+      <c r="G139" s="2">
+        <v>48</v>
+      </c>
+      <c r="H139" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>46244</v>
+      </c>
       <c r="C140" s="9">
         <f>_xlfn.XLOOKUP(Log!A140, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E140" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D140" s="9">
+        <v>0.45406249999999998</v>
+      </c>
+      <c r="E140" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H140" s="2" t="str">
+        <v>14.850000000000003</v>
+      </c>
+      <c r="F140" s="7">
+        <v>48</v>
+      </c>
+      <c r="G140" s="2">
+        <v>49</v>
+      </c>
+      <c r="H140" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>46244</v>
+      </c>
       <c r="C141" s="9">
         <f>_xlfn.XLOOKUP(Log!A141, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E141" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D141" s="9">
+        <v>0.45545138888888886</v>
+      </c>
+      <c r="E141" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H141" s="2" t="str">
+        <v>16.849999999999994</v>
+      </c>
+      <c r="F141" s="7">
+        <v>48</v>
+      </c>
+      <c r="G141" s="2">
+        <v>51</v>
+      </c>
+      <c r="H141" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>46244</v>
+      </c>
       <c r="C142" s="9">
         <f>_xlfn.XLOOKUP(Log!A142, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E142" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D142" s="9">
+        <v>0.4568402777777778</v>
+      </c>
+      <c r="E142" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H142" s="2" t="str">
+        <v>18.850000000000069</v>
+      </c>
+      <c r="F142" s="7">
+        <v>51</v>
+      </c>
+      <c r="G142" s="2">
+        <v>52</v>
+      </c>
+      <c r="H142" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>46244</v>
+      </c>
       <c r="C143" s="9">
         <f>_xlfn.XLOOKUP(Log!A143, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E143" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D143" s="9">
+        <v>0.45824074074074073</v>
+      </c>
+      <c r="E143" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H143" s="2" t="str">
+        <v>20.866666666666678</v>
+      </c>
+      <c r="F143" s="7">
+        <v>51</v>
+      </c>
+      <c r="G143" s="2">
+        <v>54</v>
+      </c>
+      <c r="H143" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>46244</v>
+      </c>
       <c r="C144" s="9">
         <f>_xlfn.XLOOKUP(Log!A144, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E144" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D144" s="9">
+        <v>0.45962962962962961</v>
+      </c>
+      <c r="E144" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H144" s="2" t="str">
+        <v>22.866666666666671</v>
+      </c>
+      <c r="F144" s="7">
+        <v>52</v>
+      </c>
+      <c r="G144" s="2">
+        <v>55</v>
+      </c>
+      <c r="H144" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>46244</v>
+      </c>
       <c r="C145" s="9">
         <f>_xlfn.XLOOKUP(Log!A145, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E145" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D145" s="9">
+        <v>0.46103009259259259</v>
+      </c>
+      <c r="E145" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H145" s="2" t="str">
+        <v>24.883333333333361</v>
+      </c>
+      <c r="F145" s="7">
+        <v>54</v>
+      </c>
+      <c r="G145" s="2">
+        <v>55</v>
+      </c>
+      <c r="H145" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>46244</v>
+      </c>
       <c r="C146" s="9">
         <f>_xlfn.XLOOKUP(Log!A146, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E146" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D146" s="9">
+        <v>0.46241898148148147</v>
+      </c>
+      <c r="E146" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H146" s="2" t="str">
+        <v>26.883333333333354</v>
+      </c>
+      <c r="F146" s="7">
+        <v>54</v>
+      </c>
+      <c r="G146" s="2">
+        <v>57</v>
+      </c>
+      <c r="H146" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>46244</v>
+      </c>
       <c r="C147" s="9">
         <f>_xlfn.XLOOKUP(Log!A147, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E147" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D147" s="9">
+        <v>0.46380787037037036</v>
+      </c>
+      <c r="E147" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H147" s="2" t="str">
+        <v>28.883333333333347</v>
+      </c>
+      <c r="F147" s="7">
+        <v>54</v>
+      </c>
+      <c r="G147" s="2">
+        <v>58</v>
+      </c>
+      <c r="H147" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>46244</v>
+      </c>
       <c r="C148" s="9">
         <f>_xlfn.XLOOKUP(Log!A148, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E148" s="6" t="str">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D148" s="9">
+        <v>0.46520833333333333</v>
+      </c>
+      <c r="E148" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H148" s="2" t="str">
+        <v>30.900000000000034</v>
+      </c>
+      <c r="F148" s="7">
+        <v>55</v>
+      </c>
+      <c r="G148" s="2">
+        <v>58</v>
+      </c>
+      <c r="H148" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>46245</v>
+      </c>
       <c r="C149" s="9">
         <f>_xlfn.XLOOKUP(Log!A149, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E149" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D149" s="9">
+        <v>0.38472222222222224</v>
+      </c>
+      <c r="E149" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H149" s="2" t="str">
+        <v>4.0000000000000657</v>
+      </c>
+      <c r="F149" s="7">
+        <v>35</v>
+      </c>
+      <c r="G149" s="2">
+        <v>36</v>
+      </c>
+      <c r="H149" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>46245</v>
+      </c>
       <c r="C150" s="9">
         <f>_xlfn.XLOOKUP(Log!A150, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E150" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D150" s="9">
+        <v>0.385625</v>
+      </c>
+      <c r="E150" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H150" s="2" t="str">
+        <v>5.3000000000000291</v>
+      </c>
+      <c r="F150" s="7">
+        <v>35</v>
+      </c>
+      <c r="G150" s="2">
+        <v>38</v>
+      </c>
+      <c r="H150" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>46245</v>
+      </c>
       <c r="C151" s="9">
         <f>_xlfn.XLOOKUP(Log!A151, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E151" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D151" s="9">
+        <v>0.38702546296296297</v>
+      </c>
+      <c r="E151" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H151" s="2" t="str">
+        <v>7.3166666666667179</v>
+      </c>
+      <c r="F151" s="7">
+        <v>38</v>
+      </c>
+      <c r="G151" s="2">
+        <v>41</v>
+      </c>
+      <c r="H151" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>46245</v>
+      </c>
       <c r="C152" s="9">
         <f>_xlfn.XLOOKUP(Log!A152, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E152" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D152" s="9">
+        <v>0.38841435185185186</v>
+      </c>
+      <c r="E152" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H152" s="2" t="str">
+        <v>9.3166666666667108</v>
+      </c>
+      <c r="F152" s="7">
+        <v>41</v>
+      </c>
+      <c r="G152" s="2">
+        <v>44</v>
+      </c>
+      <c r="H152" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>46245</v>
+      </c>
       <c r="C153" s="9">
         <f>_xlfn.XLOOKUP(Log!A153, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E153" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D153" s="9">
+        <v>0.38980324074074074</v>
+      </c>
+      <c r="E153" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H153" s="2" t="str">
+        <v>11.316666666666704</v>
+      </c>
+      <c r="F153" s="7">
+        <v>42</v>
+      </c>
+      <c r="G153" s="2">
+        <v>45</v>
+      </c>
+      <c r="H153" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>46245</v>
+      </c>
       <c r="C154" s="9">
         <f>_xlfn.XLOOKUP(Log!A154, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E154" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D154" s="9">
+        <v>0.39119212962962963</v>
+      </c>
+      <c r="E154" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H154" s="2" t="str">
+        <v>13.316666666666697</v>
+      </c>
+      <c r="F154" s="7">
+        <v>44</v>
+      </c>
+      <c r="G154" s="2">
+        <v>47</v>
+      </c>
+      <c r="H154" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>46245</v>
+      </c>
       <c r="C155" s="9">
         <f>_xlfn.XLOOKUP(Log!A155, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E155" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D155" s="9">
+        <v>0.3925925925925926</v>
+      </c>
+      <c r="E155" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H155" s="2" t="str">
+        <v>15.333333333333385</v>
+      </c>
+      <c r="F155" s="7">
+        <v>45</v>
+      </c>
+      <c r="G155" s="2">
+        <v>49</v>
+      </c>
+      <c r="H155" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>46245</v>
+      </c>
       <c r="C156" s="9">
         <f>_xlfn.XLOOKUP(Log!A156, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E156" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D156" s="9">
+        <v>0.39398148148148149</v>
+      </c>
+      <c r="E156" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H156" s="2" t="str">
+        <v>17.333333333333378</v>
+      </c>
+      <c r="F156" s="7">
+        <v>48</v>
+      </c>
+      <c r="G156" s="2">
+        <v>49</v>
+      </c>
+      <c r="H156" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>46245</v>
+      </c>
       <c r="C157" s="9">
         <f>_xlfn.XLOOKUP(Log!A157, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E157" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D157" s="9">
+        <v>0.39538194444444447</v>
+      </c>
+      <c r="E157" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H157" s="2" t="str">
+        <v>19.350000000000065</v>
+      </c>
+      <c r="F157" s="7">
+        <v>48</v>
+      </c>
+      <c r="G157" s="2">
+        <v>52</v>
+      </c>
+      <c r="H157" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>46245</v>
+      </c>
       <c r="C158" s="9">
         <f>_xlfn.XLOOKUP(Log!A158, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E158" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D158" s="9">
+        <v>0.39677083333333335</v>
+      </c>
+      <c r="E158" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H158" s="2" t="str">
+        <v>21.350000000000058</v>
+      </c>
+      <c r="F158" s="7">
+        <v>51</v>
+      </c>
+      <c r="G158" s="2">
+        <v>52</v>
+      </c>
+      <c r="H158" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>46245</v>
+      </c>
       <c r="C159" s="9">
         <f>_xlfn.XLOOKUP(Log!A159, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E159" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D159" s="9">
+        <v>0.39815972222222223</v>
+      </c>
+      <c r="E159" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H159" s="2" t="str">
+        <v>23.350000000000051</v>
+      </c>
+      <c r="F159" s="7">
+        <v>51</v>
+      </c>
+      <c r="G159" s="2">
+        <v>54</v>
+      </c>
+      <c r="H159" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>46245</v>
+      </c>
       <c r="C160" s="9">
         <f>_xlfn.XLOOKUP(Log!A160, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E160" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D160" s="9">
+        <v>0.39956018518518521</v>
+      </c>
+      <c r="E160" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H160" s="2" t="str">
+        <v>25.366666666666742</v>
+      </c>
+      <c r="F160" s="7">
+        <v>51</v>
+      </c>
+      <c r="G160" s="2">
+        <v>55</v>
+      </c>
+      <c r="H160" s="2">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>46245</v>
+      </c>
       <c r="C161" s="9">
         <f>_xlfn.XLOOKUP(Log!A161, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E161" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D161" s="9">
+        <v>0.40096064814814814</v>
+      </c>
+      <c r="E161" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H161" s="2" t="str">
+        <v>27.383333333333351</v>
+      </c>
+      <c r="F161" s="7">
+        <v>54</v>
+      </c>
+      <c r="G161" s="2">
+        <v>55</v>
+      </c>
+      <c r="H161" s="2">
         <f t="shared" ref="H161:H224" si="7">IF(AND(G161&lt;&gt;"",F161&lt;&gt;""),G161-F161,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>46245</v>
+      </c>
       <c r="C162" s="9">
         <f>_xlfn.XLOOKUP(Log!A162, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E162" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D162" s="9">
+        <v>0.40234953703703702</v>
+      </c>
+      <c r="E162" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H162" s="2" t="str">
+        <v>29.383333333333344</v>
+      </c>
+      <c r="F162" s="7">
+        <v>54</v>
+      </c>
+      <c r="G162" s="2">
+        <v>57</v>
+      </c>
+      <c r="H162" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>46245</v>
+      </c>
       <c r="C163" s="9">
         <f>_xlfn.XLOOKUP(Log!A163, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E163" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D163" s="9">
+        <v>0.40375</v>
+      </c>
+      <c r="E163" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H163" s="2" t="str">
+        <v>31.400000000000034</v>
+      </c>
+      <c r="F163" s="7">
+        <v>54</v>
+      </c>
+      <c r="G163" s="2">
+        <v>57</v>
+      </c>
+      <c r="H163" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>46245</v>
+      </c>
       <c r="C164" s="9">
         <f>_xlfn.XLOOKUP(Log!A164, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E164" s="6" t="str">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="D164" s="9">
+        <v>0.40513888888888888</v>
+      </c>
+      <c r="E164" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H164" s="2" t="str">
+        <v>33.400000000000027</v>
+      </c>
+      <c r="F164" s="7">
+        <v>54</v>
+      </c>
+      <c r="G164" s="2">
+        <v>58</v>
+      </c>
+      <c r="H164" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C165" s="9">
         <f>_xlfn.XLOOKUP(Log!A165, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7384,7 +8071,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C166" s="9">
         <f>_xlfn.XLOOKUP(Log!A166, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7398,7 +8085,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C167" s="9">
         <f>_xlfn.XLOOKUP(Log!A167, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7412,7 +8099,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C168" s="9">
         <f>_xlfn.XLOOKUP(Log!A168, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7426,7 +8113,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C169" s="9">
         <f>_xlfn.XLOOKUP(Log!A169, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7440,7 +8127,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C170" s="9">
         <f>_xlfn.XLOOKUP(Log!A170, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7454,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C171" s="9">
         <f>_xlfn.XLOOKUP(Log!A171, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7468,7 +8155,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C172" s="9">
         <f>_xlfn.XLOOKUP(Log!A172, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7482,7 +8169,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C173" s="9">
         <f>_xlfn.XLOOKUP(Log!A173, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7496,7 +8183,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C174" s="9">
         <f>_xlfn.XLOOKUP(Log!A174, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7510,7 +8197,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C175" s="9">
         <f>_xlfn.XLOOKUP(Log!A175, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -7524,7 +8211,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C176" s="9">
         <f>_xlfn.XLOOKUP(Log!A176, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -12649,7 +13336,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45 A2:C1048576">
+  <conditionalFormatting sqref="A2:C1048576 D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
@@ -12958,30 +13645,66 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="E15" s="25" t="str">
+      <c r="A15" s="1">
+        <v>46242</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C15" s="2">
+        <v>24</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="E15" s="25">
         <f>IF(AND(D15&lt;&gt;"", C15&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="E16" s="25" t="str">
+        <v>19.616666666666642</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46244</v>
+      </c>
+      <c r="C16" s="2">
+        <v>24</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="E16" s="25">
         <f>IF(AND(D16&lt;&gt;"", C16&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="E17" s="25" t="str">
+        <v>18.850000000000069</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46245</v>
+      </c>
+      <c r="C17" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="E17" s="25">
         <f>IF(AND(D17&lt;&gt;"", C17&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21.350000000000058</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="E18" s="25" t="str">
@@ -12989,7 +13712,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="E19" s="25" t="str">
@@ -12997,7 +13720,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="E20" s="25" t="str">
@@ -13005,7 +13728,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="E21" s="25" t="str">
@@ -13013,7 +13736,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="E22" s="25" t="str">
@@ -13021,7 +13744,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="E23" s="25" t="str">
@@ -13029,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="E24" s="25" t="str">
@@ -13037,7 +13760,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="E25" s="25" t="str">
@@ -13045,7 +13768,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="E26" s="25" t="str">
@@ -13053,7 +13776,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="E27" s="25" t="str">
@@ -13061,7 +13784,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="E28" s="25" t="str">
@@ -13069,7 +13792,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="E29" s="25" t="str">
@@ -13077,7 +13800,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="E30" s="25" t="str">
@@ -13085,7 +13808,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="E31" s="25" t="str">
@@ -13093,7 +13816,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="E32" s="25" t="str">
@@ -13583,6 +14306,9 @@
       <c r="C19" s="26" t="s">
         <v>43</v>
       </c>
+      <c r="K19" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.3">
       <c r="K23" s="17" t="s">
@@ -13617,7 +14343,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D01A83-1FDF-45BF-A1E3-B5167A4A0F21}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" style="41" customWidth="1"/>
@@ -13686,61 +14412,27 @@
       <c r="B3" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="35" t="str" cm="1">
-        <f t="array" ref="C3:T3">LEFT(TRANSPOSE('[1]Data-Lists'!A2:A19), 3)</f>
-        <v xml:space="preserve">#1 </v>
-      </c>
-      <c r="D3" s="35" t="str">
-        <v xml:space="preserve">#2 </v>
-      </c>
-      <c r="E3" s="35" t="str">
-        <v xml:space="preserve">#3 </v>
-      </c>
-      <c r="F3" s="35" t="str">
-        <v xml:space="preserve">#4 </v>
-      </c>
-      <c r="G3" s="35" t="str">
-        <v xml:space="preserve">#5 </v>
-      </c>
-      <c r="H3" s="35" t="str">
-        <v xml:space="preserve">#6 </v>
-      </c>
-      <c r="I3" s="46" t="str">
-        <v xml:space="preserve">#7 </v>
-      </c>
-      <c r="J3" s="46" t="str">
-        <v xml:space="preserve">#8 </v>
-      </c>
-      <c r="K3" s="35" t="str">
-        <v xml:space="preserve">#9 </v>
-      </c>
-      <c r="L3" s="35" t="str">
-        <v>#10</v>
-      </c>
-      <c r="M3" s="35" t="str">
-        <v>#11</v>
-      </c>
-      <c r="N3" s="35" t="str">
-        <v>#12</v>
-      </c>
-      <c r="O3" s="46" t="str">
-        <v>#13</v>
-      </c>
-      <c r="P3" s="35" t="str">
-        <v>#14</v>
-      </c>
-      <c r="Q3" s="35" t="str">
-        <v>#15</v>
-      </c>
-      <c r="R3" s="35" t="str">
-        <v>#16</v>
-      </c>
-      <c r="S3" s="35" t="str">
-        <v>#17</v>
-      </c>
-      <c r="T3" s="35" t="str">
-        <v>#18</v>
-      </c>
+      <c r="C3" s="35" t="e" cm="1">
+        <f t="array" ref="C3">LEFT(TRANSPOSE(#REF!), 3)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
@@ -13806,9 +14498,25 @@
       <c r="W7" s="43"/>
       <c r="X7" s="43"/>
     </row>
+    <row r="8" spans="1:25" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,21 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ED750D-F7ED-45AF-829D-E348694C3C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D591FFC-B0FD-4201-9022-4E91CDB604A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
     <sheet name="Log" sheetId="1" r:id="rId2"/>
     <sheet name="Daily Summary" sheetId="2" r:id="rId3"/>
-    <sheet name="Visualisations" sheetId="3" r:id="rId4"/>
-    <sheet name="DevScriptErrors" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Error Summary" sheetId="6" r:id="rId4"/>
+    <sheet name="Visualisations" sheetId="3" r:id="rId5"/>
+    <sheet name="DevScriptErrors" sheetId="5" state="hidden" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -96,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
   <si>
     <t>Starting Time</t>
   </si>
@@ -1133,6 +1131,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9B9B"/>
       <color rgb="FFBDD7EE"/>
       <color rgb="FF1F4E78"/>
       <color rgb="FFC65911"/>
@@ -1252,7 +1251,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
+            <c:symbol val="square"/>
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
@@ -1268,10 +1267,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Daily Summary'!$B$2:$B$100</c:f>
+              <c:f>'Daily Summary'!$B$2:$B$99</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>46228</c:v>
                 </c:pt>
@@ -1281,48 +1280,51 @@
                 <c:pt idx="2">
                   <c:v>46231</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="3">
                   <c:v>46232</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="4">
                   <c:v>46233</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="5">
                   <c:v>46234</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="6">
                   <c:v>46235</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="7">
                   <c:v>46237</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="8">
                   <c:v>46238</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="9">
                   <c:v>46239</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="10">
                   <c:v>46240</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="11">
                   <c:v>46242</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="12">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46245</c:v>
+                </c:pt>
                 <c:pt idx="14">
-                  <c:v>46245</c:v>
+                  <c:v>46246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Daily Summary'!$C$2:$C$100</c:f>
+              <c:f>'Daily Summary'!$C$2:$C$99</c:f>
               <c:numCache>
                 <c:formatCode>0.0\°\ \(\C\)</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>23.5</c:v>
                 </c:pt>
@@ -1333,28 +1335,28 @@
                   <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>24.5</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>25.5</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.5</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24</c:v>
+                  <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23.5</c:v>
+                  <c:v>24.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>24.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24.5</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>24</c:v>
@@ -1363,10 +1365,10 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>24</c:v>
+                  <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>23.5</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1378,6 +1380,20 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1072957472"/>
+        <c:axId val="1072952192"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -1403,7 +1419,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
+            <c:symbol val="square"/>
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
@@ -1419,10 +1435,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Daily Summary'!$B$2:$B$100</c:f>
+              <c:f>'Daily Summary'!$B$2:$B$99</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>46228</c:v>
                 </c:pt>
@@ -1432,48 +1448,51 @@
                 <c:pt idx="2">
                   <c:v>46231</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="3">
                   <c:v>46232</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="4">
                   <c:v>46233</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="5">
                   <c:v>46234</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="6">
                   <c:v>46235</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="7">
                   <c:v>46237</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="8">
                   <c:v>46238</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="9">
                   <c:v>46239</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="10">
                   <c:v>46240</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="11">
                   <c:v>46242</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="12">
                   <c:v>46244</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46245</c:v>
+                </c:pt>
                 <c:pt idx="14">
-                  <c:v>46245</c:v>
+                  <c:v>46246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Daily Summary'!$E$2:$E$100</c:f>
+              <c:f>'Daily Summary'!$E$2:$E$99</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>25.000000000000071</c:v>
                 </c:pt>
@@ -1484,40 +1503,40 @@
                   <c:v>26.000000000000068</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>15.999999999999943</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.999999999999943</c:v>
+                  <c:v>19.000000000000014</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19.000000000000014</c:v>
+                  <c:v>20.999999999999925</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.999999999999925</c:v>
+                  <c:v>21.583333333333243</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21.583333333333243</c:v>
+                  <c:v>21.216666666666654</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>21.216666666666654</c:v>
+                  <c:v>21.066666666666627</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>21.066666666666627</c:v>
+                  <c:v>19.600000000000026</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>19.600000000000026</c:v>
+                  <c:v>20.133333333333336</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.133333333333336</c:v>
+                  <c:v>19.616666666666642</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>19.616666666666642</c:v>
+                  <c:v>18.850000000000069</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.850000000000069</c:v>
+                  <c:v>21.350000000000058</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21.350000000000058</c:v>
+                  <c:v>21.449999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -1765,9 +1784,6 @@
                 <c:pt idx="96">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="97">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1786,8 +1802,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1072957472"/>
-        <c:axId val="1072952192"/>
+        <c:axId val="1965629424"/>
+        <c:axId val="1965623184"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="1072957472"/>
@@ -1810,7 +1826,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="dd/mm" sourceLinked="0"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
@@ -1911,6 +1927,68 @@
         </c:txPr>
         <c:crossAx val="1072957472"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1965623184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1965629424"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1965629424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1965623184"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -3400,22 +3478,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4256,16 +4318,16 @@
       <c r="B19" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="9" t="str">
         <f>_xlfn.XLOOKUP(Log!A19, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0.4284722222222222</v>
+        <v>Not found!</v>
       </c>
       <c r="D19" s="9">
         <v>0.43055555555555558</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>3.0000000000000693</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F19" s="7">
         <v>32</v>
@@ -4285,16 +4347,16 @@
       <c r="B20" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="9" t="str">
         <f>_xlfn.XLOOKUP(Log!A20, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0.4284722222222222</v>
+        <v>Not found!</v>
       </c>
       <c r="D20" s="9">
         <v>0.43402777777777779</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>8.0000000000000515</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F20" s="7">
         <v>40</v>
@@ -4314,16 +4376,16 @@
       <c r="B21" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="9" t="str">
         <f>_xlfn.XLOOKUP(Log!A21, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0.4284722222222222</v>
+        <v>Not found!</v>
       </c>
       <c r="D21" s="9">
         <v>0.43680555555555556</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>12.000000000000037</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F21" s="7">
         <v>44</v>
@@ -4340,16 +4402,16 @@
       <c r="A22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="9" t="str">
         <f>_xlfn.XLOOKUP(Log!A22, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0.4284722222222222</v>
+        <v>Not found!</v>
       </c>
       <c r="D22" s="9">
         <v>0.44027777777777777</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>17.000000000000021</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F22" s="7">
         <v>49</v>
@@ -4366,16 +4428,16 @@
       <c r="A23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="9" t="str">
         <f>_xlfn.XLOOKUP(Log!A23, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0.4284722222222222</v>
+        <v>Not found!</v>
       </c>
       <c r="D23" s="9">
         <v>0.44374999999999998</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F23" s="7">
         <v>52</v>
@@ -4392,16 +4454,16 @@
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="9" t="str">
         <f>_xlfn.XLOOKUP(Log!A24, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0.4284722222222222</v>
+        <v>Not found!</v>
       </c>
       <c r="D24" s="9">
         <v>0.4465277777777778</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>26.000000000000068</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F24" s="7">
         <v>54</v>
@@ -4418,16 +4480,16 @@
       <c r="A25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="9" t="str">
         <f>_xlfn.XLOOKUP(Log!A25, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0.4284722222222222</v>
+        <v>Not found!</v>
       </c>
       <c r="D25" s="9">
         <v>0.45069444444444445</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>32.000000000000043</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F25" s="7">
         <v>55</v>
@@ -8058,230 +8120,422 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>46246</v>
+      </c>
       <c r="C165" s="9">
         <f>_xlfn.XLOOKUP(Log!A165, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E165" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D165" s="9">
+        <v>0.41736111111111113</v>
+      </c>
+      <c r="E165" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H165" s="2" t="str">
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F165" s="7">
+        <v>27</v>
+      </c>
+      <c r="G165" s="2">
+        <v>29</v>
+      </c>
+      <c r="H165" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>46246</v>
+      </c>
       <c r="C166" s="9">
         <f>_xlfn.XLOOKUP(Log!A166, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E166" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D166" s="9">
+        <v>0.4183101851851852</v>
+      </c>
+      <c r="E166" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H166" s="2" t="str">
+        <v>3.36666666666666</v>
+      </c>
+      <c r="F166" s="7">
+        <v>32</v>
+      </c>
+      <c r="G166" s="2">
+        <v>33</v>
+      </c>
+      <c r="H166" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>46246</v>
+      </c>
       <c r="C167" s="9">
         <f>_xlfn.XLOOKUP(Log!A167, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E167" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D167" s="9">
+        <v>0.41969907407407409</v>
+      </c>
+      <c r="E167" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H167" s="2" t="str">
+        <v>5.3666666666666529</v>
+      </c>
+      <c r="F167" s="7">
+        <v>36</v>
+      </c>
+      <c r="G167" s="2">
+        <v>39</v>
+      </c>
+      <c r="H167" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>46246</v>
+      </c>
       <c r="C168" s="9">
         <f>_xlfn.XLOOKUP(Log!A168, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E168" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D168" s="9">
+        <v>0.42109953703703706</v>
+      </c>
+      <c r="E168" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H168" s="2" t="str">
+        <v>7.3833333333333417</v>
+      </c>
+      <c r="F168" s="7">
+        <v>39</v>
+      </c>
+      <c r="G168" s="2">
+        <v>42</v>
+      </c>
+      <c r="H168" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>46246</v>
+      </c>
       <c r="C169" s="9">
         <f>_xlfn.XLOOKUP(Log!A169, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E169" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D169" s="9">
+        <v>0.42248842592592595</v>
+      </c>
+      <c r="E169" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H169" s="2" t="str">
+        <v>9.3833333333333346</v>
+      </c>
+      <c r="F169" s="7">
+        <v>41</v>
+      </c>
+      <c r="G169" s="2">
+        <v>44</v>
+      </c>
+      <c r="H169" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>46246</v>
+      </c>
       <c r="C170" s="9">
         <f>_xlfn.XLOOKUP(Log!A170, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E170" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D170" s="9">
+        <v>0.42387731481481483</v>
+      </c>
+      <c r="E170" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H170" s="2" t="str">
+        <v>11.383333333333328</v>
+      </c>
+      <c r="F170" s="7">
+        <v>44</v>
+      </c>
+      <c r="G170" s="2">
+        <v>45</v>
+      </c>
+      <c r="H170" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>46246</v>
+      </c>
       <c r="C171" s="9">
         <f>_xlfn.XLOOKUP(Log!A171, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E171" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D171" s="9">
+        <v>0.42526620370370372</v>
+      </c>
+      <c r="E171" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H171" s="2" t="str">
+        <v>13.38333333333332</v>
+      </c>
+      <c r="F171" s="7">
+        <v>45</v>
+      </c>
+      <c r="G171" s="2">
+        <v>48</v>
+      </c>
+      <c r="H171" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>46246</v>
+      </c>
       <c r="C172" s="9">
         <f>_xlfn.XLOOKUP(Log!A172, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E172" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D172" s="9">
+        <v>0.42666666666666669</v>
+      </c>
+      <c r="E172" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H172" s="2" t="str">
+        <v>15.400000000000009</v>
+      </c>
+      <c r="F172" s="7">
+        <v>47</v>
+      </c>
+      <c r="G172" s="2">
+        <v>49</v>
+      </c>
+      <c r="H172" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>46246</v>
+      </c>
       <c r="C173" s="9">
         <f>_xlfn.XLOOKUP(Log!A173, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E173" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D173" s="9">
+        <v>0.42806712962962962</v>
+      </c>
+      <c r="E173" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H173" s="2" t="str">
+        <v>17.416666666666618</v>
+      </c>
+      <c r="F173" s="7">
+        <v>48</v>
+      </c>
+      <c r="G173" s="2">
+        <v>51</v>
+      </c>
+      <c r="H173" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>46246</v>
+      </c>
       <c r="C174" s="9">
         <f>_xlfn.XLOOKUP(Log!A174, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E174" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D174" s="9">
+        <v>0.4294675925925926</v>
+      </c>
+      <c r="E174" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H174" s="2" t="str">
+        <v>19.433333333333309</v>
+      </c>
+      <c r="F174" s="7">
+        <v>49</v>
+      </c>
+      <c r="G174" s="2">
+        <v>52</v>
+      </c>
+      <c r="H174" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>46246</v>
+      </c>
       <c r="C175" s="9">
         <f>_xlfn.XLOOKUP(Log!A175, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E175" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D175" s="9">
+        <v>0.43086805555555557</v>
+      </c>
+      <c r="E175" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H175" s="2" t="str">
+        <v>21.449999999999996</v>
+      </c>
+      <c r="F175" s="7">
+        <v>51</v>
+      </c>
+      <c r="G175" s="2">
+        <v>54</v>
+      </c>
+      <c r="H175" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>46246</v>
+      </c>
       <c r="C176" s="9">
         <f>_xlfn.XLOOKUP(Log!A176, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E176" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D176" s="9">
+        <v>0.43225694444444446</v>
+      </c>
+      <c r="E176" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H176" s="2" t="str">
+        <v>23.449999999999989</v>
+      </c>
+      <c r="F176" s="7">
+        <v>51</v>
+      </c>
+      <c r="G176" s="2">
+        <v>55</v>
+      </c>
+      <c r="H176" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>46246</v>
+      </c>
       <c r="C177" s="9">
         <f>_xlfn.XLOOKUP(Log!A177, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E177" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D177" s="9">
+        <v>0.43364583333333334</v>
+      </c>
+      <c r="E177" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H177" s="2" t="str">
+        <v>25.449999999999982</v>
+      </c>
+      <c r="F177" s="7">
+        <v>52</v>
+      </c>
+      <c r="G177" s="2">
+        <v>55</v>
+      </c>
+      <c r="H177" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>46246</v>
+      </c>
       <c r="C178" s="9">
         <f>_xlfn.XLOOKUP(Log!A178, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E178" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D178" s="9">
+        <v>0.43504629629629632</v>
+      </c>
+      <c r="E178" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H178" s="2" t="str">
+        <v>27.466666666666669</v>
+      </c>
+      <c r="F178" s="7">
+        <v>54</v>
+      </c>
+      <c r="G178" s="2">
+        <v>55</v>
+      </c>
+      <c r="H178" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>46246</v>
+      </c>
       <c r="C179" s="9">
         <f>_xlfn.XLOOKUP(Log!A179, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E179" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D179" s="9">
+        <v>0.4364351851851852</v>
+      </c>
+      <c r="E179" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H179" s="2" t="str">
+        <v>29.466666666666661</v>
+      </c>
+      <c r="F179" s="7">
+        <v>54</v>
+      </c>
+      <c r="G179" s="2">
+        <v>57</v>
+      </c>
+      <c r="H179" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>46246</v>
+      </c>
       <c r="C180" s="9">
         <f>_xlfn.XLOOKUP(Log!A180, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E180" s="6" t="str">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="D180" s="9">
+        <v>0.43783564814814813</v>
+      </c>
+      <c r="E180" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H180" s="2" t="str">
+        <v>31.48333333333327</v>
+      </c>
+      <c r="F180" s="7">
+        <v>55</v>
+      </c>
+      <c r="G180" s="2">
+        <v>58</v>
+      </c>
+      <c r="H180" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C181" s="9">
         <f>_xlfn.XLOOKUP(Log!A181, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8295,7 +8549,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C182" s="9">
         <f>_xlfn.XLOOKUP(Log!A182, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8309,7 +8563,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C183" s="9">
         <f>_xlfn.XLOOKUP(Log!A183, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8323,7 +8577,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C184" s="9">
         <f>_xlfn.XLOOKUP(Log!A184, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8337,7 +8591,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C185" s="9">
         <f>_xlfn.XLOOKUP(Log!A185, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8351,7 +8605,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C186" s="9">
         <f>_xlfn.XLOOKUP(Log!A186, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8365,7 +8619,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C187" s="9">
         <f>_xlfn.XLOOKUP(Log!A187, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8379,7 +8633,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C188" s="9">
         <f>_xlfn.XLOOKUP(Log!A188, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8393,7 +8647,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C189" s="9">
         <f>_xlfn.XLOOKUP(Log!A189, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8407,7 +8661,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C190" s="9">
         <f>_xlfn.XLOOKUP(Log!A190, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8421,7 +8675,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C191" s="9">
         <f>_xlfn.XLOOKUP(Log!A191, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -8435,7 +8689,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C192" s="9">
         <f>_xlfn.XLOOKUP(Log!A192, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -13354,9 +13608,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF1F4E78"/>
+    <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -13407,7 +13661,7 @@
     </row>
     <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:B9" si="0">A2+1</f>
+        <f t="shared" ref="A3:B8" si="0">A2+1</f>
         <v>46229</v>
       </c>
       <c r="B3" s="1">
@@ -13459,252 +13713,251 @@
         <v>26.000000000000068</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1"/>
+    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46232</v>
+      </c>
       <c r="C6" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.73472222222222228</v>
+      </c>
+      <c r="E6" s="25">
+        <f>IF(AND(D6&lt;&gt;"", C6&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v>15.999999999999943</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>46233</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>46233</v>
+      </c>
+      <c r="C7" s="2">
         <v>24.5</v>
       </c>
-      <c r="D6" s="8">
-        <v>0.4284722222222222</v>
-      </c>
-      <c r="E6" s="25" t="str">
-        <f>IF(AND(D6&lt;&gt;"", C6&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>–</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>46232</v>
-      </c>
-      <c r="B7" s="1">
-        <v>46232</v>
-      </c>
-      <c r="C7" s="2">
-        <v>25.5</v>
-      </c>
       <c r="D7" s="8">
-        <v>0.73472222222222228</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="E7" s="25">
         <f>IF(AND(D7&lt;&gt;"", C7&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>15.999999999999943</v>
+        <v>19.000000000000014</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C8" s="2">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D8" s="8">
-        <v>0.40972222222222221</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="E8" s="25">
         <f>IF(AND(D8&lt;&gt;"", C8&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>19.000000000000014</v>
+        <v>20.999999999999925</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="C9" s="2">
         <v>24</v>
       </c>
       <c r="D9" s="8">
-        <v>0.43055555555555558</v>
+        <v>0.70625000000000004</v>
       </c>
       <c r="E9" s="25">
         <f>IF(AND(D9&lt;&gt;"", C9&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>20.999999999999925</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>19</v>
+        <v>21.583333333333243</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B10" s="1">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C10" s="2">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D10" s="8">
-        <v>0.70625000000000004</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="E10" s="25">
         <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>21.583333333333243</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>21.216666666666654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B11" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C11" s="2">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="D11" s="8">
-        <v>0.40972222222222221</v>
+        <v>0.42986111111111114</v>
       </c>
       <c r="E11" s="25">
         <f>IF(AND(D11&lt;&gt;"", C11&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>21.216666666666654</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+        <v>21.066666666666627</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B12" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C12" s="2">
         <v>24.5</v>
       </c>
       <c r="D12" s="8">
-        <v>0.42986111111111114</v>
+        <v>0.48333333333333334</v>
       </c>
       <c r="E12" s="25">
         <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>21.066666666666627</v>
+        <v>19.600000000000026</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B13" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C13" s="2">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D13" s="8">
-        <v>0.48333333333333334</v>
+        <v>0.43888888888888888</v>
       </c>
       <c r="E13" s="25">
         <f>IF(AND(D13&lt;&gt;"", C13&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>19.600000000000026</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>51</v>
+        <v>20.133333333333336</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B14" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="C14" s="2">
         <v>24</v>
       </c>
       <c r="D14" s="8">
-        <v>0.43888888888888888</v>
+        <v>0.55833333333333335</v>
       </c>
       <c r="E14" s="25">
         <f>IF(AND(D14&lt;&gt;"", C14&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>20.133333333333336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>19.616666666666642</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B15" s="1">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C15" s="2">
         <v>24</v>
       </c>
       <c r="D15" s="8">
-        <v>0.55833333333333335</v>
+        <v>0.44374999999999998</v>
       </c>
       <c r="E15" s="25">
         <f>IF(AND(D15&lt;&gt;"", C15&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>19.616666666666642</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>18.850000000000069</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B16" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C16" s="2">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D16" s="8">
-        <v>0.44374999999999998</v>
+        <v>0.38194444444444442</v>
       </c>
       <c r="E16" s="25">
         <f>IF(AND(D16&lt;&gt;"", C16&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>18.850000000000069</v>
+        <v>21.350000000000058</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B17" s="1">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C17" s="2">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="D17" s="8">
-        <v>0.38194444444444442</v>
+        <v>0.41597222222222224</v>
       </c>
       <c r="E17" s="25">
         <f>IF(AND(D17&lt;&gt;"", C17&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>21.350000000000058</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>21.449999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="E18" s="25" t="str">
@@ -13712,7 +13965,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="E19" s="25" t="str">
@@ -13720,7 +13973,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="E20" s="25" t="str">
@@ -13728,7 +13981,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="E21" s="25" t="str">
@@ -13736,7 +13989,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="E22" s="25" t="str">
@@ -13744,7 +13997,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="E23" s="25" t="str">
@@ -13752,7 +14005,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="E24" s="25" t="str">
@@ -13760,7 +14013,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="E25" s="25" t="str">
@@ -13768,7 +14021,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="E26" s="25" t="str">
@@ -13776,7 +14029,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="E27" s="25" t="str">
@@ -13784,7 +14037,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="E28" s="25" t="str">
@@ -13792,7 +14045,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="E29" s="25" t="str">
@@ -13800,7 +14053,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="E30" s="25" t="str">
@@ -13808,7 +14061,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="E31" s="25" t="str">
@@ -13816,7 +14069,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="E32" s="25" t="str">
@@ -14025,8 +14278,6 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
       <c r="E58" s="25" t="str">
         <f>IF(AND(D58&lt;&gt;"", C58&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
         <v/>
@@ -14275,12 +14526,6 @@
     <row r="99" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E99" s="25" t="str">
         <f>IF(AND(D99&lt;&gt;"", C99&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B99,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B99,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E100" s="25" t="str">
-        <f>IF(AND(D100&lt;&gt;"", C100&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B100,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B100,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -14290,6 +14535,860 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C09E44-4CB4-4168-A368-06EB595F15D0}">
+  <sheetPr>
+    <tabColor rgb="FFFF9B9B"/>
+  </sheetPr>
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" style="25" customWidth="1"/>
+    <col min="6" max="6" width="60.77734375" style="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46232</v>
+      </c>
+      <c r="C2" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.4284722222222222</v>
+      </c>
+      <c r="E2" s="25">
+        <f>IF(AND(D2&lt;&gt;"", C2&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B2,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B2,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v>15.999999999999943</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="E3" s="25" t="str">
+        <f>IF(AND(D3&lt;&gt;"", C3&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B3,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B3,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="E4" s="25" t="str">
+        <f>IF(AND(D4&lt;&gt;"", C4&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B4,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B4,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="E5" s="25" t="str">
+        <f>IF(AND(D5&lt;&gt;"", C5&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B5,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B5,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="E6" s="25" t="str">
+        <f>IF(AND(D6&lt;&gt;"", C6&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="E7" s="25" t="str">
+        <f>IF(AND(D7&lt;&gt;"", C7&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="E8" s="25" t="str">
+        <f>IF(AND(D8&lt;&gt;"", C8&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="E9" s="25" t="str">
+        <f>IF(AND(D9&lt;&gt;"", C9&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="E10" s="25" t="str">
+        <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="E11" s="25" t="str">
+        <f>IF(AND(D11&lt;&gt;"", C11&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="E12" s="25" t="str">
+        <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="E13" s="25" t="str">
+        <f>IF(AND(D13&lt;&gt;"", C13&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="E14" s="25" t="str">
+        <f>IF(AND(D14&lt;&gt;"", C14&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="E15" s="25" t="str">
+        <f>IF(AND(D15&lt;&gt;"", C15&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="E16" s="25" t="str">
+        <f>IF(AND(D16&lt;&gt;"", C16&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="25" t="str">
+        <f>IF(AND(D17&lt;&gt;"", C17&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="25" t="str">
+        <f>IF(AND(D18&lt;&gt;"", C18&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="25" t="str">
+        <f>IF(AND(D19&lt;&gt;"", C19&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="25" t="str">
+        <f>IF(AND(D20&lt;&gt;"", C20&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="25" t="str">
+        <f>IF(AND(D21&lt;&gt;"", C21&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="25" t="str">
+        <f>IF(AND(D22&lt;&gt;"", C22&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="25" t="str">
+        <f>IF(AND(D23&lt;&gt;"", C23&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B23,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B23,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="25" t="str">
+        <f>IF(AND(D24&lt;&gt;"", C24&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B24,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B24,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="25" t="str">
+        <f>IF(AND(D25&lt;&gt;"", C25&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B25,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B25,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="25" t="str">
+        <f>IF(AND(D26&lt;&gt;"", C26&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B26,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B26,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="25" t="str">
+        <f>IF(AND(D27&lt;&gt;"", C27&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B27,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B27,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="25" t="str">
+        <f>IF(AND(D28&lt;&gt;"", C28&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B28,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B28,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="25" t="str">
+        <f>IF(AND(D29&lt;&gt;"", C29&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B29,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B29,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="25" t="str">
+        <f>IF(AND(D30&lt;&gt;"", C30&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B30,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B30,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="25" t="str">
+        <f>IF(AND(D31&lt;&gt;"", C31&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B31,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B31,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="25" t="str">
+        <f>IF(AND(D32&lt;&gt;"", C32&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B32,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B32,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="25" t="str">
+        <f>IF(AND(D33&lt;&gt;"", C33&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B33,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B33,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="25" t="str">
+        <f>IF(AND(D34&lt;&gt;"", C34&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B34,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B34,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="25" t="str">
+        <f>IF(AND(D35&lt;&gt;"", C35&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B35,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B35,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="25" t="str">
+        <f>IF(AND(D36&lt;&gt;"", C36&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B36,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B36,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="25" t="str">
+        <f>IF(AND(D37&lt;&gt;"", C37&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B37,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B37,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="25" t="str">
+        <f>IF(AND(D38&lt;&gt;"", C38&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B38,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B38,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="25" t="str">
+        <f>IF(AND(D39&lt;&gt;"", C39&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B39,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B39,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="25" t="str">
+        <f>IF(AND(D40&lt;&gt;"", C40&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B40,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B40,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="25" t="str">
+        <f>IF(AND(D41&lt;&gt;"", C41&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B41,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B41,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="25" t="str">
+        <f>IF(AND(D42&lt;&gt;"", C42&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B42,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B42,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="25" t="str">
+        <f>IF(AND(D43&lt;&gt;"", C43&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B43,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B43,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="25" t="str">
+        <f>IF(AND(D44&lt;&gt;"", C44&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B44,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B44,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="25" t="str">
+        <f>IF(AND(D45&lt;&gt;"", C45&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B45,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B45,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="25" t="str">
+        <f>IF(AND(D46&lt;&gt;"", C46&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B46,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B46,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="25" t="str">
+        <f>IF(AND(D47&lt;&gt;"", C47&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B47,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B47,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="25" t="str">
+        <f>IF(AND(D48&lt;&gt;"", C48&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B48,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B48,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="25" t="str">
+        <f>IF(AND(D49&lt;&gt;"", C49&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B49,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B49,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="25" t="str">
+        <f>IF(AND(D50&lt;&gt;"", C50&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B50,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B50,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="25" t="str">
+        <f>IF(AND(D51&lt;&gt;"", C51&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B51,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B51,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="25" t="str">
+        <f>IF(AND(D52&lt;&gt;"", C52&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B52,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B52,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="25" t="str">
+        <f>IF(AND(D53&lt;&gt;"", C53&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B53,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B53,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="25" t="str">
+        <f>IF(AND(D54&lt;&gt;"", C54&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B54,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B54,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="25" t="str">
+        <f>IF(AND(D55&lt;&gt;"", C55&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B55,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B55,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="25" t="str">
+        <f>IF(AND(D56&lt;&gt;"", C56&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B56,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B56,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="25" t="str">
+        <f>IF(AND(D57&lt;&gt;"", C57&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B57,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B57,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="25" t="str">
+        <f>IF(AND(D58&lt;&gt;"", C58&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="25" t="str">
+        <f>IF(AND(D59&lt;&gt;"", C59&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B59,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B59,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="25" t="str">
+        <f>IF(AND(D60&lt;&gt;"", C60&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B60,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B60,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="25" t="str">
+        <f>IF(AND(D61&lt;&gt;"", C61&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B61,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B61,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="25" t="str">
+        <f>IF(AND(D62&lt;&gt;"", C62&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B62,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B62,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="25" t="str">
+        <f>IF(AND(D63&lt;&gt;"", C63&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B63,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B63,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="25" t="str">
+        <f>IF(AND(D64&lt;&gt;"", C64&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B64,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B64,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="25" t="str">
+        <f>IF(AND(D65&lt;&gt;"", C65&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B65,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B65,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="25" t="str">
+        <f>IF(AND(D66&lt;&gt;"", C66&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B66,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B66,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="25" t="str">
+        <f>IF(AND(D67&lt;&gt;"", C67&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B67,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B67,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="25" t="str">
+        <f>IF(AND(D68&lt;&gt;"", C68&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B68,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B68,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="25" t="str">
+        <f>IF(AND(D69&lt;&gt;"", C69&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B69,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B69,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="25" t="str">
+        <f>IF(AND(D70&lt;&gt;"", C70&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B70,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B70,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="25" t="str">
+        <f>IF(AND(D71&lt;&gt;"", C71&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B71,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B71,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="25" t="str">
+        <f>IF(AND(D72&lt;&gt;"", C72&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B72,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B72,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="25" t="str">
+        <f>IF(AND(D73&lt;&gt;"", C73&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B73,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B73,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="25" t="str">
+        <f>IF(AND(D74&lt;&gt;"", C74&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B74,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B74,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="25" t="str">
+        <f>IF(AND(D75&lt;&gt;"", C75&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B75,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B75,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="25" t="str">
+        <f>IF(AND(D76&lt;&gt;"", C76&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B76,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B76,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="25" t="str">
+        <f>IF(AND(D77&lt;&gt;"", C77&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B77,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B77,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="25" t="str">
+        <f>IF(AND(D78&lt;&gt;"", C78&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B78,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B78,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="25" t="str">
+        <f>IF(AND(D79&lt;&gt;"", C79&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B79,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B79,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="25" t="str">
+        <f>IF(AND(D80&lt;&gt;"", C80&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B80,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B80,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="25" t="str">
+        <f>IF(AND(D81&lt;&gt;"", C81&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B81,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B81,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="25" t="str">
+        <f>IF(AND(D82&lt;&gt;"", C82&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B82,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B82,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="25" t="str">
+        <f>IF(AND(D83&lt;&gt;"", C83&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B83,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B83,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="25" t="str">
+        <f>IF(AND(D84&lt;&gt;"", C84&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B84,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B84,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE98C04E-7786-4047-B158-79D276F5E1CA}">
   <sheetPr>
     <tabColor rgb="FFC65911"/>
@@ -14341,7 +15440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D01A83-1FDF-45BF-A1E3-B5167A4A0F21}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D591FFC-B0FD-4201-9022-4E91CDB604A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A52131-F5EB-42E6-B51B-46E173FE4A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -1105,7 +1105,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1131,10 +1138,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC65911"/>
       <color rgb="FFFF9B9B"/>
       <color rgb="FFBDD7EE"/>
       <color rgb="FF1F4E78"/>
-      <color rgb="FFC65911"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1244,7 +1251,9 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1255,11 +1264,13 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:srgbClr val="C65911"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1316,6 +1327,12 @@
                 <c:pt idx="14">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46248</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1370,6 +1387,12 @@
                 <c:pt idx="14">
                   <c:v>24</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>25</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1412,7 +1435,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1423,11 +1446,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="0070C0"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1484,6 +1507,12 @@
                 <c:pt idx="14">
                   <c:v>46246</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46248</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1539,10 +1568,10 @@
                   <c:v>21.449999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>19.000000000000014</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>17.899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -1989,6 +2018,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1965623184"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -3917,7 +3947,7 @@
         <v>35</v>
       </c>
       <c r="H3" s="2">
-        <f t="shared" ref="H3:H8" si="1">G3-F3</f>
+        <f>IF(AND($G3&lt;&gt;"",$F3&lt;&gt;""), $G3-$F3, "")</f>
         <v>3</v>
       </c>
     </row>
@@ -3943,7 +3973,7 @@
         <v>44</v>
       </c>
       <c r="H4" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H4:H67" si="1">IF(AND($G4&lt;&gt;"",$F4&lt;&gt;""), $G4-$F4, "")</f>
         <v>3</v>
       </c>
     </row>
@@ -4073,7 +4103,7 @@
         <v>33</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" ref="H9:H31" si="2">IF(AND(G9&lt;&gt;"",F9&lt;&gt;""),G9-F9,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4099,7 +4129,7 @@
         <v>44</v>
       </c>
       <c r="H10" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4125,7 +4155,7 @@
         <v>49</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4151,7 +4181,7 @@
         <v>54</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4177,7 +4207,7 @@
         <v>60</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4203,7 +4233,7 @@
         <v>32</v>
       </c>
       <c r="H14" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4229,7 +4259,7 @@
         <v>49</v>
       </c>
       <c r="H15" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4255,7 +4285,7 @@
         <v>54</v>
       </c>
       <c r="H16" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4281,7 +4311,7 @@
         <v>58</v>
       </c>
       <c r="H17" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4307,7 +4337,7 @@
         <v>61</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -4336,7 +4366,7 @@
         <v>32</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -4365,7 +4395,7 @@
         <v>42</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4394,7 +4424,7 @@
         <v>47</v>
       </c>
       <c r="H21" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4420,7 +4450,7 @@
         <v>52</v>
       </c>
       <c r="H22" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4446,7 +4476,7 @@
         <v>55</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4472,7 +4502,7 @@
         <v>55</v>
       </c>
       <c r="H24" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4498,7 +4528,7 @@
         <v>58</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4524,7 +4554,7 @@
         <v>33</v>
       </c>
       <c r="H26" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4550,7 +4580,7 @@
         <v>42</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4576,7 +4606,7 @@
         <v>48</v>
       </c>
       <c r="H28" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4602,7 +4632,7 @@
         <v>52</v>
       </c>
       <c r="H29" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4628,7 +4658,7 @@
         <v>55</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4654,7 +4684,7 @@
         <v>33</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4680,7 +4710,7 @@
         <v>41</v>
       </c>
       <c r="H32" s="2">
-        <f>IF(AND(G32&lt;&gt;"",F32&lt;&gt;""),G32-F32,"")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4706,7 +4736,7 @@
         <v>45</v>
       </c>
       <c r="H33" s="2">
-        <f t="shared" ref="H33:H96" si="3">IF(AND(G33&lt;&gt;"",F33&lt;&gt;""),G33-F33,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4732,7 +4762,7 @@
         <v>49</v>
       </c>
       <c r="H34" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4758,7 +4788,7 @@
         <v>52</v>
       </c>
       <c r="H35" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4784,7 +4814,7 @@
         <v>52</v>
       </c>
       <c r="H36" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4810,7 +4840,7 @@
         <v>55</v>
       </c>
       <c r="H37" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4836,7 +4866,7 @@
         <v>55</v>
       </c>
       <c r="H38" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4862,7 +4892,7 @@
         <v>32</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4888,7 +4918,7 @@
         <v>41</v>
       </c>
       <c r="H40" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4914,7 +4944,7 @@
         <v>47</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -4940,7 +4970,7 @@
         <v>49</v>
       </c>
       <c r="H42" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -4966,7 +4996,7 @@
         <v>52</v>
       </c>
       <c r="H43" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4992,7 +5022,7 @@
         <v>55</v>
       </c>
       <c r="H44" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -5018,7 +5048,7 @@
         <v>30</v>
       </c>
       <c r="H45" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J45" s="17" t="s">
@@ -5047,7 +5077,7 @@
         <v>35</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5073,7 +5103,7 @@
         <v>39</v>
       </c>
       <c r="H47" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5099,7 +5129,7 @@
         <v>42</v>
       </c>
       <c r="H48" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5125,7 +5155,7 @@
         <v>45</v>
       </c>
       <c r="H49" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5151,7 +5181,7 @@
         <v>45</v>
       </c>
       <c r="H50" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -5177,7 +5207,7 @@
         <v>48</v>
       </c>
       <c r="H51" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5203,7 +5233,7 @@
         <v>49</v>
       </c>
       <c r="H52" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -5229,7 +5259,7 @@
         <v>51</v>
       </c>
       <c r="H53" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5255,7 +5285,7 @@
         <v>52</v>
       </c>
       <c r="H54" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5281,7 +5311,7 @@
         <v>52</v>
       </c>
       <c r="H55" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -5307,7 +5337,7 @@
         <v>54</v>
       </c>
       <c r="H56" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5333,7 +5363,7 @@
         <v>55</v>
       </c>
       <c r="H57" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5359,7 +5389,7 @@
         <v>35</v>
       </c>
       <c r="H58" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5385,7 +5415,7 @@
         <v>38</v>
       </c>
       <c r="H59" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -5411,7 +5441,7 @@
         <v>41</v>
       </c>
       <c r="H60" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -5437,7 +5467,7 @@
         <v>44</v>
       </c>
       <c r="H61" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5463,7 +5493,7 @@
         <v>44</v>
       </c>
       <c r="H62" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -5489,7 +5519,7 @@
         <v>47</v>
       </c>
       <c r="H63" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -5515,7 +5545,7 @@
         <v>49</v>
       </c>
       <c r="H64" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -5541,7 +5571,7 @@
         <v>49</v>
       </c>
       <c r="H65" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -5567,7 +5597,7 @@
         <v>52</v>
       </c>
       <c r="H66" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -5583,7 +5613,7 @@
         <v>0.4244560185185185</v>
       </c>
       <c r="E67" s="6">
-        <f t="shared" ref="E67:E130" si="4">IF(AND($D67&lt;&gt;"", $C67&lt;&gt;""), ($D67-$C67)*1440, "")</f>
+        <f t="shared" ref="E67:E130" si="2">IF(AND($D67&lt;&gt;"", $C67&lt;&gt;""), ($D67-$C67)*1440, "")</f>
         <v>21.216666666666654</v>
       </c>
       <c r="F67" s="7">
@@ -5593,7 +5623,7 @@
         <v>52</v>
       </c>
       <c r="H67" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -5609,7 +5639,7 @@
         <v>0.42584490740740738</v>
       </c>
       <c r="E68" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.216666666666647</v>
       </c>
       <c r="F68" s="7">
@@ -5619,7 +5649,7 @@
         <v>55</v>
       </c>
       <c r="H68" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H68:H131" si="3">IF(AND($G68&lt;&gt;"",$F68&lt;&gt;""), $G68-$F68, "")</f>
         <v>3</v>
       </c>
     </row>
@@ -5635,7 +5665,7 @@
         <v>0.42724537037037036</v>
       </c>
       <c r="E69" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>25.233333333333334</v>
       </c>
       <c r="F69" s="7">
@@ -5661,7 +5691,7 @@
         <v>0.42863425925925924</v>
       </c>
       <c r="E70" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>27.233333333333327</v>
       </c>
       <c r="F70" s="7">
@@ -5687,7 +5717,7 @@
         <v>0.43125000000000002</v>
       </c>
       <c r="E71" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F71" s="7">
@@ -5713,7 +5743,7 @@
         <v>0.43263888888888891</v>
       </c>
       <c r="E72" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3.9999999999999858</v>
       </c>
       <c r="F72" s="7">
@@ -5739,7 +5769,7 @@
         <v>0.43611111111111112</v>
       </c>
       <c r="E73" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8.999999999999968</v>
       </c>
       <c r="F73" s="7">
@@ -5765,7 +5795,7 @@
         <v>0.44166666666666665</v>
       </c>
       <c r="E74" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>16.99999999999994</v>
       </c>
       <c r="F74" s="7">
@@ -5791,7 +5821,7 @@
         <v>0.43334490740740739</v>
       </c>
       <c r="E75" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5.0166666666665982</v>
       </c>
       <c r="F75" s="7">
@@ -5817,7 +5847,7 @@
         <v>0.43752314814814813</v>
       </c>
       <c r="E76" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>11.033333333333273</v>
       </c>
       <c r="F76" s="7">
@@ -5843,7 +5873,7 @@
         <v>0.43892361111111111</v>
       </c>
       <c r="E77" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>13.049999999999962</v>
       </c>
       <c r="F77" s="7">
@@ -5869,7 +5899,7 @@
         <v>0.4403125</v>
       </c>
       <c r="E78" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>15.049999999999955</v>
       </c>
       <c r="F78" s="7">
@@ -5895,7 +5925,7 @@
         <v>0.44310185185185186</v>
       </c>
       <c r="E79" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>19.066666666666634</v>
       </c>
       <c r="F79" s="7">
@@ -5921,7 +5951,7 @@
         <v>0.44449074074074074</v>
       </c>
       <c r="E80" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>21.066666666666627</v>
       </c>
       <c r="F80" s="7">
@@ -5947,7 +5977,7 @@
         <v>0.44589120370370372</v>
       </c>
       <c r="E81" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.083333333333318</v>
       </c>
       <c r="F81" s="7">
@@ -5973,7 +6003,7 @@
         <v>0.4472800925925926</v>
       </c>
       <c r="E82" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>25.083333333333311</v>
       </c>
       <c r="F82" s="7">
@@ -5999,7 +6029,7 @@
         <v>0.44866898148148149</v>
       </c>
       <c r="E83" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>27.083333333333304</v>
       </c>
       <c r="F83" s="7">
@@ -6025,7 +6055,7 @@
         <v>0.45005787037037037</v>
       </c>
       <c r="E84" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>29.083333333333297</v>
       </c>
       <c r="F84" s="7">
@@ -6051,7 +6081,7 @@
         <v>0.45145833333333335</v>
       </c>
       <c r="E85" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>31.099999999999987</v>
       </c>
       <c r="F85" s="7">
@@ -6077,7 +6107,7 @@
         <v>0.48472222222222222</v>
       </c>
       <c r="E86" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F86" s="7">
@@ -6103,7 +6133,7 @@
         <v>0.48716435185185186</v>
       </c>
       <c r="E87" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5.5166666666666764</v>
       </c>
       <c r="F87" s="7">
@@ -6129,7 +6159,7 @@
         <v>0.48856481481481484</v>
       </c>
       <c r="E88" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7.5333333333333652</v>
       </c>
       <c r="F88" s="7">
@@ -6155,7 +6185,7 @@
         <v>0.48995370370370372</v>
       </c>
       <c r="E89" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>9.5333333333333581</v>
       </c>
       <c r="F89" s="7">
@@ -6181,7 +6211,7 @@
         <v>0.49135416666666665</v>
       </c>
       <c r="E90" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>11.549999999999967</v>
       </c>
       <c r="F90" s="7">
@@ -6207,7 +6237,7 @@
         <v>0.49275462962962963</v>
       </c>
       <c r="E91" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>13.566666666666656</v>
       </c>
       <c r="F91" s="7">
@@ -6233,7 +6263,7 @@
         <v>0.4941550925925926</v>
       </c>
       <c r="E92" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>15.583333333333345</v>
       </c>
       <c r="F92" s="7">
@@ -6259,7 +6289,7 @@
         <v>0.49554398148148149</v>
       </c>
       <c r="E93" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>17.583333333333336</v>
       </c>
       <c r="F93" s="7">
@@ -6285,7 +6315,7 @@
         <v>0.49694444444444447</v>
       </c>
       <c r="E94" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>19.600000000000026</v>
       </c>
       <c r="F94" s="7">
@@ -6311,7 +6341,7 @@
         <v>0.49833333333333335</v>
       </c>
       <c r="E95" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>21.600000000000019</v>
       </c>
       <c r="F95" s="7">
@@ -6337,7 +6367,7 @@
         <v>0.49972222222222223</v>
       </c>
       <c r="E96" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.600000000000012</v>
       </c>
       <c r="F96" s="7">
@@ -6363,7 +6393,7 @@
         <v>0.50111111111111106</v>
       </c>
       <c r="E97" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>25.599999999999923</v>
       </c>
       <c r="F97" s="7">
@@ -6373,7 +6403,7 @@
         <v>55</v>
       </c>
       <c r="H97" s="2">
-        <f t="shared" ref="H97:H160" si="5">IF(AND(G97&lt;&gt;"",F97&lt;&gt;""),G97-F97,"")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -6389,7 +6419,7 @@
         <v>0.5025115740740741</v>
       </c>
       <c r="E98" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>27.616666666666696</v>
       </c>
       <c r="F98" s="7">
@@ -6399,7 +6429,7 @@
         <v>57</v>
       </c>
       <c r="H98" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6415,7 +6445,7 @@
         <v>0.50391203703703702</v>
       </c>
       <c r="E99" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>29.633333333333304</v>
       </c>
       <c r="F99" s="7">
@@ -6425,7 +6455,7 @@
         <v>57</v>
       </c>
       <c r="H99" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -6441,7 +6471,7 @@
         <v>0.5053009259259259</v>
       </c>
       <c r="E100" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>31.633333333333297</v>
       </c>
       <c r="F100" s="7">
@@ -6451,7 +6481,7 @@
         <v>58</v>
       </c>
       <c r="H100" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6467,7 +6497,7 @@
         <v>0.44027777777777777</v>
       </c>
       <c r="E101" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F101" s="7">
@@ -6477,7 +6507,7 @@
         <v>33</v>
       </c>
       <c r="H101" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -6493,7 +6523,7 @@
         <v>0.44170138888888888</v>
       </c>
       <c r="E102" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>4.0499999999999936</v>
       </c>
       <c r="F102" s="7">
@@ -6503,7 +6533,7 @@
         <v>36</v>
       </c>
       <c r="H102" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -6519,7 +6549,7 @@
         <v>0.44310185185185186</v>
       </c>
       <c r="E103" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>6.0666666666666824</v>
       </c>
       <c r="F103" s="7">
@@ -6529,7 +6559,7 @@
         <v>41</v>
       </c>
       <c r="H103" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6545,7 +6575,7 @@
         <v>0.44450231481481484</v>
       </c>
       <c r="E104" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8.0833333333333712</v>
       </c>
       <c r="F104" s="7">
@@ -6555,7 +6585,7 @@
         <v>44</v>
       </c>
       <c r="H104" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6571,7 +6601,7 @@
         <v>0.44590277777777776</v>
       </c>
       <c r="E105" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10.09999999999998</v>
       </c>
       <c r="F105" s="7">
@@ -6581,7 +6611,7 @@
         <v>45</v>
       </c>
       <c r="H105" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -6597,7 +6627,7 @@
         <v>0.44729166666666664</v>
       </c>
       <c r="E106" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>12.099999999999973</v>
       </c>
       <c r="F106" s="7">
@@ -6607,7 +6637,7 @@
         <v>47</v>
       </c>
       <c r="H106" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6623,7 +6653,7 @@
         <v>0.44868055555555558</v>
       </c>
       <c r="E107" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>14.100000000000046</v>
       </c>
       <c r="F107" s="7">
@@ -6633,7 +6663,7 @@
         <v>49</v>
       </c>
       <c r="H107" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -6649,7 +6679,7 @@
         <v>0.45008101851851851</v>
       </c>
       <c r="E108" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>16.116666666666653</v>
       </c>
       <c r="F108" s="7">
@@ -6659,7 +6689,7 @@
         <v>51</v>
       </c>
       <c r="H108" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6675,7 +6705,7 @@
         <v>0.45148148148148148</v>
       </c>
       <c r="E109" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>18.133333333333344</v>
       </c>
       <c r="F109" s="7">
@@ -6685,7 +6715,7 @@
         <v>52</v>
       </c>
       <c r="H109" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6701,7 +6731,7 @@
         <v>0.45287037037037037</v>
       </c>
       <c r="E110" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>20.133333333333336</v>
       </c>
       <c r="F110" s="7">
@@ -6711,7 +6741,7 @@
         <v>52</v>
       </c>
       <c r="H110" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -6727,7 +6757,7 @@
         <v>0.45425925925925925</v>
       </c>
       <c r="E111" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>22.133333333333329</v>
       </c>
       <c r="F111" s="7">
@@ -6737,7 +6767,7 @@
         <v>54</v>
       </c>
       <c r="H111" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6753,7 +6783,7 @@
         <v>0.45565972222222223</v>
       </c>
       <c r="E112" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>24.15000000000002</v>
       </c>
       <c r="F112" s="7">
@@ -6763,7 +6793,7 @@
         <v>55</v>
       </c>
       <c r="H112" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6779,7 +6809,7 @@
         <v>0.45704861111111111</v>
       </c>
       <c r="E113" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>26.150000000000013</v>
       </c>
       <c r="F113" s="7">
@@ -6789,7 +6819,7 @@
         <v>55</v>
       </c>
       <c r="H113" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -6805,7 +6835,7 @@
         <v>0.4584375</v>
       </c>
       <c r="E114" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>28.150000000000006</v>
       </c>
       <c r="F114" s="7">
@@ -6815,7 +6845,7 @@
         <v>57</v>
       </c>
       <c r="H114" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6831,7 +6861,7 @@
         <v>0.45983796296296298</v>
       </c>
       <c r="E115" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>30.166666666666693</v>
       </c>
       <c r="F115" s="7">
@@ -6841,7 +6871,7 @@
         <v>58</v>
       </c>
       <c r="H115" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6857,7 +6887,7 @@
         <v>0.46122685185185186</v>
       </c>
       <c r="E116" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>32.166666666666686</v>
       </c>
       <c r="F116" s="7">
@@ -6867,7 +6897,7 @@
         <v>58</v>
       </c>
       <c r="H116" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6883,7 +6913,7 @@
         <v>0.55972222222222223</v>
       </c>
       <c r="E117" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F117" s="7">
@@ -6893,7 +6923,7 @@
         <v>33</v>
       </c>
       <c r="H117" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -6909,7 +6939,7 @@
         <v>0.56081018518518522</v>
       </c>
       <c r="E118" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3.5666666666666913</v>
       </c>
       <c r="F118" s="7">
@@ -6919,7 +6949,7 @@
         <v>35</v>
       </c>
       <c r="H118" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -6935,7 +6965,7 @@
         <v>0.5621990740740741</v>
       </c>
       <c r="E119" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5.5666666666666842</v>
       </c>
       <c r="F119" s="7">
@@ -6945,7 +6975,7 @@
         <v>39</v>
       </c>
       <c r="H119" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -6961,7 +6991,7 @@
         <v>0.56359953703703702</v>
       </c>
       <c r="E120" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7.5833333333332931</v>
       </c>
       <c r="F120" s="7">
@@ -6971,7 +7001,7 @@
         <v>42</v>
       </c>
       <c r="H120" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -6987,7 +7017,7 @@
         <v>0.56498842592592591</v>
       </c>
       <c r="E121" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>9.583333333333286</v>
       </c>
       <c r="F121" s="7">
@@ -6997,7 +7027,7 @@
         <v>45</v>
       </c>
       <c r="H121" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -7013,7 +7043,7 @@
         <v>0.56637731481481479</v>
       </c>
       <c r="E122" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>11.583333333333279</v>
       </c>
       <c r="F122" s="7">
@@ -7023,7 +7053,7 @@
         <v>47</v>
       </c>
       <c r="H122" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -7039,7 +7069,7 @@
         <v>0.56777777777777783</v>
       </c>
       <c r="E123" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>13.600000000000048</v>
       </c>
       <c r="F123" s="7">
@@ -7049,7 +7079,7 @@
         <v>49</v>
       </c>
       <c r="H123" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -7065,7 +7095,7 @@
         <v>0.56916666666666671</v>
       </c>
       <c r="E124" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>15.600000000000041</v>
       </c>
       <c r="F124" s="7">
@@ -7075,7 +7105,7 @@
         <v>49</v>
       </c>
       <c r="H124" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -7091,7 +7121,7 @@
         <v>0.57056712962962963</v>
       </c>
       <c r="E125" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>17.616666666666649</v>
       </c>
       <c r="F125" s="7">
@@ -7101,7 +7131,7 @@
         <v>52</v>
       </c>
       <c r="H125" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -7117,7 +7147,7 @@
         <v>0.57195601851851852</v>
       </c>
       <c r="E126" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>19.616666666666642</v>
       </c>
       <c r="F126" s="7">
@@ -7127,7 +7157,7 @@
         <v>52</v>
       </c>
       <c r="H126" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -7143,7 +7173,7 @@
         <v>0.5733449074074074</v>
       </c>
       <c r="E127" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>21.616666666666635</v>
       </c>
       <c r="F127" s="7">
@@ -7153,7 +7183,7 @@
         <v>54</v>
       </c>
       <c r="H127" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -7169,7 +7199,7 @@
         <v>0.57473379629629628</v>
       </c>
       <c r="E128" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.616666666666628</v>
       </c>
       <c r="F128" s="7">
@@ -7179,7 +7209,7 @@
         <v>55</v>
       </c>
       <c r="H128" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -7195,7 +7225,7 @@
         <v>0.57613425925925921</v>
       </c>
       <c r="E129" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>25.633333333333237</v>
       </c>
       <c r="F129" s="7">
@@ -7205,7 +7235,7 @@
         <v>55</v>
       </c>
       <c r="H129" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -7221,7 +7251,7 @@
         <v>0.5775231481481482</v>
       </c>
       <c r="E130" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>27.63333333333339</v>
       </c>
       <c r="F130" s="7">
@@ -7231,7 +7261,7 @@
         <v>57</v>
       </c>
       <c r="H130" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -7247,7 +7277,7 @@
         <v>0.57892361111111112</v>
       </c>
       <c r="E131" s="6">
-        <f t="shared" ref="E131:E194" si="6">IF(AND($D131&lt;&gt;"", $C131&lt;&gt;""), ($D131-$C131)*1440, "")</f>
+        <f t="shared" ref="E131:E194" si="4">IF(AND($D131&lt;&gt;"", $C131&lt;&gt;""), ($D131-$C131)*1440, "")</f>
         <v>29.65</v>
       </c>
       <c r="F131" s="7">
@@ -7257,7 +7287,7 @@
         <v>58</v>
       </c>
       <c r="H131" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -7273,7 +7303,7 @@
         <v>0.58031250000000001</v>
       </c>
       <c r="E132" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>31.649999999999991</v>
       </c>
       <c r="F132" s="7">
@@ -7283,7 +7313,7 @@
         <v>58</v>
       </c>
       <c r="H132" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="H132:H195" si="5">IF(AND($G132&lt;&gt;"",$F132&lt;&gt;""), $G132-$F132, "")</f>
         <v>3</v>
       </c>
     </row>
@@ -7299,7 +7329,7 @@
         <v>0.44513888888888886</v>
       </c>
       <c r="E133" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F133" s="7">
@@ -7325,7 +7355,7 @@
         <v>0.44570601851851854</v>
       </c>
       <c r="E134" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2.8166666666667339</v>
       </c>
       <c r="F134" s="7">
@@ -7351,7 +7381,7 @@
         <v>0.44709490740740743</v>
       </c>
       <c r="E135" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.8166666666667268</v>
       </c>
       <c r="F135" s="7">
@@ -7377,7 +7407,7 @@
         <v>0.44848379629629631</v>
       </c>
       <c r="E136" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>6.8166666666667197</v>
       </c>
       <c r="F136" s="7">
@@ -7403,7 +7433,7 @@
         <v>0.44988425925925923</v>
       </c>
       <c r="E137" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>8.8333333333333286</v>
       </c>
       <c r="F137" s="7">
@@ -7429,7 +7459,7 @@
         <v>0.45127314814814817</v>
       </c>
       <c r="E138" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10.833333333333401</v>
       </c>
       <c r="F138" s="7">
@@ -7455,7 +7485,7 @@
         <v>0.45266203703703706</v>
       </c>
       <c r="E139" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>12.833333333333394</v>
       </c>
       <c r="F139" s="7">
@@ -7481,7 +7511,7 @@
         <v>0.45406249999999998</v>
       </c>
       <c r="E140" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>14.850000000000003</v>
       </c>
       <c r="F140" s="7">
@@ -7507,7 +7537,7 @@
         <v>0.45545138888888886</v>
       </c>
       <c r="E141" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>16.849999999999994</v>
       </c>
       <c r="F141" s="7">
@@ -7533,7 +7563,7 @@
         <v>0.4568402777777778</v>
       </c>
       <c r="E142" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>18.850000000000069</v>
       </c>
       <c r="F142" s="7">
@@ -7559,7 +7589,7 @@
         <v>0.45824074074074073</v>
       </c>
       <c r="E143" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>20.866666666666678</v>
       </c>
       <c r="F143" s="7">
@@ -7585,7 +7615,7 @@
         <v>0.45962962962962961</v>
       </c>
       <c r="E144" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>22.866666666666671</v>
       </c>
       <c r="F144" s="7">
@@ -7611,7 +7641,7 @@
         <v>0.46103009259259259</v>
       </c>
       <c r="E145" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>24.883333333333361</v>
       </c>
       <c r="F145" s="7">
@@ -7637,7 +7667,7 @@
         <v>0.46241898148148147</v>
       </c>
       <c r="E146" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>26.883333333333354</v>
       </c>
       <c r="F146" s="7">
@@ -7663,7 +7693,7 @@
         <v>0.46380787037037036</v>
       </c>
       <c r="E147" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>28.883333333333347</v>
       </c>
       <c r="F147" s="7">
@@ -7689,7 +7719,7 @@
         <v>0.46520833333333333</v>
       </c>
       <c r="E148" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>30.900000000000034</v>
       </c>
       <c r="F148" s="7">
@@ -7715,7 +7745,7 @@
         <v>0.38472222222222224</v>
       </c>
       <c r="E149" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.0000000000000657</v>
       </c>
       <c r="F149" s="7">
@@ -7741,7 +7771,7 @@
         <v>0.385625</v>
       </c>
       <c r="E150" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5.3000000000000291</v>
       </c>
       <c r="F150" s="7">
@@ -7767,7 +7797,7 @@
         <v>0.38702546296296297</v>
       </c>
       <c r="E151" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>7.3166666666667179</v>
       </c>
       <c r="F151" s="7">
@@ -7793,7 +7823,7 @@
         <v>0.38841435185185186</v>
       </c>
       <c r="E152" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>9.3166666666667108</v>
       </c>
       <c r="F152" s="7">
@@ -7819,7 +7849,7 @@
         <v>0.38980324074074074</v>
       </c>
       <c r="E153" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11.316666666666704</v>
       </c>
       <c r="F153" s="7">
@@ -7845,7 +7875,7 @@
         <v>0.39119212962962963</v>
       </c>
       <c r="E154" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>13.316666666666697</v>
       </c>
       <c r="F154" s="7">
@@ -7871,7 +7901,7 @@
         <v>0.3925925925925926</v>
       </c>
       <c r="E155" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>15.333333333333385</v>
       </c>
       <c r="F155" s="7">
@@ -7897,7 +7927,7 @@
         <v>0.39398148148148149</v>
       </c>
       <c r="E156" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>17.333333333333378</v>
       </c>
       <c r="F156" s="7">
@@ -7923,7 +7953,7 @@
         <v>0.39538194444444447</v>
       </c>
       <c r="E157" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>19.350000000000065</v>
       </c>
       <c r="F157" s="7">
@@ -7949,7 +7979,7 @@
         <v>0.39677083333333335</v>
       </c>
       <c r="E158" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>21.350000000000058</v>
       </c>
       <c r="F158" s="7">
@@ -7975,7 +8005,7 @@
         <v>0.39815972222222223</v>
       </c>
       <c r="E159" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>23.350000000000051</v>
       </c>
       <c r="F159" s="7">
@@ -8001,7 +8031,7 @@
         <v>0.39956018518518521</v>
       </c>
       <c r="E160" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>25.366666666666742</v>
       </c>
       <c r="F160" s="7">
@@ -8027,7 +8057,7 @@
         <v>0.40096064814814814</v>
       </c>
       <c r="E161" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>27.383333333333351</v>
       </c>
       <c r="F161" s="7">
@@ -8037,7 +8067,7 @@
         <v>55</v>
       </c>
       <c r="H161" s="2">
-        <f t="shared" ref="H161:H224" si="7">IF(AND(G161&lt;&gt;"",F161&lt;&gt;""),G161-F161,"")</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -8053,7 +8083,7 @@
         <v>0.40234953703703702</v>
       </c>
       <c r="E162" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>29.383333333333344</v>
       </c>
       <c r="F162" s="7">
@@ -8063,7 +8093,7 @@
         <v>57</v>
       </c>
       <c r="H162" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8079,7 +8109,7 @@
         <v>0.40375</v>
       </c>
       <c r="E163" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>31.400000000000034</v>
       </c>
       <c r="F163" s="7">
@@ -8089,7 +8119,7 @@
         <v>57</v>
       </c>
       <c r="H163" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8105,7 +8135,7 @@
         <v>0.40513888888888888</v>
       </c>
       <c r="E164" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>33.400000000000027</v>
       </c>
       <c r="F164" s="7">
@@ -8115,7 +8145,7 @@
         <v>58</v>
       </c>
       <c r="H164" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
@@ -8131,7 +8161,7 @@
         <v>0.41736111111111113</v>
       </c>
       <c r="E165" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1.9999999999999929</v>
       </c>
       <c r="F165" s="7">
@@ -8141,7 +8171,7 @@
         <v>29</v>
       </c>
       <c r="H165" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -8157,7 +8187,7 @@
         <v>0.4183101851851852</v>
       </c>
       <c r="E166" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3.36666666666666</v>
       </c>
       <c r="F166" s="7">
@@ -8167,7 +8197,7 @@
         <v>33</v>
       </c>
       <c r="H166" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -8183,7 +8213,7 @@
         <v>0.41969907407407409</v>
       </c>
       <c r="E167" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5.3666666666666529</v>
       </c>
       <c r="F167" s="7">
@@ -8193,7 +8223,7 @@
         <v>39</v>
       </c>
       <c r="H167" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8209,7 +8239,7 @@
         <v>0.42109953703703706</v>
       </c>
       <c r="E168" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>7.3833333333333417</v>
       </c>
       <c r="F168" s="7">
@@ -8219,7 +8249,7 @@
         <v>42</v>
       </c>
       <c r="H168" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8235,7 +8265,7 @@
         <v>0.42248842592592595</v>
       </c>
       <c r="E169" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>9.3833333333333346</v>
       </c>
       <c r="F169" s="7">
@@ -8245,7 +8275,7 @@
         <v>44</v>
       </c>
       <c r="H169" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8261,7 +8291,7 @@
         <v>0.42387731481481483</v>
       </c>
       <c r="E170" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11.383333333333328</v>
       </c>
       <c r="F170" s="7">
@@ -8271,7 +8301,7 @@
         <v>45</v>
       </c>
       <c r="H170" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -8287,7 +8317,7 @@
         <v>0.42526620370370372</v>
       </c>
       <c r="E171" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>13.38333333333332</v>
       </c>
       <c r="F171" s="7">
@@ -8297,7 +8327,7 @@
         <v>48</v>
       </c>
       <c r="H171" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8313,7 +8343,7 @@
         <v>0.42666666666666669</v>
       </c>
       <c r="E172" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>15.400000000000009</v>
       </c>
       <c r="F172" s="7">
@@ -8323,7 +8353,7 @@
         <v>49</v>
       </c>
       <c r="H172" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -8339,7 +8369,7 @@
         <v>0.42806712962962962</v>
       </c>
       <c r="E173" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>17.416666666666618</v>
       </c>
       <c r="F173" s="7">
@@ -8349,7 +8379,7 @@
         <v>51</v>
       </c>
       <c r="H173" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8365,7 +8395,7 @@
         <v>0.4294675925925926</v>
       </c>
       <c r="E174" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>19.433333333333309</v>
       </c>
       <c r="F174" s="7">
@@ -8375,7 +8405,7 @@
         <v>52</v>
       </c>
       <c r="H174" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8391,7 +8421,7 @@
         <v>0.43086805555555557</v>
       </c>
       <c r="E175" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>21.449999999999996</v>
       </c>
       <c r="F175" s="7">
@@ -8401,7 +8431,7 @@
         <v>54</v>
       </c>
       <c r="H175" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8417,7 +8447,7 @@
         <v>0.43225694444444446</v>
       </c>
       <c r="E176" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>23.449999999999989</v>
       </c>
       <c r="F176" s="7">
@@ -8427,7 +8457,7 @@
         <v>55</v>
       </c>
       <c r="H176" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
@@ -8443,7 +8473,7 @@
         <v>0.43364583333333334</v>
       </c>
       <c r="E177" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>25.449999999999982</v>
       </c>
       <c r="F177" s="7">
@@ -8453,7 +8483,7 @@
         <v>55</v>
       </c>
       <c r="H177" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8469,7 +8499,7 @@
         <v>0.43504629629629632</v>
       </c>
       <c r="E178" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>27.466666666666669</v>
       </c>
       <c r="F178" s="7">
@@ -8479,7 +8509,7 @@
         <v>55</v>
       </c>
       <c r="H178" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -8495,7 +8525,7 @@
         <v>0.4364351851851852</v>
       </c>
       <c r="E179" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>29.466666666666661</v>
       </c>
       <c r="F179" s="7">
@@ -8505,7 +8535,7 @@
         <v>57</v>
       </c>
       <c r="H179" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8521,7 +8551,7 @@
         <v>0.43783564814814813</v>
       </c>
       <c r="E180" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>31.48333333333327</v>
       </c>
       <c r="F180" s="7">
@@ -8531,623 +8561,963 @@
         <v>58</v>
       </c>
       <c r="H180" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C181" s="9">
+        <f>_xlfn.XLOOKUP(Log!A181, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D181" s="9">
+        <v>0.41111111111111109</v>
+      </c>
+      <c r="E181" s="6">
+        <f t="shared" si="4"/>
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F181" s="7">
+        <v>29</v>
+      </c>
+      <c r="G181" s="2">
+        <v>30</v>
+      </c>
+      <c r="H181" s="2">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C182" s="9">
+        <f>_xlfn.XLOOKUP(Log!A182, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D182" s="9">
+        <v>0.4117824074074074</v>
+      </c>
+      <c r="E182" s="6">
+        <f t="shared" si="4"/>
+        <v>2.9666666666666774</v>
+      </c>
+      <c r="F182" s="7">
+        <v>35</v>
+      </c>
+      <c r="G182" s="2">
+        <v>35</v>
+      </c>
+      <c r="H182" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C183" s="9">
+        <f>_xlfn.XLOOKUP(Log!A183, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D183" s="9">
+        <v>0.41317129629629629</v>
+      </c>
+      <c r="E183" s="6">
+        <f t="shared" si="4"/>
+        <v>4.9666666666666703</v>
+      </c>
+      <c r="F183" s="7">
+        <v>38</v>
+      </c>
+      <c r="G183" s="2">
+        <v>41</v>
+      </c>
+      <c r="H183" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C184" s="9">
+        <f>_xlfn.XLOOKUP(Log!A184, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D184" s="9">
+        <v>0.41457175925925926</v>
+      </c>
+      <c r="E184" s="6">
+        <f t="shared" si="4"/>
+        <v>6.9833333333333591</v>
+      </c>
+      <c r="F184" s="7">
+        <v>41</v>
+      </c>
+      <c r="G184" s="2">
+        <v>44</v>
+      </c>
+      <c r="H184" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C185" s="9">
+        <f>_xlfn.XLOOKUP(Log!A185, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D185" s="9">
+        <v>0.41596064814814815</v>
+      </c>
+      <c r="E185" s="6">
+        <f t="shared" si="4"/>
+        <v>8.983333333333352</v>
+      </c>
+      <c r="F185" s="7">
+        <v>44</v>
+      </c>
+      <c r="G185" s="2">
+        <v>44</v>
+      </c>
+      <c r="H185" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C186" s="9">
+        <f>_xlfn.XLOOKUP(Log!A186, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D186" s="9">
+        <v>0.41734953703703703</v>
+      </c>
+      <c r="E186" s="6">
+        <f t="shared" si="4"/>
+        <v>10.983333333333345</v>
+      </c>
+      <c r="F186" s="7">
+        <v>44</v>
+      </c>
+      <c r="G186" s="2">
+        <v>47</v>
+      </c>
+      <c r="H186" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C187" s="9">
+        <f>_xlfn.XLOOKUP(Log!A187, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D187" s="9">
+        <v>0.41873842592592592</v>
+      </c>
+      <c r="E187" s="6">
+        <f t="shared" si="4"/>
+        <v>12.983333333333338</v>
+      </c>
+      <c r="F187" s="7">
+        <v>47</v>
+      </c>
+      <c r="G187" s="2">
+        <v>49</v>
+      </c>
+      <c r="H187" s="2">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C188" s="9">
+        <f>_xlfn.XLOOKUP(Log!A188, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D188" s="9">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="E188" s="6">
+        <f t="shared" si="4"/>
+        <v>15.000000000000027</v>
+      </c>
+      <c r="F188" s="7">
+        <v>49</v>
+      </c>
+      <c r="G188" s="2">
+        <v>49</v>
+      </c>
+      <c r="H188" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C189" s="9">
+        <f>_xlfn.XLOOKUP(Log!A189, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D189" s="9">
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="E189" s="6">
+        <f t="shared" si="4"/>
+        <v>17.000000000000021</v>
+      </c>
+      <c r="F189" s="7">
+        <v>49</v>
+      </c>
+      <c r="G189" s="2">
+        <v>52</v>
+      </c>
+      <c r="H189" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C190" s="9">
+        <f>_xlfn.XLOOKUP(Log!A190, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D190" s="9">
+        <v>0.42291666666666666</v>
+      </c>
+      <c r="E190" s="6">
+        <f t="shared" si="4"/>
+        <v>19.000000000000014</v>
+      </c>
+      <c r="F190" s="7">
+        <v>52</v>
+      </c>
+      <c r="G190" s="2">
+        <v>52</v>
+      </c>
+      <c r="H190" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C191" s="9">
+        <f>_xlfn.XLOOKUP(Log!A191, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D191" s="9">
+        <v>0.42431712962962964</v>
+      </c>
+      <c r="E191" s="6">
+        <f t="shared" si="4"/>
+        <v>21.016666666666701</v>
+      </c>
+      <c r="F191" s="7">
+        <v>52</v>
+      </c>
+      <c r="G191" s="2">
+        <v>55</v>
+      </c>
+      <c r="H191" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C192" s="9">
+        <f>_xlfn.XLOOKUP(Log!A192, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D192" s="9">
+        <v>0.42571759259259262</v>
+      </c>
+      <c r="E192" s="6">
+        <f t="shared" si="4"/>
+        <v>23.033333333333388</v>
+      </c>
+      <c r="F192" s="7">
+        <v>52</v>
+      </c>
+      <c r="G192" s="2">
+        <v>55</v>
+      </c>
+      <c r="H192" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C193" s="9">
+        <f>_xlfn.XLOOKUP(Log!A193, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D193" s="9">
+        <v>0.4271064814814815</v>
+      </c>
+      <c r="E193" s="6">
+        <f t="shared" si="4"/>
+        <v>25.033333333333381</v>
+      </c>
+      <c r="F193" s="7">
+        <v>55</v>
+      </c>
+      <c r="G193" s="2">
+        <v>55</v>
+      </c>
+      <c r="H193" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C194" s="9">
+        <f>_xlfn.XLOOKUP(Log!A194, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D194" s="9">
+        <v>0.42849537037037039</v>
+      </c>
+      <c r="E194" s="6">
+        <f t="shared" si="4"/>
+        <v>27.033333333333374</v>
+      </c>
+      <c r="F194" s="7">
+        <v>55</v>
+      </c>
+      <c r="G194" s="2">
+        <v>55</v>
+      </c>
+      <c r="H194" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C195" s="9">
+        <f>_xlfn.XLOOKUP(Log!A195, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D195" s="9">
+        <v>0.42989583333333331</v>
+      </c>
+      <c r="E195" s="6">
+        <f t="shared" ref="E195:E258" si="6">IF(AND($D195&lt;&gt;"", $C195&lt;&gt;""), ($D195-$C195)*1440, "")</f>
+        <v>29.049999999999983</v>
+      </c>
+      <c r="F195" s="7">
+        <v>55</v>
+      </c>
+      <c r="G195" s="2">
+        <v>58</v>
+      </c>
+      <c r="H195" s="2">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C196" s="9">
+        <f>_xlfn.XLOOKUP(Log!A196, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D196" s="9">
+        <v>0.43129629629629629</v>
+      </c>
+      <c r="E196" s="6">
+        <f t="shared" si="6"/>
+        <v>31.066666666666674</v>
+      </c>
+      <c r="F196" s="7">
+        <v>55</v>
+      </c>
+      <c r="G196" s="2">
+        <v>58</v>
+      </c>
+      <c r="H196" s="2">
+        <f t="shared" ref="H196:H211" si="7">IF(AND($G196&lt;&gt;"",$F196&lt;&gt;""), $G196-$F196, "")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C197" s="9">
+        <f>_xlfn.XLOOKUP(Log!A197, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D197" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="E197" s="6">
+        <f t="shared" si="6"/>
+        <v>3.9999999999999858</v>
+      </c>
+      <c r="F197" s="7">
+        <v>38</v>
+      </c>
+      <c r="G197" s="2">
+        <v>38</v>
+      </c>
+      <c r="H197" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C198" s="9">
+        <f>_xlfn.XLOOKUP(Log!A198, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D198" s="9">
+        <v>0.4387847222222222</v>
+      </c>
+      <c r="E198" s="6">
+        <f t="shared" si="6"/>
+        <v>5.8499999999999552</v>
+      </c>
+      <c r="F198" s="7">
+        <v>41</v>
+      </c>
+      <c r="G198" s="2">
+        <v>41</v>
+      </c>
+      <c r="H198" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C199" s="9">
+        <f>_xlfn.XLOOKUP(Log!A199, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D199" s="9">
+        <v>0.44018518518518518</v>
+      </c>
+      <c r="E199" s="6">
+        <f t="shared" si="6"/>
+        <v>7.866666666666644</v>
+      </c>
+      <c r="F199" s="7">
+        <v>44</v>
+      </c>
+      <c r="G199" s="2">
+        <v>44</v>
+      </c>
+      <c r="H199" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C200" s="9">
+        <f>_xlfn.XLOOKUP(Log!A200, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D200" s="9">
+        <v>0.44157407407407406</v>
+      </c>
+      <c r="E200" s="6">
+        <f t="shared" si="6"/>
+        <v>9.8666666666666369</v>
+      </c>
+      <c r="F200" s="7">
+        <v>44</v>
+      </c>
+      <c r="G200" s="2">
+        <v>47</v>
+      </c>
+      <c r="H200" s="2">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C181" s="9">
-        <f>_xlfn.XLOOKUP(Log!A181, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E181" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H181" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C182" s="9">
-        <f>_xlfn.XLOOKUP(Log!A182, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E182" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H182" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C183" s="9">
-        <f>_xlfn.XLOOKUP(Log!A183, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E183" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H183" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C184" s="9">
-        <f>_xlfn.XLOOKUP(Log!A184, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E184" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H184" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C185" s="9">
-        <f>_xlfn.XLOOKUP(Log!A185, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E185" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H185" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C186" s="9">
-        <f>_xlfn.XLOOKUP(Log!A186, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E186" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H186" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C187" s="9">
-        <f>_xlfn.XLOOKUP(Log!A187, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E187" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H187" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C188" s="9">
-        <f>_xlfn.XLOOKUP(Log!A188, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E188" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H188" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C189" s="9">
-        <f>_xlfn.XLOOKUP(Log!A189, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E189" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H189" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C190" s="9">
-        <f>_xlfn.XLOOKUP(Log!A190, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E190" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H190" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C191" s="9">
-        <f>_xlfn.XLOOKUP(Log!A191, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E191" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H191" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C192" s="9">
-        <f>_xlfn.XLOOKUP(Log!A192, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E192" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H192" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C193" s="9">
-        <f>_xlfn.XLOOKUP(Log!A193, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E193" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H193" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C194" s="9">
-        <f>_xlfn.XLOOKUP(Log!A194, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E194" s="6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H194" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C195" s="9">
-        <f>_xlfn.XLOOKUP(Log!A195, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E195" s="6" t="str">
-        <f t="shared" ref="E195:E258" si="8">IF(AND($D195&lt;&gt;"", $C195&lt;&gt;""), ($D195-$C195)*1440, "")</f>
-        <v/>
-      </c>
-      <c r="H195" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C196" s="9">
-        <f>_xlfn.XLOOKUP(Log!A196, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E196" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H196" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C197" s="9">
-        <f>_xlfn.XLOOKUP(Log!A197, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E197" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H197" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C198" s="9">
-        <f>_xlfn.XLOOKUP(Log!A198, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E198" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H198" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C199" s="9">
-        <f>_xlfn.XLOOKUP(Log!A199, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E199" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H199" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C200" s="9">
-        <f>_xlfn.XLOOKUP(Log!A200, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E200" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H200" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>46248</v>
+      </c>
       <c r="C201" s="9">
         <f>_xlfn.XLOOKUP(Log!A201, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E201" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H201" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D201" s="9">
+        <v>0.44436342592592593</v>
+      </c>
+      <c r="E201" s="6">
+        <f t="shared" si="6"/>
+        <v>13.883333333333319</v>
+      </c>
+      <c r="F201" s="7">
+        <v>49</v>
+      </c>
+      <c r="G201" s="2">
+        <v>49</v>
+      </c>
+      <c r="H201" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>46248</v>
+      </c>
       <c r="C202" s="9">
         <f>_xlfn.XLOOKUP(Log!A202, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E202" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H202" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D202" s="9">
+        <v>0.44575231481481481</v>
+      </c>
+      <c r="E202" s="6">
+        <f t="shared" si="6"/>
+        <v>15.883333333333312</v>
+      </c>
+      <c r="F202" s="7">
+        <v>49</v>
+      </c>
+      <c r="G202" s="2">
+        <v>52</v>
+      </c>
+      <c r="H202" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>46248</v>
+      </c>
       <c r="C203" s="9">
         <f>_xlfn.XLOOKUP(Log!A203, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E203" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H203" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D203" s="9">
+        <v>0.44715277777777779</v>
+      </c>
+      <c r="E203" s="6">
+        <f t="shared" si="6"/>
+        <v>17.899999999999999</v>
+      </c>
+      <c r="F203" s="7">
+        <v>52</v>
+      </c>
+      <c r="G203" s="2">
+        <v>52</v>
+      </c>
+      <c r="H203" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>46248</v>
+      </c>
       <c r="C204" s="9">
         <f>_xlfn.XLOOKUP(Log!A204, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E204" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H204" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D204" s="9">
+        <v>0.44855324074074077</v>
+      </c>
+      <c r="E204" s="6">
+        <f t="shared" si="6"/>
+        <v>19.916666666666689</v>
+      </c>
+      <c r="F204" s="7">
+        <v>52</v>
+      </c>
+      <c r="G204" s="2">
+        <v>52</v>
+      </c>
+      <c r="H204" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" s="1">
+        <v>46248</v>
+      </c>
       <c r="C205" s="9">
         <f>_xlfn.XLOOKUP(Log!A205, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E205" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H205" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D205" s="9">
+        <v>0.44994212962962965</v>
+      </c>
+      <c r="E205" s="6">
+        <f t="shared" si="6"/>
+        <v>21.916666666666682</v>
+      </c>
+      <c r="F205" s="7">
+        <v>52</v>
+      </c>
+      <c r="G205" s="2">
+        <v>55</v>
+      </c>
+      <c r="H205" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206" s="1">
+        <v>46248</v>
+      </c>
       <c r="C206" s="9">
         <f>_xlfn.XLOOKUP(Log!A206, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E206" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H206" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D206" s="9">
+        <v>0.45134259259259257</v>
+      </c>
+      <c r="E206" s="6">
+        <f t="shared" si="6"/>
+        <v>23.933333333333291</v>
+      </c>
+      <c r="F206" s="7">
+        <v>55</v>
+      </c>
+      <c r="G206" s="2">
+        <v>55</v>
+      </c>
+      <c r="H206" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>46248</v>
+      </c>
       <c r="C207" s="9">
         <f>_xlfn.XLOOKUP(Log!A207, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E207" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H207" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D207" s="9">
+        <v>0.45274305555555555</v>
+      </c>
+      <c r="E207" s="6">
+        <f t="shared" si="6"/>
+        <v>25.949999999999982</v>
+      </c>
+      <c r="F207" s="7">
+        <v>55</v>
+      </c>
+      <c r="G207" s="2">
+        <v>55</v>
+      </c>
+      <c r="H207" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>46248</v>
+      </c>
       <c r="C208" s="9">
         <f>_xlfn.XLOOKUP(Log!A208, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E208" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H208" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D208" s="9">
+        <v>0.45413194444444444</v>
+      </c>
+      <c r="E208" s="6">
+        <f t="shared" si="6"/>
+        <v>27.949999999999974</v>
+      </c>
+      <c r="F208" s="7">
+        <v>55</v>
+      </c>
+      <c r="G208" s="2">
+        <v>58</v>
+      </c>
+      <c r="H208" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>46248</v>
+      </c>
       <c r="C209" s="9">
         <f>_xlfn.XLOOKUP(Log!A209, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E209" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H209" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D209" s="9">
+        <v>0.45553240740740741</v>
+      </c>
+      <c r="E209" s="6">
+        <f t="shared" si="6"/>
+        <v>29.966666666666661</v>
+      </c>
+      <c r="F209" s="7">
+        <v>55</v>
+      </c>
+      <c r="G209" s="2">
+        <v>58</v>
+      </c>
+      <c r="H209" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>46248</v>
+      </c>
       <c r="C210" s="9">
         <f>_xlfn.XLOOKUP(Log!A210, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E210" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H210" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D210" s="9">
+        <v>0.4569212962962963</v>
+      </c>
+      <c r="E210" s="6">
+        <f t="shared" si="6"/>
+        <v>31.966666666666654</v>
+      </c>
+      <c r="F210" s="7">
+        <v>58</v>
+      </c>
+      <c r="G210" s="2">
+        <v>58</v>
+      </c>
+      <c r="H210" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>46248</v>
+      </c>
       <c r="C211" s="9">
         <f>_xlfn.XLOOKUP(Log!A211, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E211" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H211" s="2" t="str">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D211" s="9">
+        <v>0.45831018518518518</v>
+      </c>
+      <c r="E211" s="6">
+        <f t="shared" si="6"/>
+        <v>33.966666666666647</v>
+      </c>
+      <c r="F211" s="7">
+        <v>58</v>
+      </c>
+      <c r="G211" s="2">
+        <v>58</v>
+      </c>
+      <c r="H211" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C212" s="9">
         <f>_xlfn.XLOOKUP(Log!A212, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E212" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H212" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C213" s="9">
         <f>_xlfn.XLOOKUP(Log!A213, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E213" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H213" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C214" s="9">
         <f>_xlfn.XLOOKUP(Log!A214, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E214" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H214" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C215" s="9">
         <f>_xlfn.XLOOKUP(Log!A215, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E215" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H215" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C216" s="9">
         <f>_xlfn.XLOOKUP(Log!A216, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E216" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H216" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C217" s="9">
         <f>_xlfn.XLOOKUP(Log!A217, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E217" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H217" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C218" s="9">
         <f>_xlfn.XLOOKUP(Log!A218, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E218" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H218" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C219" s="9">
         <f>_xlfn.XLOOKUP(Log!A219, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E219" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H219" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C220" s="9">
         <f>_xlfn.XLOOKUP(Log!A220, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E220" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H220" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" ref="H161:H224" si="8">IF(AND(G220&lt;&gt;"",F220&lt;&gt;""),G220-F220,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C221" s="9">
         <f>_xlfn.XLOOKUP(Log!A221, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E221" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H221" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="H221" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="3:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C222" s="9">
         <f>_xlfn.XLOOKUP(Log!A222, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E222" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H222" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="H222" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="3:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C223" s="9">
         <f>_xlfn.XLOOKUP(Log!A223, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E223" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H223" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="H223" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="3:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C224" s="9">
         <f>_xlfn.XLOOKUP(Log!A224, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E224" s="6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H224" s="2" t="str">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H224" s="2" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9157,7 +9527,7 @@
         <v>0</v>
       </c>
       <c r="E225" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H225" s="2" t="str">
@@ -9171,7 +9541,7 @@
         <v>0</v>
       </c>
       <c r="E226" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H226" s="2" t="str">
@@ -9185,7 +9555,7 @@
         <v>0</v>
       </c>
       <c r="E227" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H227" s="2" t="str">
@@ -9199,7 +9569,7 @@
         <v>0</v>
       </c>
       <c r="E228" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H228" s="2" t="str">
@@ -9213,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="E229" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H229" s="2" t="str">
@@ -9227,7 +9597,7 @@
         <v>0</v>
       </c>
       <c r="E230" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H230" s="2" t="str">
@@ -9241,7 +9611,7 @@
         <v>0</v>
       </c>
       <c r="E231" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H231" s="2" t="str">
@@ -9255,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="E232" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H232" s="2" t="str">
@@ -9269,7 +9639,7 @@
         <v>0</v>
       </c>
       <c r="E233" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H233" s="2" t="str">
@@ -9283,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="E234" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H234" s="2" t="str">
@@ -9297,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="E235" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H235" s="2" t="str">
@@ -9311,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="E236" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H236" s="2" t="str">
@@ -9325,7 +9695,7 @@
         <v>0</v>
       </c>
       <c r="E237" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H237" s="2" t="str">
@@ -9339,7 +9709,7 @@
         <v>0</v>
       </c>
       <c r="E238" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H238" s="2" t="str">
@@ -9353,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="E239" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H239" s="2" t="str">
@@ -9367,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="E240" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H240" s="2" t="str">
@@ -9381,7 +9751,7 @@
         <v>0</v>
       </c>
       <c r="E241" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H241" s="2" t="str">
@@ -9395,7 +9765,7 @@
         <v>0</v>
       </c>
       <c r="E242" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H242" s="2" t="str">
@@ -9409,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="E243" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H243" s="2" t="str">
@@ -9423,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="E244" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H244" s="2" t="str">
@@ -9437,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="E245" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H245" s="2" t="str">
@@ -9451,7 +9821,7 @@
         <v>0</v>
       </c>
       <c r="E246" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H246" s="2" t="str">
@@ -9465,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="E247" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H247" s="2" t="str">
@@ -9479,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="E248" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H248" s="2" t="str">
@@ -9493,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="E249" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H249" s="2" t="str">
@@ -9507,7 +9877,7 @@
         <v>0</v>
       </c>
       <c r="E250" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H250" s="2" t="str">
@@ -9521,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="E251" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H251" s="2" t="str">
@@ -9535,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="E252" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H252" s="2" t="str">
@@ -9549,7 +9919,7 @@
         <v>0</v>
       </c>
       <c r="E253" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H253" s="2" t="str">
@@ -9563,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="E254" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H254" s="2" t="str">
@@ -9577,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="E255" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H255" s="2" t="str">
@@ -9591,7 +9961,7 @@
         <v>0</v>
       </c>
       <c r="E256" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H256" s="2" t="str">
@@ -9605,7 +9975,7 @@
         <v>0</v>
       </c>
       <c r="E257" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H257" s="2" t="str">
@@ -9619,7 +9989,7 @@
         <v>0</v>
       </c>
       <c r="E258" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="H258" s="2" t="str">
@@ -13590,14 +13960,19 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="A2:C1048576 D3:XFD32 D33:L40 D41:XFD44 D45:H45 D46:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45">
-    <cfRule type="expression" dxfId="2" priority="2">
+  <conditionalFormatting sqref="D3:XFD3 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45 D197:F211 G198:G211 A2:C1048576 D212:XFD1048576 I46:XFD211 I41:XFD44 I33:L40 D4:G196 I4:XFD32 H4:H211">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H9999">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="A3:H3 A197:F211 A212:H9999 A4:G196 H4:H211">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B3&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G198:G211">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>$B197&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13958,19 +14333,39 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="E18" s="25" t="str">
+      <c r="A18" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C18" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="E18" s="25">
         <f>IF(AND(D18&lt;&gt;"", C18&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>19.000000000000014</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="E19" s="25" t="str">
+      <c r="A19" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C19" s="2">
+        <v>25</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="E19" s="25">
         <f>IF(AND(D19&lt;&gt;"", C19&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -15431,7 +15826,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K23">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A52131-F5EB-42E6-B51B-46E173FE4A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171008E2-98C0-43AC-B73C-CE4A24E33C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1109,14 +1109,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1333,6 +1333,9 @@
                 <c:pt idx="16">
                   <c:v>46248</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1392,6 +1395,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>24.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1513,6 +1519,9 @@
                 <c:pt idx="16">
                   <c:v>46248</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46251</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1574,7 +1583,7 @@
                   <c:v>17.899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>21.483333333333388</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -8977,7 +8986,7 @@
         <v>58</v>
       </c>
       <c r="H196" s="2">
-        <f t="shared" ref="H196:H211" si="7">IF(AND($G196&lt;&gt;"",$F196&lt;&gt;""), $G196-$F196, "")</f>
+        <f t="shared" ref="H196:H259" si="7">IF(AND($G196&lt;&gt;"",$F196&lt;&gt;""), $G196-$F196, "")</f>
         <v>3</v>
       </c>
     </row>
@@ -9372,198 +9381,422 @@
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>46251</v>
+      </c>
       <c r="C212" s="9">
         <f>_xlfn.XLOOKUP(Log!A212, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E212" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D212" s="9">
+        <v>0.56111111111111112</v>
+      </c>
+      <c r="E212" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2.9999999999999893</v>
+      </c>
+      <c r="F212" s="7">
+        <v>29</v>
+      </c>
+      <c r="G212" s="2">
+        <v>31</v>
+      </c>
+      <c r="H212" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>46251</v>
+      </c>
       <c r="C213" s="9">
         <f>_xlfn.XLOOKUP(Log!A213, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E213" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D213" s="9">
+        <v>0.56137731481481479</v>
+      </c>
+      <c r="E213" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3.383333333333276</v>
+      </c>
+      <c r="F213" s="7">
+        <v>32</v>
+      </c>
+      <c r="G213" s="2">
+        <v>33</v>
+      </c>
+      <c r="H213" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>46251</v>
+      </c>
       <c r="C214" s="9">
         <f>_xlfn.XLOOKUP(Log!A214, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E214" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D214" s="9">
+        <v>0.56277777777777782</v>
+      </c>
+      <c r="E214" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>5.4000000000000448</v>
+      </c>
+      <c r="F214" s="7">
+        <v>36</v>
+      </c>
+      <c r="G214" s="2">
+        <v>38</v>
+      </c>
+      <c r="H214" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>46251</v>
+      </c>
       <c r="C215" s="9">
         <f>_xlfn.XLOOKUP(Log!A215, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E215" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D215" s="9">
+        <v>0.56417824074074074</v>
+      </c>
+      <c r="E215" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>7.4166666666666536</v>
+      </c>
+      <c r="F215" s="7">
+        <v>39</v>
+      </c>
+      <c r="G215" s="2">
+        <v>41</v>
+      </c>
+      <c r="H215" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>46251</v>
+      </c>
       <c r="C216" s="9">
         <f>_xlfn.XLOOKUP(Log!A216, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E216" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D216" s="9">
+        <v>0.56557870370370367</v>
+      </c>
+      <c r="E216" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>9.4333333333332625</v>
+      </c>
+      <c r="F216" s="7">
+        <v>41</v>
+      </c>
+      <c r="G216" s="2">
+        <v>44</v>
+      </c>
+      <c r="H216" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A217" s="1">
+        <v>46251</v>
+      </c>
       <c r="C217" s="9">
         <f>_xlfn.XLOOKUP(Log!A217, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E217" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D217" s="9">
+        <v>0.56696759259259255</v>
+      </c>
+      <c r="E217" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>11.433333333333255</v>
+      </c>
+      <c r="F217" s="7">
+        <v>44</v>
+      </c>
+      <c r="G217" s="2">
+        <v>45</v>
+      </c>
+      <c r="H217" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" s="1">
+        <v>46251</v>
+      </c>
       <c r="C218" s="9">
         <f>_xlfn.XLOOKUP(Log!A218, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E218" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D218" s="9">
+        <v>0.56836805555555558</v>
+      </c>
+      <c r="E218" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>13.450000000000024</v>
+      </c>
+      <c r="F218" s="7">
+        <v>45</v>
+      </c>
+      <c r="G218" s="2">
+        <v>47</v>
+      </c>
+      <c r="H218" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>46251</v>
+      </c>
       <c r="C219" s="9">
         <f>_xlfn.XLOOKUP(Log!A219, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E219" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D219" s="9">
+        <v>0.56975694444444447</v>
+      </c>
+      <c r="E219" s="6">
         <f t="shared" si="6"/>
-        <v/>
+        <v>15.450000000000017</v>
+      </c>
+      <c r="F219" s="7">
+        <v>47</v>
+      </c>
+      <c r="G219" s="2">
+        <v>49</v>
+      </c>
+      <c r="H219" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>46251</v>
+      </c>
       <c r="C220" s="9">
         <f>_xlfn.XLOOKUP(Log!A220, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E220" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D220" s="9">
+        <v>0.57115740740740739</v>
+      </c>
+      <c r="E220" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H220" s="2" t="str">
-        <f t="shared" ref="H161:H224" si="8">IF(AND(G220&lt;&gt;"",F220&lt;&gt;""),G220-F220,"")</f>
-        <v/>
+        <v>17.466666666666626</v>
+      </c>
+      <c r="F220" s="7">
+        <v>48</v>
+      </c>
+      <c r="G220" s="2">
+        <v>49</v>
+      </c>
+      <c r="H220" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>46251</v>
+      </c>
       <c r="C221" s="9">
         <f>_xlfn.XLOOKUP(Log!A221, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E221" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D221" s="9">
+        <v>0.57255787037037043</v>
+      </c>
+      <c r="E221" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H221" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <v>19.483333333333395</v>
+      </c>
+      <c r="F221" s="7">
+        <v>49</v>
+      </c>
+      <c r="G221" s="2">
+        <v>52</v>
+      </c>
+      <c r="H221" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
+        <v>46251</v>
+      </c>
       <c r="C222" s="9">
         <f>_xlfn.XLOOKUP(Log!A222, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E222" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D222" s="9">
+        <v>0.57394675925925931</v>
+      </c>
+      <c r="E222" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H222" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <v>21.483333333333388</v>
+      </c>
+      <c r="F222" s="7">
+        <v>51</v>
+      </c>
+      <c r="G222" s="2">
+        <v>52</v>
+      </c>
+      <c r="H222" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" s="1">
+        <v>46251</v>
+      </c>
       <c r="C223" s="9">
         <f>_xlfn.XLOOKUP(Log!A223, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E223" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D223" s="9">
+        <v>0.57534722222222223</v>
+      </c>
+      <c r="E223" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H223" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+        <v>23.499999999999996</v>
+      </c>
+      <c r="F223" s="7">
+        <v>51</v>
+      </c>
+      <c r="G223" s="2">
+        <v>52</v>
+      </c>
+      <c r="H223" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" s="1">
+        <v>46251</v>
+      </c>
       <c r="C224" s="9">
         <f>_xlfn.XLOOKUP(Log!A224, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E224" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D224" s="9">
+        <v>0.57673611111111112</v>
+      </c>
+      <c r="E224" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H224" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="3:8" x14ac:dyDescent="0.3">
+        <v>25.499999999999989</v>
+      </c>
+      <c r="F224" s="7">
+        <v>52</v>
+      </c>
+      <c r="G224" s="2">
+        <v>55</v>
+      </c>
+      <c r="H224" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>46251</v>
+      </c>
       <c r="C225" s="9">
         <f>_xlfn.XLOOKUP(Log!A225, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E225" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D225" s="9">
+        <v>0.578125</v>
+      </c>
+      <c r="E225" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H225" s="2" t="str">
-        <f t="shared" ref="H225:H288" si="9">IF(AND(G225&lt;&gt;"",F225&lt;&gt;""),G225-F225,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="3:8" x14ac:dyDescent="0.3">
+        <v>27.499999999999982</v>
+      </c>
+      <c r="F225" s="7">
+        <v>54</v>
+      </c>
+      <c r="G225" s="2">
+        <v>55</v>
+      </c>
+      <c r="H225" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A226" s="1">
+        <v>46251</v>
+      </c>
       <c r="C226" s="9">
         <f>_xlfn.XLOOKUP(Log!A226, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E226" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D226" s="9">
+        <v>0.57951388888888888</v>
+      </c>
+      <c r="E226" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H226" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="3:8" x14ac:dyDescent="0.3">
+        <v>29.499999999999975</v>
+      </c>
+      <c r="F226" s="7">
+        <v>54</v>
+      </c>
+      <c r="G226" s="2">
+        <v>55</v>
+      </c>
+      <c r="H226" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>46251</v>
+      </c>
       <c r="C227" s="9">
         <f>_xlfn.XLOOKUP(Log!A227, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E227" s="6" t="str">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D227" s="9">
+        <v>0.58090277777777777</v>
+      </c>
+      <c r="E227" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H227" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="3:8" x14ac:dyDescent="0.3">
+        <v>31.499999999999968</v>
+      </c>
+      <c r="F227" s="7">
+        <v>54</v>
+      </c>
+      <c r="G227" s="2">
+        <v>55</v>
+      </c>
+      <c r="H227" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C228" s="9">
         <f>_xlfn.XLOOKUP(Log!A228, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9573,11 +9806,11 @@
         <v/>
       </c>
       <c r="H228" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C229" s="9">
         <f>_xlfn.XLOOKUP(Log!A229, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9587,11 +9820,11 @@
         <v/>
       </c>
       <c r="H229" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C230" s="9">
         <f>_xlfn.XLOOKUP(Log!A230, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9601,11 +9834,11 @@
         <v/>
       </c>
       <c r="H230" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C231" s="9">
         <f>_xlfn.XLOOKUP(Log!A231, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9615,11 +9848,11 @@
         <v/>
       </c>
       <c r="H231" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C232" s="9">
         <f>_xlfn.XLOOKUP(Log!A232, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9629,11 +9862,11 @@
         <v/>
       </c>
       <c r="H232" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C233" s="9">
         <f>_xlfn.XLOOKUP(Log!A233, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9643,11 +9876,11 @@
         <v/>
       </c>
       <c r="H233" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C234" s="9">
         <f>_xlfn.XLOOKUP(Log!A234, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9657,11 +9890,11 @@
         <v/>
       </c>
       <c r="H234" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C235" s="9">
         <f>_xlfn.XLOOKUP(Log!A235, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9671,11 +9904,11 @@
         <v/>
       </c>
       <c r="H235" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C236" s="9">
         <f>_xlfn.XLOOKUP(Log!A236, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9685,11 +9918,11 @@
         <v/>
       </c>
       <c r="H236" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C237" s="9">
         <f>_xlfn.XLOOKUP(Log!A237, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9699,11 +9932,11 @@
         <v/>
       </c>
       <c r="H237" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C238" s="9">
         <f>_xlfn.XLOOKUP(Log!A238, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9713,11 +9946,11 @@
         <v/>
       </c>
       <c r="H238" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C239" s="9">
         <f>_xlfn.XLOOKUP(Log!A239, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9727,11 +9960,11 @@
         <v/>
       </c>
       <c r="H239" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C240" s="9">
         <f>_xlfn.XLOOKUP(Log!A240, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -9741,7 +9974,7 @@
         <v/>
       </c>
       <c r="H240" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9755,7 +9988,7 @@
         <v/>
       </c>
       <c r="H241" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9769,7 +10002,7 @@
         <v/>
       </c>
       <c r="H242" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9783,7 +10016,7 @@
         <v/>
       </c>
       <c r="H243" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9797,7 +10030,7 @@
         <v/>
       </c>
       <c r="H244" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9811,7 +10044,7 @@
         <v/>
       </c>
       <c r="H245" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9825,7 +10058,7 @@
         <v/>
       </c>
       <c r="H246" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9839,7 +10072,7 @@
         <v/>
       </c>
       <c r="H247" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9853,7 +10086,7 @@
         <v/>
       </c>
       <c r="H248" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9867,7 +10100,7 @@
         <v/>
       </c>
       <c r="H249" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9881,7 +10114,7 @@
         <v/>
       </c>
       <c r="H250" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9895,7 +10128,7 @@
         <v/>
       </c>
       <c r="H251" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9909,7 +10142,7 @@
         <v/>
       </c>
       <c r="H252" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9923,7 +10156,7 @@
         <v/>
       </c>
       <c r="H253" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9937,7 +10170,7 @@
         <v/>
       </c>
       <c r="H254" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9951,7 +10184,7 @@
         <v/>
       </c>
       <c r="H255" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9965,7 +10198,7 @@
         <v/>
       </c>
       <c r="H256" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9979,7 +10212,7 @@
         <v/>
       </c>
       <c r="H257" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -9993,7 +10226,7 @@
         <v/>
       </c>
       <c r="H258" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -10003,11 +10236,11 @@
         <v>0</v>
       </c>
       <c r="E259" s="6" t="str">
-        <f t="shared" ref="E259:E322" si="10">IF(AND($D259&lt;&gt;"", $C259&lt;&gt;""), ($D259-$C259)*1440, "")</f>
+        <f t="shared" ref="E259:E322" si="8">IF(AND($D259&lt;&gt;"", $C259&lt;&gt;""), ($D259-$C259)*1440, "")</f>
         <v/>
       </c>
       <c r="H259" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -10017,11 +10250,11 @@
         <v>0</v>
       </c>
       <c r="E260" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H260" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="H225:H288" si="9">IF(AND(G260&lt;&gt;"",F260&lt;&gt;""),G260-F260,"")</f>
         <v/>
       </c>
     </row>
@@ -10031,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="E261" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H261" s="2" t="str">
@@ -10045,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="E262" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H262" s="2" t="str">
@@ -10059,7 +10292,7 @@
         <v>0</v>
       </c>
       <c r="E263" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H263" s="2" t="str">
@@ -10073,7 +10306,7 @@
         <v>0</v>
       </c>
       <c r="E264" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H264" s="2" t="str">
@@ -10087,7 +10320,7 @@
         <v>0</v>
       </c>
       <c r="E265" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H265" s="2" t="str">
@@ -10101,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="E266" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H266" s="2" t="str">
@@ -10115,7 +10348,7 @@
         <v>0</v>
       </c>
       <c r="E267" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H267" s="2" t="str">
@@ -10129,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="E268" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H268" s="2" t="str">
@@ -10143,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="E269" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H269" s="2" t="str">
@@ -10157,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="E270" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H270" s="2" t="str">
@@ -10171,7 +10404,7 @@
         <v>0</v>
       </c>
       <c r="E271" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H271" s="2" t="str">
@@ -10185,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="E272" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H272" s="2" t="str">
@@ -10199,7 +10432,7 @@
         <v>0</v>
       </c>
       <c r="E273" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H273" s="2" t="str">
@@ -10213,7 +10446,7 @@
         <v>0</v>
       </c>
       <c r="E274" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H274" s="2" t="str">
@@ -10227,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="E275" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H275" s="2" t="str">
@@ -10241,7 +10474,7 @@
         <v>0</v>
       </c>
       <c r="E276" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H276" s="2" t="str">
@@ -10255,7 +10488,7 @@
         <v>0</v>
       </c>
       <c r="E277" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H277" s="2" t="str">
@@ -10269,7 +10502,7 @@
         <v>0</v>
       </c>
       <c r="E278" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H278" s="2" t="str">
@@ -10283,7 +10516,7 @@
         <v>0</v>
       </c>
       <c r="E279" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H279" s="2" t="str">
@@ -10297,7 +10530,7 @@
         <v>0</v>
       </c>
       <c r="E280" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H280" s="2" t="str">
@@ -10311,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="E281" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H281" s="2" t="str">
@@ -10325,7 +10558,7 @@
         <v>0</v>
       </c>
       <c r="E282" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H282" s="2" t="str">
@@ -10339,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="E283" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H283" s="2" t="str">
@@ -10353,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="E284" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H284" s="2" t="str">
@@ -10367,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="E285" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H285" s="2" t="str">
@@ -10381,7 +10614,7 @@
         <v>0</v>
       </c>
       <c r="E286" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H286" s="2" t="str">
@@ -10395,7 +10628,7 @@
         <v>0</v>
       </c>
       <c r="E287" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H287" s="2" t="str">
@@ -10409,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="E288" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H288" s="2" t="str">
@@ -10423,11 +10656,11 @@
         <v>0</v>
       </c>
       <c r="E289" s="6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H289" s="2" t="str">
-        <f t="shared" ref="H289:H352" si="11">IF(AND(G289&lt;&gt;"",F289&lt;&gt;""),G289-F289,"")</f>
+        <f t="shared" ref="H289:H352" si="10">IF(AND(G289&lt;&gt;"",F289&lt;&gt;""),G289-F289,"")</f>
         <v/>
       </c>
     </row>
@@ -10437,11 +10670,11 @@
         <v>0</v>
       </c>
       <c r="E290" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H290" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H290" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10451,11 +10684,11 @@
         <v>0</v>
       </c>
       <c r="E291" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H291" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H291" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10465,11 +10698,11 @@
         <v>0</v>
       </c>
       <c r="E292" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H292" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H292" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10479,11 +10712,11 @@
         <v>0</v>
       </c>
       <c r="E293" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H293" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H293" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10493,11 +10726,11 @@
         <v>0</v>
       </c>
       <c r="E294" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H294" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H294" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10507,11 +10740,11 @@
         <v>0</v>
       </c>
       <c r="E295" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H295" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H295" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10521,11 +10754,11 @@
         <v>0</v>
       </c>
       <c r="E296" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H296" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H296" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10535,11 +10768,11 @@
         <v>0</v>
       </c>
       <c r="E297" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H297" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H297" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10549,11 +10782,11 @@
         <v>0</v>
       </c>
       <c r="E298" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H298" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H298" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10563,11 +10796,11 @@
         <v>0</v>
       </c>
       <c r="E299" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H299" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H299" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10577,11 +10810,11 @@
         <v>0</v>
       </c>
       <c r="E300" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H300" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H300" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10591,11 +10824,11 @@
         <v>0</v>
       </c>
       <c r="E301" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H301" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H301" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10605,11 +10838,11 @@
         <v>0</v>
       </c>
       <c r="E302" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H302" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H302" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10619,11 +10852,11 @@
         <v>0</v>
       </c>
       <c r="E303" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H303" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H303" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10633,11 +10866,11 @@
         <v>0</v>
       </c>
       <c r="E304" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H304" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H304" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10647,11 +10880,11 @@
         <v>0</v>
       </c>
       <c r="E305" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H305" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H305" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10661,11 +10894,11 @@
         <v>0</v>
       </c>
       <c r="E306" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H306" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H306" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10675,11 +10908,11 @@
         <v>0</v>
       </c>
       <c r="E307" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H307" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H307" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10689,11 +10922,11 @@
         <v>0</v>
       </c>
       <c r="E308" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H308" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H308" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10703,11 +10936,11 @@
         <v>0</v>
       </c>
       <c r="E309" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H309" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H309" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10717,11 +10950,11 @@
         <v>0</v>
       </c>
       <c r="E310" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H310" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H310" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10731,11 +10964,11 @@
         <v>0</v>
       </c>
       <c r="E311" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H311" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H311" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10745,11 +10978,11 @@
         <v>0</v>
       </c>
       <c r="E312" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H312" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H312" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10759,11 +10992,11 @@
         <v>0</v>
       </c>
       <c r="E313" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H313" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H313" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10773,11 +11006,11 @@
         <v>0</v>
       </c>
       <c r="E314" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H314" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H314" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10787,11 +11020,11 @@
         <v>0</v>
       </c>
       <c r="E315" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H315" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H315" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10801,11 +11034,11 @@
         <v>0</v>
       </c>
       <c r="E316" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H316" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H316" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10815,11 +11048,11 @@
         <v>0</v>
       </c>
       <c r="E317" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H317" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H317" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10829,11 +11062,11 @@
         <v>0</v>
       </c>
       <c r="E318" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H318" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H318" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10843,11 +11076,11 @@
         <v>0</v>
       </c>
       <c r="E319" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H319" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H319" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10857,11 +11090,11 @@
         <v>0</v>
       </c>
       <c r="E320" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H320" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H320" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10871,11 +11104,11 @@
         <v>0</v>
       </c>
       <c r="E321" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H321" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H321" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10885,11 +11118,11 @@
         <v>0</v>
       </c>
       <c r="E322" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="H322" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H322" s="2" t="str">
-        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -10899,11 +11132,11 @@
         <v>0</v>
       </c>
       <c r="E323" s="6" t="str">
-        <f t="shared" ref="E323:E386" si="12">IF(AND($D323&lt;&gt;"", $C323&lt;&gt;""), ($D323-$C323)*1440, "")</f>
+        <f t="shared" ref="E323:E386" si="11">IF(AND($D323&lt;&gt;"", $C323&lt;&gt;""), ($D323-$C323)*1440, "")</f>
         <v/>
       </c>
       <c r="H323" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -10913,11 +11146,11 @@
         <v>0</v>
       </c>
       <c r="E324" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H324" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -10927,11 +11160,11 @@
         <v>0</v>
       </c>
       <c r="E325" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H325" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -10941,11 +11174,11 @@
         <v>0</v>
       </c>
       <c r="E326" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H326" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -10955,11 +11188,11 @@
         <v>0</v>
       </c>
       <c r="E327" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H327" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -10969,11 +11202,11 @@
         <v>0</v>
       </c>
       <c r="E328" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H328" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -10983,11 +11216,11 @@
         <v>0</v>
       </c>
       <c r="E329" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H329" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -10997,11 +11230,11 @@
         <v>0</v>
       </c>
       <c r="E330" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H330" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11011,11 +11244,11 @@
         <v>0</v>
       </c>
       <c r="E331" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H331" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11025,11 +11258,11 @@
         <v>0</v>
       </c>
       <c r="E332" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H332" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11039,11 +11272,11 @@
         <v>0</v>
       </c>
       <c r="E333" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H333" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11053,11 +11286,11 @@
         <v>0</v>
       </c>
       <c r="E334" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H334" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11067,11 +11300,11 @@
         <v>0</v>
       </c>
       <c r="E335" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H335" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11081,11 +11314,11 @@
         <v>0</v>
       </c>
       <c r="E336" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H336" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11095,11 +11328,11 @@
         <v>0</v>
       </c>
       <c r="E337" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H337" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11109,11 +11342,11 @@
         <v>0</v>
       </c>
       <c r="E338" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H338" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11123,11 +11356,11 @@
         <v>0</v>
       </c>
       <c r="E339" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H339" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11137,11 +11370,11 @@
         <v>0</v>
       </c>
       <c r="E340" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H340" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11151,11 +11384,11 @@
         <v>0</v>
       </c>
       <c r="E341" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H341" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11165,11 +11398,11 @@
         <v>0</v>
       </c>
       <c r="E342" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H342" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11179,11 +11412,11 @@
         <v>0</v>
       </c>
       <c r="E343" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H343" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11193,11 +11426,11 @@
         <v>0</v>
       </c>
       <c r="E344" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H344" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11207,11 +11440,11 @@
         <v>0</v>
       </c>
       <c r="E345" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H345" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11221,11 +11454,11 @@
         <v>0</v>
       </c>
       <c r="E346" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H346" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11235,11 +11468,11 @@
         <v>0</v>
       </c>
       <c r="E347" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H347" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11249,11 +11482,11 @@
         <v>0</v>
       </c>
       <c r="E348" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H348" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11263,11 +11496,11 @@
         <v>0</v>
       </c>
       <c r="E349" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H349" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11277,11 +11510,11 @@
         <v>0</v>
       </c>
       <c r="E350" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H350" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11291,11 +11524,11 @@
         <v>0</v>
       </c>
       <c r="E351" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H351" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11305,11 +11538,11 @@
         <v>0</v>
       </c>
       <c r="E352" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H352" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11319,11 +11552,11 @@
         <v>0</v>
       </c>
       <c r="E353" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="H353" s="2" t="str">
-        <f t="shared" ref="H353:H375" si="13">IF(AND(G353&lt;&gt;"",F353&lt;&gt;""),G353-F353,"")</f>
+        <f t="shared" ref="H353:H375" si="12">IF(AND(G353&lt;&gt;"",F353&lt;&gt;""),G353-F353,"")</f>
         <v/>
       </c>
     </row>
@@ -11333,11 +11566,11 @@
         <v>0</v>
       </c>
       <c r="E354" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H354" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H354" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11347,11 +11580,11 @@
         <v>0</v>
       </c>
       <c r="E355" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H355" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H355" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11361,11 +11594,11 @@
         <v>0</v>
       </c>
       <c r="E356" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H356" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H356" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11375,11 +11608,11 @@
         <v>0</v>
       </c>
       <c r="E357" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H357" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H357" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11389,11 +11622,11 @@
         <v>0</v>
       </c>
       <c r="E358" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H358" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H358" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11403,11 +11636,11 @@
         <v>0</v>
       </c>
       <c r="E359" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H359" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H359" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11417,11 +11650,11 @@
         <v>0</v>
       </c>
       <c r="E360" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H360" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H360" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11431,11 +11664,11 @@
         <v>0</v>
       </c>
       <c r="E361" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H361" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H361" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11445,11 +11678,11 @@
         <v>0</v>
       </c>
       <c r="E362" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H362" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H362" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11459,11 +11692,11 @@
         <v>0</v>
       </c>
       <c r="E363" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H363" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H363" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11473,11 +11706,11 @@
         <v>0</v>
       </c>
       <c r="E364" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H364" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H364" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11487,11 +11720,11 @@
         <v>0</v>
       </c>
       <c r="E365" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H365" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H365" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11501,11 +11734,11 @@
         <v>0</v>
       </c>
       <c r="E366" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H366" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H366" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11515,11 +11748,11 @@
         <v>0</v>
       </c>
       <c r="E367" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H367" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H367" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11529,11 +11762,11 @@
         <v>0</v>
       </c>
       <c r="E368" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H368" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H368" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11543,11 +11776,11 @@
         <v>0</v>
       </c>
       <c r="E369" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H369" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H369" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11557,11 +11790,11 @@
         <v>0</v>
       </c>
       <c r="E370" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H370" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H370" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11571,11 +11804,11 @@
         <v>0</v>
       </c>
       <c r="E371" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H371" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H371" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11585,11 +11818,11 @@
         <v>0</v>
       </c>
       <c r="E372" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H372" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H372" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11599,11 +11832,11 @@
         <v>0</v>
       </c>
       <c r="E373" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H373" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H373" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11613,11 +11846,11 @@
         <v>0</v>
       </c>
       <c r="E374" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H374" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H374" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11627,11 +11860,11 @@
         <v>0</v>
       </c>
       <c r="E375" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H375" s="2" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H375" s="2" t="str">
-        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11641,7 +11874,7 @@
         <v>0</v>
       </c>
       <c r="E376" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11651,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="E377" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11661,7 +11894,7 @@
         <v>0</v>
       </c>
       <c r="E378" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11671,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="E379" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11681,7 +11914,7 @@
         <v>0</v>
       </c>
       <c r="E380" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11691,7 +11924,7 @@
         <v>0</v>
       </c>
       <c r="E381" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11701,7 +11934,7 @@
         <v>0</v>
       </c>
       <c r="E382" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11711,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="E383" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11721,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="E384" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11731,7 +11964,7 @@
         <v>0</v>
       </c>
       <c r="E385" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11741,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="E386" s="6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -11751,7 +11984,7 @@
         <v>0</v>
       </c>
       <c r="E387" s="6" t="str">
-        <f t="shared" ref="E387:E450" si="14">IF(AND($D387&lt;&gt;"", $C387&lt;&gt;""), ($D387-$C387)*1440, "")</f>
+        <f t="shared" ref="E387:E450" si="13">IF(AND($D387&lt;&gt;"", $C387&lt;&gt;""), ($D387-$C387)*1440, "")</f>
         <v/>
       </c>
     </row>
@@ -11761,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="E388" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11771,7 +12004,7 @@
         <v>0</v>
       </c>
       <c r="E389" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11781,7 +12014,7 @@
         <v>0</v>
       </c>
       <c r="E390" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11791,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="E391" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11801,7 +12034,7 @@
         <v>0</v>
       </c>
       <c r="E392" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11811,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="E393" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11821,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="E394" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11831,7 +12064,7 @@
         <v>0</v>
       </c>
       <c r="E395" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11841,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="E396" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11851,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="E397" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11861,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="E398" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11871,7 +12104,7 @@
         <v>0</v>
       </c>
       <c r="E399" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11881,7 +12114,7 @@
         <v>0</v>
       </c>
       <c r="E400" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11891,7 +12124,7 @@
         <v>0</v>
       </c>
       <c r="E401" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11901,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="E402" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11911,7 +12144,7 @@
         <v>0</v>
       </c>
       <c r="E403" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11921,7 +12154,7 @@
         <v>0</v>
       </c>
       <c r="E404" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11931,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="E405" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11941,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="E406" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11951,7 +12184,7 @@
         <v>0</v>
       </c>
       <c r="E407" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11961,7 +12194,7 @@
         <v>0</v>
       </c>
       <c r="E408" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11971,7 +12204,7 @@
         <v>0</v>
       </c>
       <c r="E409" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11981,7 +12214,7 @@
         <v>0</v>
       </c>
       <c r="E410" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -11991,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="E411" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12001,7 +12234,7 @@
         <v>0</v>
       </c>
       <c r="E412" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12011,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="E413" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12021,7 +12254,7 @@
         <v>0</v>
       </c>
       <c r="E414" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12031,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="E415" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12041,7 +12274,7 @@
         <v>0</v>
       </c>
       <c r="E416" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12051,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="E417" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12061,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="E418" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12071,7 +12304,7 @@
         <v>0</v>
       </c>
       <c r="E419" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12081,7 +12314,7 @@
         <v>0</v>
       </c>
       <c r="E420" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12091,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="E421" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12101,7 +12334,7 @@
         <v>0</v>
       </c>
       <c r="E422" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12111,7 +12344,7 @@
         <v>0</v>
       </c>
       <c r="E423" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12121,7 +12354,7 @@
         <v>0</v>
       </c>
       <c r="E424" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12131,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="E425" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12141,7 +12374,7 @@
         <v>0</v>
       </c>
       <c r="E426" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12151,7 +12384,7 @@
         <v>0</v>
       </c>
       <c r="E427" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12161,7 +12394,7 @@
         <v>0</v>
       </c>
       <c r="E428" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12171,7 +12404,7 @@
         <v>0</v>
       </c>
       <c r="E429" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12181,7 +12414,7 @@
         <v>0</v>
       </c>
       <c r="E430" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12191,7 +12424,7 @@
         <v>0</v>
       </c>
       <c r="E431" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12201,7 +12434,7 @@
         <v>0</v>
       </c>
       <c r="E432" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12211,7 +12444,7 @@
         <v>0</v>
       </c>
       <c r="E433" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12221,7 +12454,7 @@
         <v>0</v>
       </c>
       <c r="E434" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12231,7 +12464,7 @@
         <v>0</v>
       </c>
       <c r="E435" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12241,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="E436" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12251,7 +12484,7 @@
         <v>0</v>
       </c>
       <c r="E437" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12261,7 +12494,7 @@
         <v>0</v>
       </c>
       <c r="E438" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12271,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="E439" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12281,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="E440" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12291,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="E441" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12301,7 +12534,7 @@
         <v>0</v>
       </c>
       <c r="E442" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12311,7 +12544,7 @@
         <v>0</v>
       </c>
       <c r="E443" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12321,7 +12554,7 @@
         <v>0</v>
       </c>
       <c r="E444" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12331,7 +12564,7 @@
         <v>0</v>
       </c>
       <c r="E445" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12341,7 +12574,7 @@
         <v>0</v>
       </c>
       <c r="E446" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12351,7 +12584,7 @@
         <v>0</v>
       </c>
       <c r="E447" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12361,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="E448" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12371,7 +12604,7 @@
         <v>0</v>
       </c>
       <c r="E449" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12381,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="E450" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12391,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="E451" s="6" t="str">
-        <f t="shared" ref="E451:E514" si="15">IF(AND($D451&lt;&gt;"", $C451&lt;&gt;""), ($D451-$C451)*1440, "")</f>
+        <f t="shared" ref="E451:E514" si="14">IF(AND($D451&lt;&gt;"", $C451&lt;&gt;""), ($D451-$C451)*1440, "")</f>
         <v/>
       </c>
     </row>
@@ -12401,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="E452" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12411,7 +12644,7 @@
         <v>0</v>
       </c>
       <c r="E453" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12421,7 +12654,7 @@
         <v>0</v>
       </c>
       <c r="E454" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12431,7 +12664,7 @@
         <v>0</v>
       </c>
       <c r="E455" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12441,7 +12674,7 @@
         <v>0</v>
       </c>
       <c r="E456" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12451,7 +12684,7 @@
         <v>0</v>
       </c>
       <c r="E457" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12461,7 +12694,7 @@
         <v>0</v>
       </c>
       <c r="E458" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12471,7 +12704,7 @@
         <v>0</v>
       </c>
       <c r="E459" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12481,7 +12714,7 @@
         <v>0</v>
       </c>
       <c r="E460" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12491,7 +12724,7 @@
         <v>0</v>
       </c>
       <c r="E461" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12501,7 +12734,7 @@
         <v>0</v>
       </c>
       <c r="E462" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12511,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="E463" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12521,7 +12754,7 @@
         <v>0</v>
       </c>
       <c r="E464" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12531,7 +12764,7 @@
         <v>0</v>
       </c>
       <c r="E465" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12541,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="E466" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12551,7 +12784,7 @@
         <v>0</v>
       </c>
       <c r="E467" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12561,7 +12794,7 @@
         <v>0</v>
       </c>
       <c r="E468" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12571,7 +12804,7 @@
         <v>0</v>
       </c>
       <c r="E469" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12581,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="E470" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12591,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="E471" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12601,7 +12834,7 @@
         <v>0</v>
       </c>
       <c r="E472" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12611,7 +12844,7 @@
         <v>0</v>
       </c>
       <c r="E473" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12621,7 +12854,7 @@
         <v>0</v>
       </c>
       <c r="E474" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12631,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="E475" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12641,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="E476" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12651,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="E477" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12661,7 +12894,7 @@
         <v>0</v>
       </c>
       <c r="E478" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12671,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="E479" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12681,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="E480" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12691,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="E481" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12701,7 +12934,7 @@
         <v>0</v>
       </c>
       <c r="E482" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12711,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="E483" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12721,7 +12954,7 @@
         <v>0</v>
       </c>
       <c r="E484" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12731,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="E485" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12741,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="E486" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12751,7 +12984,7 @@
         <v>0</v>
       </c>
       <c r="E487" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12761,7 +12994,7 @@
         <v>0</v>
       </c>
       <c r="E488" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12771,7 +13004,7 @@
         <v>0</v>
       </c>
       <c r="E489" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12781,1177 +13014,1177 @@
         <v>0</v>
       </c>
       <c r="E490" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E491" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E492" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E493" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E494" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E495" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E496" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E497" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E498" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E499" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E500" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E501" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E502" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E503" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E504" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E505" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E506" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E507" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E508" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E509" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E510" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E511" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E512" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E513" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E514" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E515" s="6" t="str">
-        <f t="shared" ref="E515:E578" si="16">IF(AND($D515&lt;&gt;"", $C515&lt;&gt;""), ($D515-$C515)*1440, "")</f>
+        <f t="shared" ref="E515:E578" si="15">IF(AND($D515&lt;&gt;"", $C515&lt;&gt;""), ($D515-$C515)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="516" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E516" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E517" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E518" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E519" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E520" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E521" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E522" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E523" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E524" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E525" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E526" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E527" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E528" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E529" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E530" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E531" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E532" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E533" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E534" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E535" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E536" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E537" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E538" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E539" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E540" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E541" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E542" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E543" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E544" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E545" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="546" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E546" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E547" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E548" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E549" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E550" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E551" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E552" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E553" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E554" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E555" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E556" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E557" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E558" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E559" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E560" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E561" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E562" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E563" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E564" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E565" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E566" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E567" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E568" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E569" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E570" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E571" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E572" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E573" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E574" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E575" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E576" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E577" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E578" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E579" s="6" t="str">
-        <f t="shared" ref="E579:E642" si="17">IF(AND($D579&lt;&gt;"", $C579&lt;&gt;""), ($D579-$C579)*1440, "")</f>
+        <f t="shared" ref="E579:E642" si="16">IF(AND($D579&lt;&gt;"", $C579&lt;&gt;""), ($D579-$C579)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="580" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E580" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E581" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E582" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E583" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E584" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E585" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E586" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E587" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E588" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E589" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E590" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E591" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E592" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E593" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E594" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E595" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E596" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E597" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E598" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E599" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E600" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E601" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E602" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E603" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E604" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E605" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E606" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E607" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E608" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E609" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="610" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E610" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E611" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E612" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E613" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E614" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E615" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E616" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E617" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E618" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E619" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E620" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E621" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E622" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E623" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E624" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E625" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E626" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E627" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E628" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E629" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E630" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E631" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E632" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E633" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E634" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E635" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E636" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E637" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E638" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E639" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E640" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E641" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E642" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E643" s="6" t="str">
-        <f t="shared" ref="E643:E685" si="18">IF(AND($D643&lt;&gt;"", $C643&lt;&gt;""), ($D643-$C643)*1440, "")</f>
+        <f t="shared" ref="E643:E685" si="17">IF(AND($D643&lt;&gt;"", $C643&lt;&gt;""), ($D643-$C643)*1440, "")</f>
         <v/>
       </c>
     </row>
     <row r="644" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E644" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E645" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E646" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E647" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E648" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E649" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E650" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E651" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E652" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E653" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E654" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E655" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E656" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E657" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E658" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E659" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E660" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E661" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E662" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E663" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E664" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E665" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E666" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E667" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E668" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E669" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E670" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E671" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E672" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E673" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="674" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E674" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E675" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E676" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E677" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E678" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E679" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E680" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E681" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E682" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E683" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E684" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E685" s="6" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13960,18 +14193,18 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="D3:XFD3 A1 I1:XFD1 D2:I2 K2:XFD2 O33:XFD40 J45:XFD45 D197:F211 G198:G211 A2:C1048576 D212:XFD1048576 I46:XFD211 I41:XFD44 I33:L40 D4:G196 I4:XFD32 H4:H211">
+  <conditionalFormatting sqref="A2:C1048576 D3:XFD3 D4:G196 H4:H211 D197:F211 A1 I1:XFD1 D2:I2 K2:XFD2 I4:XFD32 I33:L40 O33:XFD40 I41:XFD44 J45:XFD45 I46:XFD211 G198:G211 D212:XFD1048576">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H3 A197:F211 A212:H9999 A4:G196 H4:H211">
+  <conditionalFormatting sqref="A3:H3 A4:G196 H4:H211 A197:F211 A212:H9999">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B3&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G198:G211">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>$B197&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14369,11 +14602,21 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="E20" s="25" t="str">
+      <c r="A20" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46251</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="E20" s="25">
         <f>IF(AND(D20&lt;&gt;"", C20&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>21.483333333333388</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -15826,7 +16069,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K23">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171008E2-98C0-43AC-B73C-CE4A24E33C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B44BFD-60D8-4207-9720-F8CAC10EE65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -1105,7 +1105,21 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1336,6 +1350,9 @@
                 <c:pt idx="17">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46252</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1397,6 +1414,9 @@
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>24.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1522,6 +1542,9 @@
                 <c:pt idx="17">
                   <c:v>46251</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46252</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1586,7 +1609,7 @@
                   <c:v>21.483333333333388</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>19.63333333333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -9797,230 +9820,422 @@
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>46252</v>
+      </c>
       <c r="C228" s="9">
         <f>_xlfn.XLOOKUP(Log!A228, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E228" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D228" s="9">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="E228" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H228" s="2" t="str">
+        <v>0</v>
+      </c>
+      <c r="F228" s="7">
+        <v>29</v>
+      </c>
+      <c r="G228" s="2">
+        <v>30</v>
+      </c>
+      <c r="H228" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>46252</v>
+      </c>
       <c r="C229" s="9">
         <f>_xlfn.XLOOKUP(Log!A229, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E229" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D229" s="9">
+        <v>0.42815972222222221</v>
+      </c>
+      <c r="E229" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H229" s="2" t="str">
+        <v>1.5500000000000025</v>
+      </c>
+      <c r="F229" s="7">
+        <v>33</v>
+      </c>
+      <c r="G229" s="2">
+        <v>35</v>
+      </c>
+      <c r="H229" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>46252</v>
+      </c>
       <c r="C230" s="9">
         <f>_xlfn.XLOOKUP(Log!A230, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E230" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D230" s="9">
+        <v>0.42956018518518518</v>
+      </c>
+      <c r="E230" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H230" s="2" t="str">
+        <v>3.5666666666666913</v>
+      </c>
+      <c r="F230" s="7">
+        <v>38</v>
+      </c>
+      <c r="G230" s="2">
+        <v>39</v>
+      </c>
+      <c r="H230" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>46252</v>
+      </c>
       <c r="C231" s="9">
         <f>_xlfn.XLOOKUP(Log!A231, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E231" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D231" s="9">
+        <v>0.43094907407407407</v>
+      </c>
+      <c r="E231" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H231" s="2" t="str">
+        <v>5.5666666666666842</v>
+      </c>
+      <c r="F231" s="7">
+        <v>41</v>
+      </c>
+      <c r="G231" s="2">
+        <v>42</v>
+      </c>
+      <c r="H231" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A232" s="1">
+        <v>46252</v>
+      </c>
       <c r="C232" s="9">
         <f>_xlfn.XLOOKUP(Log!A232, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E232" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D232" s="9">
+        <v>0.43234953703703705</v>
+      </c>
+      <c r="E232" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H232" s="2" t="str">
+        <v>7.583333333333373</v>
+      </c>
+      <c r="F232" s="7">
+        <v>41</v>
+      </c>
+      <c r="G232" s="2">
+        <v>44</v>
+      </c>
+      <c r="H232" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>46252</v>
+      </c>
       <c r="C233" s="9">
         <f>_xlfn.XLOOKUP(Log!A233, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E233" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D233" s="9">
+        <v>0.43375000000000002</v>
+      </c>
+      <c r="E233" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H233" s="2" t="str">
+        <v>9.6000000000000618</v>
+      </c>
+      <c r="F233" s="7">
+        <v>44</v>
+      </c>
+      <c r="G233" s="2">
+        <v>47</v>
+      </c>
+      <c r="H233" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>46252</v>
+      </c>
       <c r="C234" s="9">
         <f>_xlfn.XLOOKUP(Log!A234, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E234" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D234" s="9">
+        <v>0.43513888888888891</v>
+      </c>
+      <c r="E234" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H234" s="2" t="str">
+        <v>11.600000000000055</v>
+      </c>
+      <c r="F234" s="7">
+        <v>45</v>
+      </c>
+      <c r="G234" s="2">
+        <v>49</v>
+      </c>
+      <c r="H234" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>46252</v>
+      </c>
       <c r="C235" s="9">
         <f>_xlfn.XLOOKUP(Log!A235, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E235" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D235" s="9">
+        <v>0.43653935185185183</v>
+      </c>
+      <c r="E235" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H235" s="2" t="str">
+        <v>13.616666666666664</v>
+      </c>
+      <c r="F235" s="7">
+        <v>48</v>
+      </c>
+      <c r="G235" s="2">
+        <v>49</v>
+      </c>
+      <c r="H235" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A236" s="1">
+        <v>46252</v>
+      </c>
       <c r="C236" s="9">
         <f>_xlfn.XLOOKUP(Log!A236, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E236" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D236" s="9">
+        <v>0.43793981481481481</v>
+      </c>
+      <c r="E236" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H236" s="2" t="str">
+        <v>15.633333333333352</v>
+      </c>
+      <c r="F236" s="7">
+        <v>48</v>
+      </c>
+      <c r="G236" s="2">
+        <v>52</v>
+      </c>
+      <c r="H236" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>46252</v>
+      </c>
       <c r="C237" s="9">
         <f>_xlfn.XLOOKUP(Log!A237, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E237" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D237" s="9">
+        <v>0.43932870370370369</v>
+      </c>
+      <c r="E237" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H237" s="2" t="str">
+        <v>17.633333333333347</v>
+      </c>
+      <c r="F237" s="7">
+        <v>49</v>
+      </c>
+      <c r="G237" s="2">
+        <v>52</v>
+      </c>
+      <c r="H237" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>46252</v>
+      </c>
       <c r="C238" s="9">
         <f>_xlfn.XLOOKUP(Log!A238, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E238" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D238" s="9">
+        <v>0.44071759259259258</v>
+      </c>
+      <c r="E238" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H238" s="2" t="str">
+        <v>19.63333333333334</v>
+      </c>
+      <c r="F238" s="7">
+        <v>51</v>
+      </c>
+      <c r="G238" s="2">
+        <v>52</v>
+      </c>
+      <c r="H238" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>46252</v>
+      </c>
       <c r="C239" s="9">
         <f>_xlfn.XLOOKUP(Log!A239, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E239" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D239" s="9">
+        <v>0.44211805555555556</v>
+      </c>
+      <c r="E239" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H239" s="2" t="str">
+        <v>21.650000000000027</v>
+      </c>
+      <c r="F239" s="7">
+        <v>52</v>
+      </c>
+      <c r="G239" s="2">
+        <v>55</v>
+      </c>
+      <c r="H239" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>46252</v>
+      </c>
       <c r="C240" s="9">
         <f>_xlfn.XLOOKUP(Log!A240, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E240" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D240" s="9">
+        <v>0.44350694444444444</v>
+      </c>
+      <c r="E240" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H240" s="2" t="str">
+        <v>23.65000000000002</v>
+      </c>
+      <c r="F240" s="7">
+        <v>52</v>
+      </c>
+      <c r="G240" s="2">
+        <v>55</v>
+      </c>
+      <c r="H240" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A241" s="1">
+        <v>46252</v>
+      </c>
       <c r="C241" s="9">
         <f>_xlfn.XLOOKUP(Log!A241, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E241" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D241" s="9">
+        <v>0.44489583333333332</v>
+      </c>
+      <c r="E241" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H241" s="2" t="str">
+        <v>25.650000000000013</v>
+      </c>
+      <c r="F241" s="7">
+        <v>54</v>
+      </c>
+      <c r="G241" s="2">
+        <v>55</v>
+      </c>
+      <c r="H241" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A242" s="1">
+        <v>46252</v>
+      </c>
       <c r="C242" s="9">
         <f>_xlfn.XLOOKUP(Log!A242, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E242" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D242" s="9">
+        <v>0.4462962962962963</v>
+      </c>
+      <c r="E242" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H242" s="2" t="str">
+        <v>27.6666666666667</v>
+      </c>
+      <c r="F242" s="7">
+        <v>54</v>
+      </c>
+      <c r="G242" s="2">
+        <v>58</v>
+      </c>
+      <c r="H242" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>46252</v>
+      </c>
       <c r="C243" s="9">
         <f>_xlfn.XLOOKUP(Log!A243, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E243" s="6" t="str">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D243" s="9">
+        <v>0.44769675925925928</v>
+      </c>
+      <c r="E243" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H243" s="2" t="str">
+        <v>29.68333333333339</v>
+      </c>
+      <c r="F243" s="7">
+        <v>55</v>
+      </c>
+      <c r="G243" s="2">
+        <v>58</v>
+      </c>
+      <c r="H243" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C244" s="9">
         <f>_xlfn.XLOOKUP(Log!A244, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10034,7 +10249,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C245" s="9">
         <f>_xlfn.XLOOKUP(Log!A245, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10048,7 +10263,7 @@
         <v/>
       </c>
     </row>
-    <row r="246" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C246" s="9">
         <f>_xlfn.XLOOKUP(Log!A246, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10062,7 +10277,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C247" s="9">
         <f>_xlfn.XLOOKUP(Log!A247, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10076,7 +10291,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C248" s="9">
         <f>_xlfn.XLOOKUP(Log!A248, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10090,7 +10305,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C249" s="9">
         <f>_xlfn.XLOOKUP(Log!A249, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10104,7 +10319,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C250" s="9">
         <f>_xlfn.XLOOKUP(Log!A250, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10118,7 +10333,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C251" s="9">
         <f>_xlfn.XLOOKUP(Log!A251, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10132,7 +10347,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C252" s="9">
         <f>_xlfn.XLOOKUP(Log!A252, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10146,7 +10361,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C253" s="9">
         <f>_xlfn.XLOOKUP(Log!A253, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10160,7 +10375,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C254" s="9">
         <f>_xlfn.XLOOKUP(Log!A254, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10174,7 +10389,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C255" s="9">
         <f>_xlfn.XLOOKUP(Log!A255, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10188,7 +10403,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C256" s="9">
         <f>_xlfn.XLOOKUP(Log!A256, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10254,7 +10469,7 @@
         <v/>
       </c>
       <c r="H260" s="2" t="str">
-        <f t="shared" ref="H225:H288" si="9">IF(AND(G260&lt;&gt;"",F260&lt;&gt;""),G260-F260,"")</f>
+        <f t="shared" ref="H260:H288" si="9">IF(AND(G260&lt;&gt;"",F260&lt;&gt;""),G260-F260,"")</f>
         <v/>
       </c>
     </row>
@@ -14193,18 +14408,18 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="A2:C1048576 D3:XFD3 D4:G196 H4:H211 D197:F211 A1 I1:XFD1 D2:I2 K2:XFD2 I4:XFD32 I33:L40 O33:XFD40 I41:XFD44 J45:XFD45 I46:XFD211 G198:G211 D212:XFD1048576">
-    <cfRule type="expression" dxfId="3" priority="2">
+  <conditionalFormatting sqref="D3:XFD3 D4:G196 H4:H211 D197:F211 D212:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 I4:XFD32 I33:L40 O33:XFD40 I41:XFD44 J45:XFD45 I46:XFD211 G198:G211 A2:C1048576">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:H3 A4:G196 H4:H211 A197:F211 A212:H9999">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$B3&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G198:G211">
-    <cfRule type="expression" dxfId="1" priority="7">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>$B197&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14620,11 +14835,21 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="E21" s="25" t="str">
+      <c r="A21" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C21" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="E21" s="25">
         <f>IF(AND(D21&lt;&gt;"", C21&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>19.63333333333334</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -16069,7 +16294,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K23">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B44BFD-60D8-4207-9720-F8CAC10EE65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A323F941-842D-4663-B17E-29CB0358A1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -1353,6 +1353,9 @@
                 <c:pt idx="18">
                   <c:v>46252</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46253</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1417,6 +1420,9 @@
                   <c:v>24.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>24.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1544,6 +1550,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10236,17 +10245,29 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>46253</v>
+      </c>
       <c r="C244" s="9">
         <f>_xlfn.XLOOKUP(Log!A244, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E244" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D244" s="9">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="E244" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H244" s="2" t="str">
+        <v>4.0000000000000657</v>
+      </c>
+      <c r="F244" s="7">
+        <v>38</v>
+      </c>
+      <c r="G244" s="2">
+        <v>39</v>
+      </c>
+      <c r="H244" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
@@ -14853,11 +14874,21 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="A22" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46253</v>
+      </c>
+      <c r="C22" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.45902777777777776</v>
+      </c>
       <c r="E22" s="25" t="str">
         <f>IF(AND(D22&lt;&gt;"", C22&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
+        <v>–</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A323F941-842D-4663-B17E-29CB0358A1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1DC83B-A84B-47A7-B756-9B2F8EB23AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Visualisations" sheetId="3" r:id="rId5"/>
     <sheet name="DevScriptErrors" sheetId="5" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>Starting Time</t>
   </si>
@@ -550,6 +550,9 @@
   </si>
   <si>
     <t>initial recording/camera startup time slightly delayed by interruption</t>
+  </si>
+  <si>
+    <t>lab interruption, delay in starting reader &amp; adjusting window - script read for 12 cameras instead of 18 for several read cycles</t>
   </si>
 </sst>
 </file>
@@ -1105,21 +1108,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1204,15 +1193,23 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-GB"/>
-              <a:t>Effect of Room</a:t>
+              <a:t>Temperature</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" baseline="0"/>
-              <a:t> Temperature on Startup Time</a:t>
+              <a:t> Effect on Startup Time</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.4270778652668405E-2"/>
+          <c:y val="2.4630541871921183E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1244,7 +1241,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.9358705161854772E-2"/>
+          <c:y val="0.20151888341543514"/>
+          <c:w val="0.86683814523184599"/>
+          <c:h val="0.58522781635054233"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1356,6 +1363,12 @@
                 <c:pt idx="19">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46255</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1424,6 +1437,12 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1554,6 +1573,12 @@
                 <c:pt idx="19">
                   <c:v>46253</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46255</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1621,13 +1646,13 @@
                   <c:v>19.63333333333334</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>20.11666666666672</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>20.883333333333454</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>18.816666666666677</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
@@ -1914,11 +1939,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2072,6 +2097,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.66121281714785651"/>
+          <c:y val="1.1698537682789651E-2"/>
+          <c:w val="0.3359076990376203"/>
+          <c:h val="0.14265285804791641"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2085,7 +2120,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3475,15 +3510,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
+      <xdr:colOff>121920</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>396240</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3912,7 +3947,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E78"/>
   </sheetPr>
-  <dimension ref="A1:J685"/>
+  <dimension ref="A1:J700"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
@@ -8982,7 +9017,7 @@
         <v>0.42989583333333331</v>
       </c>
       <c r="E195" s="6">
-        <f t="shared" ref="E195:E258" si="6">IF(AND($D195&lt;&gt;"", $C195&lt;&gt;""), ($D195-$C195)*1440, "")</f>
+        <f t="shared" ref="E195:E273" si="6">IF(AND($D195&lt;&gt;"", $C195&lt;&gt;""), ($D195-$C195)*1440, "")</f>
         <v>29.049999999999983</v>
       </c>
       <c r="F195" s="7">
@@ -9018,7 +9053,7 @@
         <v>58</v>
       </c>
       <c r="H196" s="2">
-        <f t="shared" ref="H196:H259" si="7">IF(AND($G196&lt;&gt;"",$F196&lt;&gt;""), $G196-$F196, "")</f>
+        <f t="shared" ref="H196:H274" si="7">IF(AND($G196&lt;&gt;"",$F196&lt;&gt;""), $G196-$F196, "")</f>
         <v>3</v>
       </c>
     </row>
@@ -10271,664 +10306,1229 @@
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>46253</v>
+      </c>
       <c r="C245" s="9">
         <f>_xlfn.XLOOKUP(Log!A245, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E245" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D245" s="9">
+        <v>0.46325231481481483</v>
+      </c>
+      <c r="E245" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H245" s="2" t="str">
+        <v>6.0833333333333783</v>
+      </c>
+      <c r="F245" s="7">
+        <v>38</v>
+      </c>
+      <c r="G245" s="2">
+        <v>41</v>
+      </c>
+      <c r="H245" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>46253</v>
+      </c>
       <c r="C246" s="9">
         <f>_xlfn.XLOOKUP(Log!A246, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E246" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D246" s="9">
+        <v>0.4646527777777778</v>
+      </c>
+      <c r="E246" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H246" s="2" t="str">
+        <v>8.1000000000000671</v>
+      </c>
+      <c r="F246" s="7">
+        <v>41</v>
+      </c>
+      <c r="G246" s="2">
+        <v>42</v>
+      </c>
+      <c r="H246" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>46253</v>
+      </c>
       <c r="C247" s="9">
         <f>_xlfn.XLOOKUP(Log!A247, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E247" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D247" s="9">
+        <v>0.46604166666666669</v>
+      </c>
+      <c r="E247" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H247" s="2" t="str">
+        <v>10.10000000000006</v>
+      </c>
+      <c r="F247" s="7">
+        <v>42</v>
+      </c>
+      <c r="G247" s="2">
+        <v>45</v>
+      </c>
+      <c r="H247" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>46253</v>
+      </c>
       <c r="C248" s="9">
         <f>_xlfn.XLOOKUP(Log!A248, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E248" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D248" s="9">
+        <v>0.46743055555555557</v>
+      </c>
+      <c r="E248" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H248" s="2" t="str">
+        <v>12.100000000000053</v>
+      </c>
+      <c r="F248" s="7">
+        <v>44</v>
+      </c>
+      <c r="G248" s="2">
+        <v>47</v>
+      </c>
+      <c r="H248" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>46253</v>
+      </c>
       <c r="C249" s="9">
         <f>_xlfn.XLOOKUP(Log!A249, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E249" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D249" s="9">
+        <v>0.46881944444444446</v>
+      </c>
+      <c r="E249" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H249" s="2" t="str">
+        <v>14.100000000000046</v>
+      </c>
+      <c r="F249" s="7">
+        <v>47</v>
+      </c>
+      <c r="G249" s="2">
+        <v>49</v>
+      </c>
+      <c r="H249" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>46253</v>
+      </c>
       <c r="C250" s="9">
         <f>_xlfn.XLOOKUP(Log!A250, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E250" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D250" s="9">
+        <v>0.47021990740740743</v>
+      </c>
+      <c r="E250" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H250" s="2" t="str">
+        <v>16.116666666666735</v>
+      </c>
+      <c r="F250" s="7">
+        <v>48</v>
+      </c>
+      <c r="G250" s="2">
+        <v>51</v>
+      </c>
+      <c r="H250" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>46253</v>
+      </c>
       <c r="C251" s="9">
         <f>_xlfn.XLOOKUP(Log!A251, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E251" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D251" s="9">
+        <v>0.47160879629629632</v>
+      </c>
+      <c r="E251" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H251" s="2" t="str">
+        <v>18.116666666666728</v>
+      </c>
+      <c r="F251" s="7">
+        <v>49</v>
+      </c>
+      <c r="G251" s="2">
+        <v>52</v>
+      </c>
+      <c r="H251" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>46253</v>
+      </c>
       <c r="C252" s="9">
         <f>_xlfn.XLOOKUP(Log!A252, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E252" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D252" s="9">
+        <v>0.4729976851851852</v>
+      </c>
+      <c r="E252" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H252" s="2" t="str">
+        <v>20.11666666666672</v>
+      </c>
+      <c r="F252" s="7">
+        <v>51</v>
+      </c>
+      <c r="G252" s="2">
+        <v>52</v>
+      </c>
+      <c r="H252" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>46253</v>
+      </c>
       <c r="C253" s="9">
         <f>_xlfn.XLOOKUP(Log!A253, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E253" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D253" s="9">
+        <v>0.47439814814814812</v>
+      </c>
+      <c r="E253" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H253" s="2" t="str">
+        <v>22.133333333333329</v>
+      </c>
+      <c r="F253" s="7">
+        <v>51</v>
+      </c>
+      <c r="G253" s="2">
+        <v>54</v>
+      </c>
+      <c r="H253" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>46253</v>
+      </c>
       <c r="C254" s="9">
         <f>_xlfn.XLOOKUP(Log!A254, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E254" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D254" s="9">
+        <v>0.47578703703703706</v>
+      </c>
+      <c r="E254" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H254" s="2" t="str">
+        <v>24.133333333333404</v>
+      </c>
+      <c r="F254" s="7">
+        <v>52</v>
+      </c>
+      <c r="G254" s="2">
+        <v>55</v>
+      </c>
+      <c r="H254" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>46253</v>
+      </c>
       <c r="C255" s="9">
         <f>_xlfn.XLOOKUP(Log!A255, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E255" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D255" s="9">
+        <v>0.47717592592592595</v>
+      </c>
+      <c r="E255" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H255" s="2" t="str">
+        <v>26.133333333333397</v>
+      </c>
+      <c r="F255" s="7">
+        <v>54</v>
+      </c>
+      <c r="G255" s="2">
+        <v>55</v>
+      </c>
+      <c r="H255" s="2">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>46253</v>
+      </c>
       <c r="C256" s="9">
         <f>_xlfn.XLOOKUP(Log!A256, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E256" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D256" s="9">
+        <v>0.47857638888888887</v>
+      </c>
+      <c r="E256" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H256" s="2" t="str">
+        <v>28.150000000000006</v>
+      </c>
+      <c r="F256" s="7">
+        <v>54</v>
+      </c>
+      <c r="G256" s="2">
+        <v>57</v>
+      </c>
+      <c r="H256" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>46253</v>
+      </c>
       <c r="C257" s="9">
         <f>_xlfn.XLOOKUP(Log!A257, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E257" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D257" s="9">
+        <v>0.47997685185185185</v>
+      </c>
+      <c r="E257" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H257" s="2" t="str">
+        <v>30.166666666666693</v>
+      </c>
+      <c r="F257" s="7">
+        <v>55</v>
+      </c>
+      <c r="G257" s="2">
+        <v>58</v>
+      </c>
+      <c r="H257" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>46253</v>
+      </c>
       <c r="C258" s="9">
         <f>_xlfn.XLOOKUP(Log!A258, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E258" s="6" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D258" s="9">
+        <v>0.48136574074074073</v>
+      </c>
+      <c r="E258" s="6">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="H258" s="2" t="str">
+        <v>32.166666666666686</v>
+      </c>
+      <c r="F258" s="7">
+        <v>55</v>
+      </c>
+      <c r="G258" s="2">
+        <v>58</v>
+      </c>
+      <c r="H258" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>46253</v>
+      </c>
       <c r="C259" s="9">
         <f>_xlfn.XLOOKUP(Log!A259, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E259" s="6" t="str">
-        <f t="shared" ref="E259:E322" si="8">IF(AND($D259&lt;&gt;"", $C259&lt;&gt;""), ($D259-$C259)*1440, "")</f>
-        <v/>
-      </c>
-      <c r="H259" s="2" t="str">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="D259" s="9">
+        <v>0.48276620370370371</v>
+      </c>
+      <c r="E259" s="6">
+        <f t="shared" si="6"/>
+        <v>34.183333333333373</v>
+      </c>
+      <c r="F259" s="7">
+        <v>55</v>
+      </c>
+      <c r="G259" s="2">
+        <v>58</v>
+      </c>
+      <c r="H259" s="2">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>46254</v>
+      </c>
       <c r="C260" s="9">
         <f>_xlfn.XLOOKUP(Log!A260, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E260" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H260" s="2" t="str">
-        <f t="shared" ref="H260:H288" si="9">IF(AND(G260&lt;&gt;"",F260&lt;&gt;""),G260-F260,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D260" s="9">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="E260" s="6">
+        <f t="shared" si="6"/>
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F260" s="7">
+        <v>28</v>
+      </c>
+      <c r="G260" s="2">
+        <v>31</v>
+      </c>
+      <c r="H260" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>46254</v>
+      </c>
       <c r="C261" s="9">
         <f>_xlfn.XLOOKUP(Log!A261, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E261" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H261" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D261" s="9">
+        <v>0.54432870370370368</v>
+      </c>
+      <c r="E261" s="6">
+        <f t="shared" si="6"/>
+        <v>2.8333333333333499</v>
+      </c>
+      <c r="F261" s="7">
+        <v>32</v>
+      </c>
+      <c r="G261" s="2">
+        <v>33</v>
+      </c>
+      <c r="H261" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="J261" s="17"/>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>46254</v>
+      </c>
       <c r="C262" s="9">
         <f>_xlfn.XLOOKUP(Log!A262, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E262" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H262" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D262" s="9">
+        <v>0.54571759259259256</v>
+      </c>
+      <c r="E262" s="6">
+        <f t="shared" si="6"/>
+        <v>4.8333333333333428</v>
+      </c>
+      <c r="F262" s="7">
+        <v>36</v>
+      </c>
+      <c r="G262" s="2">
+        <v>39</v>
+      </c>
+      <c r="H262" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>46254</v>
+      </c>
       <c r="C263" s="9">
         <f>_xlfn.XLOOKUP(Log!A263, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E263" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H263" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D263" s="9">
+        <v>0.54710648148148144</v>
+      </c>
+      <c r="E263" s="6">
+        <f t="shared" si="6"/>
+        <v>6.8333333333333357</v>
+      </c>
+      <c r="F263" s="7">
+        <v>39</v>
+      </c>
+      <c r="G263" s="2">
+        <v>42</v>
+      </c>
+      <c r="H263" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>46254</v>
+      </c>
       <c r="C264" s="9">
         <f>_xlfn.XLOOKUP(Log!A264, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E264" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H264" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D264" s="9">
+        <v>0.54849537037037033</v>
+      </c>
+      <c r="E264" s="6">
+        <f t="shared" si="6"/>
+        <v>8.8333333333333286</v>
+      </c>
+      <c r="F264" s="7">
+        <v>41</v>
+      </c>
+      <c r="G264" s="2">
+        <v>44</v>
+      </c>
+      <c r="H264" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>46254</v>
+      </c>
       <c r="C265" s="9">
         <f>_xlfn.XLOOKUP(Log!A265, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E265" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H265" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D265" s="9">
+        <v>0.54989583333333336</v>
+      </c>
+      <c r="E265" s="6">
+        <f t="shared" si="6"/>
+        <v>10.850000000000097</v>
+      </c>
+      <c r="F265" s="7">
+        <v>44</v>
+      </c>
+      <c r="G265" s="2">
+        <v>45</v>
+      </c>
+      <c r="H265" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>46254</v>
+      </c>
       <c r="C266" s="9">
         <f>_xlfn.XLOOKUP(Log!A266, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E266" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H266" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D266" s="9">
+        <v>0.55128472222222225</v>
+      </c>
+      <c r="E266" s="6">
+        <f t="shared" si="6"/>
+        <v>12.85000000000009</v>
+      </c>
+      <c r="F266" s="7">
+        <v>45</v>
+      </c>
+      <c r="G266" s="2">
+        <v>48</v>
+      </c>
+      <c r="H266" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>46254</v>
+      </c>
       <c r="C267" s="9">
         <f>_xlfn.XLOOKUP(Log!A267, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E267" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H267" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D267" s="9">
+        <v>0.55268518518518517</v>
+      </c>
+      <c r="E267" s="6">
+        <f t="shared" si="6"/>
+        <v>14.866666666666699</v>
+      </c>
+      <c r="F267" s="7">
+        <v>47</v>
+      </c>
+      <c r="G267" s="2">
+        <v>49</v>
+      </c>
+      <c r="H267" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>46254</v>
+      </c>
       <c r="C268" s="9">
         <f>_xlfn.XLOOKUP(Log!A268, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E268" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H268" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D268" s="9">
+        <v>0.55407407407407405</v>
+      </c>
+      <c r="E268" s="6">
+        <f t="shared" si="6"/>
+        <v>16.866666666666692</v>
+      </c>
+      <c r="F268" s="7">
+        <v>48</v>
+      </c>
+      <c r="G268" s="2">
+        <v>51</v>
+      </c>
+      <c r="H268" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>46254</v>
+      </c>
       <c r="C269" s="9">
         <f>_xlfn.XLOOKUP(Log!A269, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E269" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H269" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D269" s="9">
+        <v>0.55547453703703709</v>
+      </c>
+      <c r="E269" s="6">
+        <f t="shared" si="6"/>
+        <v>18.883333333333461</v>
+      </c>
+      <c r="F269" s="7">
+        <v>49</v>
+      </c>
+      <c r="G269" s="2">
+        <v>52</v>
+      </c>
+      <c r="H269" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>46254</v>
+      </c>
       <c r="C270" s="9">
         <f>_xlfn.XLOOKUP(Log!A270, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E270" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H270" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D270" s="9">
+        <v>0.55686342592592597</v>
+      </c>
+      <c r="E270" s="6">
+        <f t="shared" si="6"/>
+        <v>20.883333333333454</v>
+      </c>
+      <c r="F270" s="7">
+        <v>51</v>
+      </c>
+      <c r="G270" s="2">
+        <v>54</v>
+      </c>
+      <c r="H270" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>46254</v>
+      </c>
       <c r="C271" s="9">
         <f>_xlfn.XLOOKUP(Log!A271, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E271" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H271" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D271" s="9">
+        <v>0.55825231481481485</v>
+      </c>
+      <c r="E271" s="6">
+        <f t="shared" si="6"/>
+        <v>22.883333333333447</v>
+      </c>
+      <c r="F271" s="7">
+        <v>51</v>
+      </c>
+      <c r="G271" s="2">
+        <v>55</v>
+      </c>
+      <c r="H271" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>46254</v>
+      </c>
       <c r="C272" s="9">
         <f>_xlfn.XLOOKUP(Log!A272, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E272" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H272" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D272" s="9">
+        <v>0.55965277777777778</v>
+      </c>
+      <c r="E272" s="6">
+        <f t="shared" si="6"/>
+        <v>24.900000000000055</v>
+      </c>
+      <c r="F272" s="7">
+        <v>52</v>
+      </c>
+      <c r="G272" s="2">
+        <v>55</v>
+      </c>
+      <c r="H272" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A273" s="1">
+        <v>46254</v>
+      </c>
       <c r="C273" s="9">
         <f>_xlfn.XLOOKUP(Log!A273, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E273" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H273" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D273" s="9">
+        <v>0.56104166666666666</v>
+      </c>
+      <c r="E273" s="6">
+        <f t="shared" si="6"/>
+        <v>26.900000000000048</v>
+      </c>
+      <c r="F273" s="7">
+        <v>54</v>
+      </c>
+      <c r="G273" s="2">
+        <v>55</v>
+      </c>
+      <c r="H273" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A274" s="1">
+        <v>46254</v>
+      </c>
       <c r="C274" s="9">
         <f>_xlfn.XLOOKUP(Log!A274, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E274" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H274" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="3:8" x14ac:dyDescent="0.3">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D274" s="9">
+        <v>0.56243055555555554</v>
+      </c>
+      <c r="E274" s="6">
+        <f t="shared" ref="E274:E337" si="8">IF(AND($D274&lt;&gt;"", $C274&lt;&gt;""), ($D274-$C274)*1440, "")</f>
+        <v>28.900000000000041</v>
+      </c>
+      <c r="F274" s="7">
+        <v>54</v>
+      </c>
+      <c r="G274" s="2">
+        <v>57</v>
+      </c>
+      <c r="H274" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>46254</v>
+      </c>
       <c r="C275" s="9">
         <f>_xlfn.XLOOKUP(Log!A275, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E275" s="6" t="str">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="D275" s="9">
+        <v>0.56381944444444443</v>
+      </c>
+      <c r="E275" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H275" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="3:8" x14ac:dyDescent="0.3">
+        <v>30.900000000000034</v>
+      </c>
+      <c r="F275" s="7">
+        <v>54</v>
+      </c>
+      <c r="G275" s="2">
+        <v>58</v>
+      </c>
+      <c r="H275" s="2">
+        <f t="shared" ref="H275:H303" si="9">IF(AND(G275&lt;&gt;"",F275&lt;&gt;""),G275-F275,"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
+        <v>46255</v>
+      </c>
       <c r="C276" s="9">
         <f>_xlfn.XLOOKUP(Log!A276, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E276" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D276" s="9">
+        <v>0.59375</v>
+      </c>
+      <c r="E276" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H276" s="2" t="str">
+        <v>0.99999999999999645</v>
+      </c>
+      <c r="F276" s="7">
+        <v>29</v>
+      </c>
+      <c r="G276" s="2">
+        <v>31</v>
+      </c>
+      <c r="H276" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="3:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A277" s="1">
+        <v>46255</v>
+      </c>
       <c r="C277" s="9">
         <f>_xlfn.XLOOKUP(Log!A277, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E277" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D277" s="9">
+        <v>0.60334490740740743</v>
+      </c>
+      <c r="E277" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H277" s="2" t="str">
+        <v>14.816666666666691</v>
+      </c>
+      <c r="F277" s="7">
+        <v>48</v>
+      </c>
+      <c r="G277" s="2">
+        <v>49</v>
+      </c>
+      <c r="H277" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A278" s="1">
+        <v>46255</v>
+      </c>
       <c r="C278" s="9">
         <f>_xlfn.XLOOKUP(Log!A278, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E278" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D278" s="9">
+        <v>0.60473379629629631</v>
+      </c>
+      <c r="E278" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H278" s="2" t="str">
+        <v>16.816666666666684</v>
+      </c>
+      <c r="F278" s="7">
+        <v>49</v>
+      </c>
+      <c r="G278" s="2">
+        <v>52</v>
+      </c>
+      <c r="H278" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A279" s="1">
+        <v>46255</v>
+      </c>
       <c r="C279" s="9">
         <f>_xlfn.XLOOKUP(Log!A279, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E279" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D279" s="9">
+        <v>0.60612268518518519</v>
+      </c>
+      <c r="E279" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H279" s="2" t="str">
+        <v>18.816666666666677</v>
+      </c>
+      <c r="F279" s="7">
+        <v>51</v>
+      </c>
+      <c r="G279" s="2">
+        <v>52</v>
+      </c>
+      <c r="H279" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A280" s="1">
+        <v>46255</v>
+      </c>
       <c r="C280" s="9">
         <f>_xlfn.XLOOKUP(Log!A280, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E280" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D280" s="9">
+        <v>0.60752314814814812</v>
+      </c>
+      <c r="E280" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H280" s="2" t="str">
+        <v>20.833333333333286</v>
+      </c>
+      <c r="F280" s="7">
+        <v>51</v>
+      </c>
+      <c r="G280" s="2">
+        <v>52</v>
+      </c>
+      <c r="H280" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>46255</v>
+      </c>
       <c r="C281" s="9">
         <f>_xlfn.XLOOKUP(Log!A281, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E281" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D281" s="9">
+        <v>0.60892361111111115</v>
+      </c>
+      <c r="E281" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H281" s="2" t="str">
+        <v>22.850000000000055</v>
+      </c>
+      <c r="F281" s="7">
+        <v>52</v>
+      </c>
+      <c r="G281" s="2">
+        <v>55</v>
+      </c>
+      <c r="H281" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>46255</v>
+      </c>
       <c r="C282" s="9">
         <f>_xlfn.XLOOKUP(Log!A282, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E282" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D282" s="9">
+        <v>0.61031250000000004</v>
+      </c>
+      <c r="E282" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H282" s="2" t="str">
+        <v>24.850000000000048</v>
+      </c>
+      <c r="F282" s="7">
+        <v>54</v>
+      </c>
+      <c r="G282" s="2">
+        <v>55</v>
+      </c>
+      <c r="H282" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A283" s="1">
+        <v>46255</v>
+      </c>
       <c r="C283" s="9">
         <f>_xlfn.XLOOKUP(Log!A283, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E283" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D283" s="9">
+        <v>0.61171296296296296</v>
+      </c>
+      <c r="E283" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H283" s="2" t="str">
+        <v>26.866666666666656</v>
+      </c>
+      <c r="F283" s="7">
+        <v>54</v>
+      </c>
+      <c r="G283" s="2">
+        <v>55</v>
+      </c>
+      <c r="H283" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>46255</v>
+      </c>
       <c r="C284" s="9">
         <f>_xlfn.XLOOKUP(Log!A284, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E284" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D284" s="9">
+        <v>0.61311342592592588</v>
+      </c>
+      <c r="E284" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H284" s="2" t="str">
+        <v>28.883333333333265</v>
+      </c>
+      <c r="F284" s="7">
+        <v>54</v>
+      </c>
+      <c r="G284" s="2">
+        <v>55</v>
+      </c>
+      <c r="H284" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A285" s="1">
+        <v>46255</v>
+      </c>
       <c r="C285" s="9">
         <f>_xlfn.XLOOKUP(Log!A285, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E285" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D285" s="9">
+        <v>0.61450231481481477</v>
+      </c>
+      <c r="E285" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H285" s="2" t="str">
+        <v>30.883333333333258</v>
+      </c>
+      <c r="F285" s="7">
+        <v>54</v>
+      </c>
+      <c r="G285" s="2">
+        <v>58</v>
+      </c>
+      <c r="H285" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>46255</v>
+      </c>
       <c r="C286" s="9">
         <f>_xlfn.XLOOKUP(Log!A286, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E286" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D286" s="9">
+        <v>0.6159027777777778</v>
+      </c>
+      <c r="E286" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H286" s="2" t="str">
+        <v>32.900000000000027</v>
+      </c>
+      <c r="F286" s="7">
+        <v>55</v>
+      </c>
+      <c r="G286" s="2">
+        <v>58</v>
+      </c>
+      <c r="H286" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>46255</v>
+      </c>
       <c r="C287" s="9">
         <f>_xlfn.XLOOKUP(Log!A287, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E287" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D287" s="9">
+        <v>0.61730324074074072</v>
+      </c>
+      <c r="E287" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H287" s="2" t="str">
+        <v>34.916666666666636</v>
+      </c>
+      <c r="F287" s="7">
+        <v>57</v>
+      </c>
+      <c r="G287" s="2">
+        <v>58</v>
+      </c>
+      <c r="H287" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>46255</v>
+      </c>
       <c r="C288" s="9">
         <f>_xlfn.XLOOKUP(Log!A288, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E288" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D288" s="9">
+        <v>0.61870370370370376</v>
+      </c>
+      <c r="E288" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H288" s="2" t="str">
+        <v>36.933333333333408</v>
+      </c>
+      <c r="F288" s="7">
+        <v>57</v>
+      </c>
+      <c r="G288" s="2">
+        <v>58</v>
+      </c>
+      <c r="H288" s="2">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>46255</v>
+      </c>
       <c r="C289" s="9">
         <f>_xlfn.XLOOKUP(Log!A289, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E289" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D289" s="9">
+        <v>0.62009259259259264</v>
+      </c>
+      <c r="E289" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H289" s="2" t="str">
-        <f t="shared" ref="H289:H352" si="10">IF(AND(G289&lt;&gt;"",F289&lt;&gt;""),G289-F289,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="3:8" x14ac:dyDescent="0.3">
+        <v>38.933333333333394</v>
+      </c>
+      <c r="F289" s="7">
+        <v>57</v>
+      </c>
+      <c r="G289" s="2">
+        <v>58</v>
+      </c>
+      <c r="H289" s="2">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A290" s="1">
+        <v>46255</v>
+      </c>
       <c r="C290" s="9">
         <f>_xlfn.XLOOKUP(Log!A290, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E290" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D290" s="9">
+        <v>0.62149305555555556</v>
+      </c>
+      <c r="E290" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H290" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="3:8" x14ac:dyDescent="0.3">
+        <v>40.950000000000003</v>
+      </c>
+      <c r="F290" s="7">
+        <v>57</v>
+      </c>
+      <c r="G290" s="2">
+        <v>58</v>
+      </c>
+      <c r="H290" s="2">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>46255</v>
+      </c>
       <c r="C291" s="9">
         <f>_xlfn.XLOOKUP(Log!A291, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E291" s="6" t="str">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D291" s="9">
+        <v>0.62288194444444445</v>
+      </c>
+      <c r="E291" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H291" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="3:8" x14ac:dyDescent="0.3">
+        <v>42.95</v>
+      </c>
+      <c r="F291" s="7">
+        <v>57</v>
+      </c>
+      <c r="G291" s="2">
+        <v>61</v>
+      </c>
+      <c r="H291" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C292" s="9">
         <f>_xlfn.XLOOKUP(Log!A292, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10938,11 +11538,11 @@
         <v/>
       </c>
       <c r="H292" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C293" s="9">
         <f>_xlfn.XLOOKUP(Log!A293, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10952,11 +11552,11 @@
         <v/>
       </c>
       <c r="H293" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C294" s="9">
         <f>_xlfn.XLOOKUP(Log!A294, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10966,11 +11566,11 @@
         <v/>
       </c>
       <c r="H294" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C295" s="9">
         <f>_xlfn.XLOOKUP(Log!A295, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10980,11 +11580,11 @@
         <v/>
       </c>
       <c r="H295" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C296" s="9">
         <f>_xlfn.XLOOKUP(Log!A296, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -10994,11 +11594,11 @@
         <v/>
       </c>
       <c r="H296" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C297" s="9">
         <f>_xlfn.XLOOKUP(Log!A297, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11008,11 +11608,11 @@
         <v/>
       </c>
       <c r="H297" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C298" s="9">
         <f>_xlfn.XLOOKUP(Log!A298, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11022,11 +11622,11 @@
         <v/>
       </c>
       <c r="H298" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C299" s="9">
         <f>_xlfn.XLOOKUP(Log!A299, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11036,11 +11636,11 @@
         <v/>
       </c>
       <c r="H299" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C300" s="9">
         <f>_xlfn.XLOOKUP(Log!A300, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11050,11 +11650,11 @@
         <v/>
       </c>
       <c r="H300" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C301" s="9">
         <f>_xlfn.XLOOKUP(Log!A301, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11064,11 +11664,11 @@
         <v/>
       </c>
       <c r="H301" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C302" s="9">
         <f>_xlfn.XLOOKUP(Log!A302, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11078,11 +11678,11 @@
         <v/>
       </c>
       <c r="H302" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C303" s="9">
         <f>_xlfn.XLOOKUP(Log!A303, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11092,11 +11692,11 @@
         <v/>
       </c>
       <c r="H303" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="3:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C304" s="9">
         <f>_xlfn.XLOOKUP(Log!A304, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11106,7 +11706,7 @@
         <v/>
       </c>
       <c r="H304" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H304:H367" si="10">IF(AND(G304&lt;&gt;"",F304&lt;&gt;""),G304-F304,"")</f>
         <v/>
       </c>
     </row>
@@ -11368,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="E323" s="6" t="str">
-        <f t="shared" ref="E323:E386" si="11">IF(AND($D323&lt;&gt;"", $C323&lt;&gt;""), ($D323-$C323)*1440, "")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H323" s="2" t="str">
@@ -11382,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="E324" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H324" s="2" t="str">
@@ -11396,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="E325" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H325" s="2" t="str">
@@ -11410,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="E326" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H326" s="2" t="str">
@@ -11424,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="E327" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H327" s="2" t="str">
@@ -11438,7 +12038,7 @@
         <v>0</v>
       </c>
       <c r="E328" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H328" s="2" t="str">
@@ -11452,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="E329" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H329" s="2" t="str">
@@ -11466,7 +12066,7 @@
         <v>0</v>
       </c>
       <c r="E330" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H330" s="2" t="str">
@@ -11480,7 +12080,7 @@
         <v>0</v>
       </c>
       <c r="E331" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H331" s="2" t="str">
@@ -11494,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="E332" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H332" s="2" t="str">
@@ -11508,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="E333" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H333" s="2" t="str">
@@ -11522,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="E334" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H334" s="2" t="str">
@@ -11536,7 +12136,7 @@
         <v>0</v>
       </c>
       <c r="E335" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H335" s="2" t="str">
@@ -11550,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="E336" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H336" s="2" t="str">
@@ -11564,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="E337" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="H337" s="2" t="str">
@@ -11578,7 +12178,7 @@
         <v>0</v>
       </c>
       <c r="E338" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="E338:E401" si="11">IF(AND($D338&lt;&gt;"", $C338&lt;&gt;""), ($D338-$C338)*1440, "")</f>
         <v/>
       </c>
       <c r="H338" s="2" t="str">
@@ -11792,7 +12392,7 @@
         <v/>
       </c>
       <c r="H353" s="2" t="str">
-        <f t="shared" ref="H353:H375" si="12">IF(AND(G353&lt;&gt;"",F353&lt;&gt;""),G353-F353,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11806,7 +12406,7 @@
         <v/>
       </c>
       <c r="H354" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11820,7 +12420,7 @@
         <v/>
       </c>
       <c r="H355" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11834,7 +12434,7 @@
         <v/>
       </c>
       <c r="H356" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11848,7 +12448,7 @@
         <v/>
       </c>
       <c r="H357" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11862,7 +12462,7 @@
         <v/>
       </c>
       <c r="H358" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11876,7 +12476,7 @@
         <v/>
       </c>
       <c r="H359" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11890,7 +12490,7 @@
         <v/>
       </c>
       <c r="H360" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11904,7 +12504,7 @@
         <v/>
       </c>
       <c r="H361" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11918,7 +12518,7 @@
         <v/>
       </c>
       <c r="H362" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11932,7 +12532,7 @@
         <v/>
       </c>
       <c r="H363" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11946,7 +12546,7 @@
         <v/>
       </c>
       <c r="H364" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11960,7 +12560,7 @@
         <v/>
       </c>
       <c r="H365" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11974,7 +12574,7 @@
         <v/>
       </c>
       <c r="H366" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11988,7 +12588,7 @@
         <v/>
       </c>
       <c r="H367" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -12002,7 +12602,7 @@
         <v/>
       </c>
       <c r="H368" s="2" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="H368:H390" si="12">IF(AND(G368&lt;&gt;"",F368&lt;&gt;""),G368-F368,"")</f>
         <v/>
       </c>
     </row>
@@ -12113,6 +12713,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H376" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="377" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C377" s="9">
@@ -12123,6 +12727,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H377" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="378" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C378" s="9">
@@ -12133,6 +12741,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H378" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="379" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C379" s="9">
@@ -12143,6 +12755,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H379" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="380" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C380" s="9">
@@ -12153,6 +12769,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H380" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="381" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C381" s="9">
@@ -12163,6 +12783,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H381" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="382" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C382" s="9">
@@ -12173,6 +12797,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H382" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="383" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C383" s="9">
@@ -12183,6 +12811,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
+      <c r="H383" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
     </row>
     <row r="384" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C384" s="9">
@@ -12193,8 +12825,12 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-    </row>
-    <row r="385" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="H384" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="385" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C385" s="9">
         <f>_xlfn.XLOOKUP(Log!A385, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -12203,8 +12839,12 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-    </row>
-    <row r="386" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="H385" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="386" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C386" s="9">
         <f>_xlfn.XLOOKUP(Log!A386, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -12213,144 +12853,164 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-    </row>
-    <row r="387" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="H386" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="387" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C387" s="9">
         <f>_xlfn.XLOOKUP(Log!A387, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E387" s="6" t="str">
-        <f t="shared" ref="E387:E450" si="13">IF(AND($D387&lt;&gt;"", $C387&lt;&gt;""), ($D387-$C387)*1440, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="388" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H387" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="388" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C388" s="9">
         <f>_xlfn.XLOOKUP(Log!A388, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E388" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="389" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H388" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="389" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C389" s="9">
         <f>_xlfn.XLOOKUP(Log!A389, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E389" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="390" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H389" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="390" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C390" s="9">
         <f>_xlfn.XLOOKUP(Log!A390, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E390" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="391" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H390" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="391" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C391" s="9">
         <f>_xlfn.XLOOKUP(Log!A391, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E391" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="392" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C392" s="9">
         <f>_xlfn.XLOOKUP(Log!A392, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E392" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="393" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="393" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C393" s="9">
         <f>_xlfn.XLOOKUP(Log!A393, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E393" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="394" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="394" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C394" s="9">
         <f>_xlfn.XLOOKUP(Log!A394, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E394" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="395" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="395" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C395" s="9">
         <f>_xlfn.XLOOKUP(Log!A395, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E395" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="396" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="396" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C396" s="9">
         <f>_xlfn.XLOOKUP(Log!A396, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E396" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="397" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="397" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C397" s="9">
         <f>_xlfn.XLOOKUP(Log!A397, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E397" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="398" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="398" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C398" s="9">
         <f>_xlfn.XLOOKUP(Log!A398, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E398" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="399" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="399" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C399" s="9">
         <f>_xlfn.XLOOKUP(Log!A399, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E399" s="6" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="400" spans="3:5" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="400" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C400" s="9">
         <f>_xlfn.XLOOKUP(Log!A400, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
       </c>
       <c r="E400" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -12360,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="E401" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -12370,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="E402" s="6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="E402:E465" si="13">IF(AND($D402&lt;&gt;"", $C402&lt;&gt;""), ($D402-$C402)*1440, "")</f>
         <v/>
       </c>
     </row>
@@ -12860,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="E451" s="6" t="str">
-        <f t="shared" ref="E451:E514" si="14">IF(AND($D451&lt;&gt;"", $C451&lt;&gt;""), ($D451-$C451)*1440, "")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12870,7 +13530,7 @@
         <v>0</v>
       </c>
       <c r="E452" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12880,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="E453" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12890,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="E454" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12900,7 +13560,7 @@
         <v>0</v>
       </c>
       <c r="E455" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12910,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="E456" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12920,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="E457" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12930,7 +13590,7 @@
         <v>0</v>
       </c>
       <c r="E458" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12940,7 +13600,7 @@
         <v>0</v>
       </c>
       <c r="E459" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12950,7 +13610,7 @@
         <v>0</v>
       </c>
       <c r="E460" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12960,7 +13620,7 @@
         <v>0</v>
       </c>
       <c r="E461" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12970,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="E462" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12980,7 +13640,7 @@
         <v>0</v>
       </c>
       <c r="E463" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12990,7 +13650,7 @@
         <v>0</v>
       </c>
       <c r="E464" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -13000,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="E465" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -13010,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="E466" s="6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="E466:E529" si="14">IF(AND($D466&lt;&gt;"", $C466&lt;&gt;""), ($D466-$C466)*1440, "")</f>
         <v/>
       </c>
     </row>
@@ -13255,132 +13915,192 @@
       </c>
     </row>
     <row r="491" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C491" s="9">
+        <f>_xlfn.XLOOKUP(Log!A491, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E491" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C492" s="9">
+        <f>_xlfn.XLOOKUP(Log!A492, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E492" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C493" s="9">
+        <f>_xlfn.XLOOKUP(Log!A493, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E493" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C494" s="9">
+        <f>_xlfn.XLOOKUP(Log!A494, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E494" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C495" s="9">
+        <f>_xlfn.XLOOKUP(Log!A495, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E495" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C496" s="9">
+        <f>_xlfn.XLOOKUP(Log!A496, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E496" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="497" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C497" s="9">
+        <f>_xlfn.XLOOKUP(Log!A497, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E497" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="498" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C498" s="9">
+        <f>_xlfn.XLOOKUP(Log!A498, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E498" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="499" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C499" s="9">
+        <f>_xlfn.XLOOKUP(Log!A499, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E499" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="500" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C500" s="9">
+        <f>_xlfn.XLOOKUP(Log!A500, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E500" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="501" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C501" s="9">
+        <f>_xlfn.XLOOKUP(Log!A501, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E501" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="502" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C502" s="9">
+        <f>_xlfn.XLOOKUP(Log!A502, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E502" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="503" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C503" s="9">
+        <f>_xlfn.XLOOKUP(Log!A503, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E503" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="504" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C504" s="9">
+        <f>_xlfn.XLOOKUP(Log!A504, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E504" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="505" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C505" s="9">
+        <f>_xlfn.XLOOKUP(Log!A505, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
+        <v>0</v>
+      </c>
       <c r="E505" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="506" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E506" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="507" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E507" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="508" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E508" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="509" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E509" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="510" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E510" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="511" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E511" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
-    <row r="512" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E512" s="6" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -13400,97 +14120,97 @@
     </row>
     <row r="515" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E515" s="6" t="str">
-        <f t="shared" ref="E515:E578" si="15">IF(AND($D515&lt;&gt;"", $C515&lt;&gt;""), ($D515-$C515)*1440, "")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E516" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E517" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E518" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E519" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E520" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E521" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E522" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E523" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E524" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E525" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E526" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E527" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E528" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E529" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E530" s="6" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="E530:E593" si="15">IF(AND($D530&lt;&gt;"", $C530&lt;&gt;""), ($D530-$C530)*1440, "")</f>
         <v/>
       </c>
     </row>
@@ -13784,97 +14504,97 @@
     </row>
     <row r="579" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E579" s="6" t="str">
-        <f t="shared" ref="E579:E642" si="16">IF(AND($D579&lt;&gt;"", $C579&lt;&gt;""), ($D579-$C579)*1440, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E580" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E581" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E582" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E583" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E584" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E585" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E586" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E587" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E588" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E589" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E590" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E591" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E592" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E593" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E594" s="6" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="E594:E657" si="16">IF(AND($D594&lt;&gt;"", $C594&lt;&gt;""), ($D594-$C594)*1440, "")</f>
         <v/>
       </c>
     </row>
@@ -14168,97 +14888,97 @@
     </row>
     <row r="643" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E643" s="6" t="str">
-        <f t="shared" ref="E643:E685" si="17">IF(AND($D643&lt;&gt;"", $C643&lt;&gt;""), ($D643-$C643)*1440, "")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E644" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E645" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E646" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E647" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E648" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E649" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E650" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E651" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E652" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E653" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E654" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E655" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E656" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E657" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E658" s="6" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="E658:E700" si="17">IF(AND($D658&lt;&gt;"", $C658&lt;&gt;""), ($D658-$C658)*1440, "")</f>
         <v/>
       </c>
     </row>
@@ -14420,6 +15140,96 @@
     </row>
     <row r="685" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E685" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="686" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E686" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="687" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E687" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="688" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E688" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="689" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E689" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="690" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E690" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="691" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E691" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="692" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E692" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="693" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E693" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="694" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E694" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="695" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E695" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="696" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E696" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="697" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E697" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="698" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E698" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="699" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E699" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+    </row>
+    <row r="700" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E700" s="6" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -14430,17 +15240,17 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="D3:XFD3 D4:G196 H4:H211 D197:F211 D212:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 I4:XFD32 I33:L40 O33:XFD40 I41:XFD44 J45:XFD45 I46:XFD211 G198:G211 A2:C1048576">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H3 A4:G196 H4:H211 A197:F211 A212:H9999">
-    <cfRule type="expression" dxfId="4" priority="1">
+  <conditionalFormatting sqref="A3:H3 A4:G196 H4:H211 A197:F211 A212:H10014">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B3&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G198:G211">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>$B197&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14499,7 +15309,7 @@
         <v>0.78819444444444442</v>
       </c>
       <c r="E2" s="25">
-        <f>IF(AND(D2&lt;&gt;"", C2&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B2,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B2,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D2&lt;&gt;"", C2&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B2,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B2,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>25.000000000000071</v>
       </c>
     </row>
@@ -14513,7 +15323,7 @@
         <v>46229</v>
       </c>
       <c r="E3" s="25" t="str">
-        <f>IF(AND(D3&lt;&gt;"", C3&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B3,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B3,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D3&lt;&gt;"", C3&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B3,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B3,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -14533,7 +15343,7 @@
         <v>0.42916666666666659</v>
       </c>
       <c r="E4" s="25">
-        <f>IF(AND(D4&lt;&gt;"", C4&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B4,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B4,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D4&lt;&gt;"", C4&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B4,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B4,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>24.000000000000234</v>
       </c>
     </row>
@@ -14553,7 +15363,7 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="E5" s="25">
-        <f>IF(AND(D5&lt;&gt;"", C5&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B5,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B5,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D5&lt;&gt;"", C5&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B5,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B5,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>26.000000000000068</v>
       </c>
     </row>
@@ -14571,7 +15381,7 @@
         <v>0.73472222222222228</v>
       </c>
       <c r="E6" s="25">
-        <f>IF(AND(D6&lt;&gt;"", C6&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D6&lt;&gt;"", C6&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B6,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B6,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>15.999999999999943</v>
       </c>
       <c r="F6" s="15" t="s">
@@ -14594,7 +15404,7 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="E7" s="25">
-        <f>IF(AND(D7&lt;&gt;"", C7&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D7&lt;&gt;"", C7&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B7,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B7,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>19.000000000000014</v>
       </c>
       <c r="F7" s="15" t="s">
@@ -14617,7 +15427,7 @@
         <v>0.43055555555555558</v>
       </c>
       <c r="E8" s="25">
-        <f>IF(AND(D8&lt;&gt;"", C8&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D8&lt;&gt;"", C8&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B8,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B8,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>20.999999999999925</v>
       </c>
       <c r="F8" s="15" t="s">
@@ -14638,7 +15448,7 @@
         <v>0.70625000000000004</v>
       </c>
       <c r="E9" s="25">
-        <f>IF(AND(D9&lt;&gt;"", C9&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D9&lt;&gt;"", C9&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B9,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B9,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>21.583333333333243</v>
       </c>
       <c r="F9" s="27" t="s">
@@ -14659,7 +15469,7 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="E10" s="25">
-        <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B10,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B10,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>21.216666666666654</v>
       </c>
     </row>
@@ -14677,7 +15487,7 @@
         <v>0.42986111111111114</v>
       </c>
       <c r="E11" s="25">
-        <f>IF(AND(D11&lt;&gt;"", C11&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D11&lt;&gt;"", C11&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B11,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B11,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>21.066666666666627</v>
       </c>
       <c r="F11" s="15" t="s">
@@ -14698,7 +15508,7 @@
         <v>0.48333333333333334</v>
       </c>
       <c r="E12" s="25">
-        <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B12,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B12,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>19.600000000000026</v>
       </c>
       <c r="F12" s="15" t="s">
@@ -14719,7 +15529,7 @@
         <v>0.43888888888888888</v>
       </c>
       <c r="E13" s="25">
-        <f>IF(AND(D13&lt;&gt;"", C13&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D13&lt;&gt;"", C13&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B13,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B13,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>20.133333333333336</v>
       </c>
     </row>
@@ -14737,7 +15547,7 @@
         <v>0.55833333333333335</v>
       </c>
       <c r="E14" s="25">
-        <f>IF(AND(D14&lt;&gt;"", C14&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D14&lt;&gt;"", C14&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B14,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B14,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>19.616666666666642</v>
       </c>
     </row>
@@ -14755,7 +15565,7 @@
         <v>0.44374999999999998</v>
       </c>
       <c r="E15" s="25">
-        <f>IF(AND(D15&lt;&gt;"", C15&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D15&lt;&gt;"", C15&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B15,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B15,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>18.850000000000069</v>
       </c>
       <c r="F15" s="15" t="s">
@@ -14776,14 +15586,14 @@
         <v>0.38194444444444442</v>
       </c>
       <c r="E16" s="25">
-        <f>IF(AND(D16&lt;&gt;"", C16&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D16&lt;&gt;"", C16&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B16,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B16,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>21.350000000000058</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46246</v>
       </c>
@@ -14797,11 +15607,11 @@
         <v>0.41597222222222224</v>
       </c>
       <c r="E17" s="25">
-        <f>IF(AND(D17&lt;&gt;"", C17&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D17&lt;&gt;"", C17&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B17,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B17,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>21.449999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46247</v>
       </c>
@@ -14815,11 +15625,11 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="E18" s="25">
-        <f>IF(AND(D18&lt;&gt;"", C18&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D18&lt;&gt;"", C18&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B18,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B18,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>19.000000000000014</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46248</v>
       </c>
@@ -14833,11 +15643,11 @@
         <v>0.43472222222222223</v>
       </c>
       <c r="E19" s="25">
-        <f>IF(AND(D19&lt;&gt;"", C19&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D19&lt;&gt;"", C19&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B19,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B19,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46251</v>
       </c>
@@ -14851,11 +15661,11 @@
         <v>0.55902777777777779</v>
       </c>
       <c r="E20" s="25">
-        <f>IF(AND(D20&lt;&gt;"", C20&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D20&lt;&gt;"", C20&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B20,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B20,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>21.483333333333388</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46252</v>
       </c>
@@ -14869,11 +15679,11 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="E21" s="25">
-        <f>IF(AND(D21&lt;&gt;"", C21&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D21&lt;&gt;"", C21&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B21,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B21,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>19.63333333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46253</v>
       </c>
@@ -14886,88 +15696,111 @@
       <c r="D22" s="8">
         <v>0.45902777777777776</v>
       </c>
-      <c r="E22" s="25" t="str">
-        <f>IF(AND(D22&lt;&gt;"", C22&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v>–</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="E23" s="25" t="str">
-        <f>IF(AND(D23&lt;&gt;"", C23&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B23,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B23,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="E24" s="25" t="str">
-        <f>IF(AND(D24&lt;&gt;"", C24&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B24,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B24,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E22" s="25">
+        <f>IF(AND(D22&lt;&gt;"", C22&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B22,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B22,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v>20.11666666666672</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C23" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E23" s="25">
+        <f>IF(AND(D23&lt;&gt;"", C23&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B23,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B23,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v>20.883333333333454</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46255</v>
+      </c>
+      <c r="C24" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="E24" s="25">
+        <f>IF(AND(D24&lt;&gt;"", C24&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B24,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B24,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v>18.816666666666677</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="E25" s="25" t="str">
-        <f>IF(AND(D25&lt;&gt;"", C25&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B25,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B25,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <f>IF(AND(D25&lt;&gt;"", C25&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B25,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B25,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="E26" s="25" t="str">
-        <f>IF(AND(D26&lt;&gt;"", C26&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B26,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B26,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <f>IF(AND(D26&lt;&gt;"", C26&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B26,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B26,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="E27" s="25" t="str">
-        <f>IF(AND(D27&lt;&gt;"", C27&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B27,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B27,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <f>IF(AND(D27&lt;&gt;"", C27&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B27,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B27,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="E28" s="25" t="str">
-        <f>IF(AND(D28&lt;&gt;"", C28&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B28,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B28,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <f>IF(AND(D28&lt;&gt;"", C28&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B28,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B28,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="E29" s="25" t="str">
-        <f>IF(AND(D29&lt;&gt;"", C29&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B29,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B29,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <f>IF(AND(D29&lt;&gt;"", C29&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B29,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B29,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="E30" s="25" t="str">
-        <f>IF(AND(D30&lt;&gt;"", C30&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B30,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B30,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <f>IF(AND(D30&lt;&gt;"", C30&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B30,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B30,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="E31" s="25" t="str">
-        <f>IF(AND(D31&lt;&gt;"", C31&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B31,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B31,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <f>IF(AND(D31&lt;&gt;"", C31&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B31,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B31,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="E32" s="25" t="str">
-        <f>IF(AND(D32&lt;&gt;"", C32&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B32,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B32,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D32&lt;&gt;"", C32&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B32,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B32,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -14975,7 +15808,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="E33" s="25" t="str">
-        <f>IF(AND(D33&lt;&gt;"", C33&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B33,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B33,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D33&lt;&gt;"", C33&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B33,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B33,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -14983,7 +15816,7 @@
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="E34" s="25" t="str">
-        <f>IF(AND(D34&lt;&gt;"", C34&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B34,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B34,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D34&lt;&gt;"", C34&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B34,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B34,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -14991,7 +15824,7 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="E35" s="25" t="str">
-        <f>IF(AND(D35&lt;&gt;"", C35&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B35,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B35,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D35&lt;&gt;"", C35&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B35,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B35,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -14999,7 +15832,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="E36" s="25" t="str">
-        <f>IF(AND(D36&lt;&gt;"", C36&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B36,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B36,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D36&lt;&gt;"", C36&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B36,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B36,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15007,7 +15840,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="E37" s="25" t="str">
-        <f>IF(AND(D37&lt;&gt;"", C37&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B37,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B37,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D37&lt;&gt;"", C37&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B37,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B37,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15015,7 +15848,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="E38" s="25" t="str">
-        <f>IF(AND(D38&lt;&gt;"", C38&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B38,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B38,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D38&lt;&gt;"", C38&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B38,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B38,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15023,7 +15856,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="E39" s="25" t="str">
-        <f>IF(AND(D39&lt;&gt;"", C39&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B39,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B39,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D39&lt;&gt;"", C39&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B39,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B39,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15031,7 +15864,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="E40" s="25" t="str">
-        <f>IF(AND(D40&lt;&gt;"", C40&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B40,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B40,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D40&lt;&gt;"", C40&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B40,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B40,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15039,7 +15872,7 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="E41" s="25" t="str">
-        <f>IF(AND(D41&lt;&gt;"", C41&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B41,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B41,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D41&lt;&gt;"", C41&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B41,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B41,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15047,7 +15880,7 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="E42" s="25" t="str">
-        <f>IF(AND(D42&lt;&gt;"", C42&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B42,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B42,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D42&lt;&gt;"", C42&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B42,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B42,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15055,7 +15888,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="E43" s="25" t="str">
-        <f>IF(AND(D43&lt;&gt;"", C43&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B43,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B43,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D43&lt;&gt;"", C43&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B43,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B43,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15063,7 +15896,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="E44" s="25" t="str">
-        <f>IF(AND(D44&lt;&gt;"", C44&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B44,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B44,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D44&lt;&gt;"", C44&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B44,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B44,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15071,7 +15904,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="E45" s="25" t="str">
-        <f>IF(AND(D45&lt;&gt;"", C45&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B45,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B45,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D45&lt;&gt;"", C45&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B45,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B45,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15079,7 +15912,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="E46" s="25" t="str">
-        <f>IF(AND(D46&lt;&gt;"", C46&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B46,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B46,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D46&lt;&gt;"", C46&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B46,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B46,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15087,7 +15920,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="E47" s="25" t="str">
-        <f>IF(AND(D47&lt;&gt;"", C47&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B47,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B47,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D47&lt;&gt;"", C47&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B47,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B47,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15095,7 +15928,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="E48" s="25" t="str">
-        <f>IF(AND(D48&lt;&gt;"", C48&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B48,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B48,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D48&lt;&gt;"", C48&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B48,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B48,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15103,7 +15936,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="E49" s="25" t="str">
-        <f>IF(AND(D49&lt;&gt;"", C49&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B49,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B49,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D49&lt;&gt;"", C49&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B49,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B49,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15111,7 +15944,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="E50" s="25" t="str">
-        <f>IF(AND(D50&lt;&gt;"", C50&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B50,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B50,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D50&lt;&gt;"", C50&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B50,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B50,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15119,7 +15952,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="E51" s="25" t="str">
-        <f>IF(AND(D51&lt;&gt;"", C51&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B51,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B51,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D51&lt;&gt;"", C51&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B51,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B51,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15127,7 +15960,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="E52" s="25" t="str">
-        <f>IF(AND(D52&lt;&gt;"", C52&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B52,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B52,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D52&lt;&gt;"", C52&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B52,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B52,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15135,7 +15968,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="E53" s="25" t="str">
-        <f>IF(AND(D53&lt;&gt;"", C53&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B53,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B53,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D53&lt;&gt;"", C53&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B53,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B53,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15143,7 +15976,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="E54" s="25" t="str">
-        <f>IF(AND(D54&lt;&gt;"", C54&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B54,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B54,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D54&lt;&gt;"", C54&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B54,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B54,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15151,7 +15984,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="E55" s="25" t="str">
-        <f>IF(AND(D55&lt;&gt;"", C55&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B55,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B55,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D55&lt;&gt;"", C55&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B55,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B55,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15159,7 +15992,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="E56" s="25" t="str">
-        <f>IF(AND(D56&lt;&gt;"", C56&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B56,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B56,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D56&lt;&gt;"", C56&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B56,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B56,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15167,259 +16000,259 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="E57" s="25" t="str">
-        <f>IF(AND(D57&lt;&gt;"", C57&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B57,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B57,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D57&lt;&gt;"", C57&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B57,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B57,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E58" s="25" t="str">
-        <f>IF(AND(D58&lt;&gt;"", C58&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D58&lt;&gt;"", C58&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B58,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B58,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E59" s="25" t="str">
-        <f>IF(AND(D59&lt;&gt;"", C59&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B59,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B59,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D59&lt;&gt;"", C59&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B59,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B59,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E60" s="25" t="str">
-        <f>IF(AND(D60&lt;&gt;"", C60&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B60,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B60,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D60&lt;&gt;"", C60&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B60,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B60,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E61" s="25" t="str">
-        <f>IF(AND(D61&lt;&gt;"", C61&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B61,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B61,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D61&lt;&gt;"", C61&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B61,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B61,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E62" s="25" t="str">
-        <f>IF(AND(D62&lt;&gt;"", C62&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B62,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B62,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D62&lt;&gt;"", C62&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B62,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B62,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E63" s="25" t="str">
-        <f>IF(AND(D63&lt;&gt;"", C63&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B63,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B63,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D63&lt;&gt;"", C63&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B63,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B63,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E64" s="25" t="str">
-        <f>IF(AND(D64&lt;&gt;"", C64&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B64,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B64,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D64&lt;&gt;"", C64&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B64,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B64,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="65" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E65" s="25" t="str">
-        <f>IF(AND(D65&lt;&gt;"", C65&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B65,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B65,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D65&lt;&gt;"", C65&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B65,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B65,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="66" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E66" s="25" t="str">
-        <f>IF(AND(D66&lt;&gt;"", C66&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B66,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B66,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D66&lt;&gt;"", C66&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B66,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B66,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="67" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E67" s="25" t="str">
-        <f>IF(AND(D67&lt;&gt;"", C67&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B67,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B67,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D67&lt;&gt;"", C67&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B67,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B67,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="68" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E68" s="25" t="str">
-        <f>IF(AND(D68&lt;&gt;"", C68&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B68,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B68,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D68&lt;&gt;"", C68&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B68,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B68,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="69" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E69" s="25" t="str">
-        <f>IF(AND(D69&lt;&gt;"", C69&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B69,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B69,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D69&lt;&gt;"", C69&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B69,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B69,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="70" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E70" s="25" t="str">
-        <f>IF(AND(D70&lt;&gt;"", C70&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B70,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B70,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D70&lt;&gt;"", C70&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B70,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B70,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="71" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E71" s="25" t="str">
-        <f>IF(AND(D71&lt;&gt;"", C71&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B71,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B71,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D71&lt;&gt;"", C71&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B71,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B71,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="72" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E72" s="25" t="str">
-        <f>IF(AND(D72&lt;&gt;"", C72&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B72,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B72,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D72&lt;&gt;"", C72&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B72,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B72,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="73" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E73" s="25" t="str">
-        <f>IF(AND(D73&lt;&gt;"", C73&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B73,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B73,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D73&lt;&gt;"", C73&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B73,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B73,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="74" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E74" s="25" t="str">
-        <f>IF(AND(D74&lt;&gt;"", C74&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B74,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B74,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D74&lt;&gt;"", C74&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B74,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B74,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="75" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E75" s="25" t="str">
-        <f>IF(AND(D75&lt;&gt;"", C75&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B75,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B75,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D75&lt;&gt;"", C75&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B75,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B75,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="76" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E76" s="25" t="str">
-        <f>IF(AND(D76&lt;&gt;"", C76&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B76,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B76,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D76&lt;&gt;"", C76&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B76,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B76,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="77" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E77" s="25" t="str">
-        <f>IF(AND(D77&lt;&gt;"", C77&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B77,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B77,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D77&lt;&gt;"", C77&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B77,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B77,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="78" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E78" s="25" t="str">
-        <f>IF(AND(D78&lt;&gt;"", C78&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B78,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B78,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D78&lt;&gt;"", C78&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B78,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B78,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="79" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E79" s="25" t="str">
-        <f>IF(AND(D79&lt;&gt;"", C79&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B79,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B79,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D79&lt;&gt;"", C79&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B79,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B79,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="80" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E80" s="25" t="str">
-        <f>IF(AND(D80&lt;&gt;"", C80&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B80,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B80,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D80&lt;&gt;"", C80&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B80,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B80,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="81" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E81" s="25" t="str">
-        <f>IF(AND(D81&lt;&gt;"", C81&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B81,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B81,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D81&lt;&gt;"", C81&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B81,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B81,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="82" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E82" s="25" t="str">
-        <f>IF(AND(D82&lt;&gt;"", C82&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B82,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B82,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D82&lt;&gt;"", C82&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B82,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B82,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="83" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E83" s="25" t="str">
-        <f>IF(AND(D83&lt;&gt;"", C83&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B83,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B83,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D83&lt;&gt;"", C83&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B83,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B83,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="84" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E84" s="25" t="str">
-        <f>IF(AND(D84&lt;&gt;"", C84&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B84,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B84,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D84&lt;&gt;"", C84&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B84,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B84,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="85" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E85" s="25" t="str">
-        <f>IF(AND(D85&lt;&gt;"", C85&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B85,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B85,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D85&lt;&gt;"", C85&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B85,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B85,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="86" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E86" s="25" t="str">
-        <f>IF(AND(D86&lt;&gt;"", C86&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B86,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B86,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D86&lt;&gt;"", C86&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B86,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B86,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="87" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E87" s="25" t="str">
-        <f>IF(AND(D87&lt;&gt;"", C87&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B87,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B87,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D87&lt;&gt;"", C87&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B87,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B87,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="88" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E88" s="25" t="str">
-        <f>IF(AND(D88&lt;&gt;"", C88&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B88,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B88,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D88&lt;&gt;"", C88&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B88,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B88,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="89" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E89" s="25" t="str">
-        <f>IF(AND(D89&lt;&gt;"", C89&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B89,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B89,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D89&lt;&gt;"", C89&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B89,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B89,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="90" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E90" s="25" t="str">
-        <f>IF(AND(D90&lt;&gt;"", C90&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B90,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B90,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D90&lt;&gt;"", C90&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B90,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B90,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="91" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E91" s="25" t="str">
-        <f>IF(AND(D91&lt;&gt;"", C91&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B91,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B91,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D91&lt;&gt;"", C91&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B91,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B91,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="92" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E92" s="25" t="str">
-        <f>IF(AND(D92&lt;&gt;"", C92&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B92,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B92,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D92&lt;&gt;"", C92&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B92,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B92,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="93" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E93" s="25" t="str">
-        <f>IF(AND(D93&lt;&gt;"", C93&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B93,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B93,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D93&lt;&gt;"", C93&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B93,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B93,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="94" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E94" s="25" t="str">
-        <f>IF(AND(D94&lt;&gt;"", C94&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B94,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B94,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D94&lt;&gt;"", C94&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B94,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B94,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="95" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E95" s="25" t="str">
-        <f>IF(AND(D95&lt;&gt;"", C95&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B95,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B95,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D95&lt;&gt;"", C95&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B95,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B95,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="96" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E96" s="25" t="str">
-        <f>IF(AND(D96&lt;&gt;"", C96&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B96,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B96,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D96&lt;&gt;"", C96&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B96,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B96,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="97" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E97" s="25" t="str">
-        <f>IF(AND(D97&lt;&gt;"", C97&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B97,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B97,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D97&lt;&gt;"", C97&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B97,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B97,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="98" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E98" s="25" t="str">
-        <f>IF(AND(D98&lt;&gt;"", C98&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B98,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B98,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D98&lt;&gt;"", C98&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B98,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B98,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
     <row r="99" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E99" s="25" t="str">
-        <f>IF(AND(D99&lt;&gt;"", C99&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B99,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B99,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D99&lt;&gt;"", C99&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B99,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B99,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15478,7 +16311,7 @@
         <v>0.4284722222222222</v>
       </c>
       <c r="E2" s="25">
-        <f>IF(AND(D2&lt;&gt;"", C2&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B2,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B2,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D2&lt;&gt;"", C2&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B2,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B2,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v>15.999999999999943</v>
       </c>
       <c r="F2" s="16" t="s">
@@ -15489,7 +16322,7 @@
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="E3" s="25" t="str">
-        <f>IF(AND(D3&lt;&gt;"", C3&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B3,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B3,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D3&lt;&gt;"", C3&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B3,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B3,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15497,7 +16330,7 @@
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="E4" s="25" t="str">
-        <f>IF(AND(D4&lt;&gt;"", C4&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B4,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B4,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D4&lt;&gt;"", C4&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B4,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B4,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15505,7 +16338,7 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="E5" s="25" t="str">
-        <f>IF(AND(D5&lt;&gt;"", C5&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B5,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B5,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D5&lt;&gt;"", C5&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B5,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B5,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15513,7 +16346,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="E6" s="25" t="str">
-        <f>IF(AND(D6&lt;&gt;"", C6&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B6,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D6&lt;&gt;"", C6&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B6,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B6,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15521,7 +16354,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="E7" s="25" t="str">
-        <f>IF(AND(D7&lt;&gt;"", C7&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B7,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D7&lt;&gt;"", C7&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B7,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B7,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15529,7 +16362,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="E8" s="25" t="str">
-        <f>IF(AND(D8&lt;&gt;"", C8&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B8,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D8&lt;&gt;"", C8&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B8,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B8,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15537,7 +16370,7 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="E9" s="25" t="str">
-        <f>IF(AND(D9&lt;&gt;"", C9&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B9,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D9&lt;&gt;"", C9&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B9,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B9,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15545,7 +16378,7 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="E10" s="25" t="str">
-        <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B10,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D10&lt;&gt;"", C10&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B10,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B10,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15553,7 +16386,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="E11" s="25" t="str">
-        <f>IF(AND(D11&lt;&gt;"", C11&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B11,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D11&lt;&gt;"", C11&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B11,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B11,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15561,7 +16394,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="E12" s="25" t="str">
-        <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B12,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D12&lt;&gt;"", C12&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B12,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B12,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15569,7 +16402,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="E13" s="25" t="str">
-        <f>IF(AND(D13&lt;&gt;"", C13&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B13,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D13&lt;&gt;"", C13&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B13,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B13,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15577,7 +16410,7 @@
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="E14" s="25" t="str">
-        <f>IF(AND(D14&lt;&gt;"", C14&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B14,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D14&lt;&gt;"", C14&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B14,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B14,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15585,7 +16418,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="E15" s="25" t="str">
-        <f>IF(AND(D15&lt;&gt;"", C15&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B15,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D15&lt;&gt;"", C15&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B15,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B15,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15593,7 +16426,7 @@
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="E16" s="25" t="str">
-        <f>IF(AND(D16&lt;&gt;"", C16&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B16,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D16&lt;&gt;"", C16&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B16,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B16,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15603,7 +16436,7 @@
       <c r="C17" s="2"/>
       <c r="D17" s="8"/>
       <c r="E17" s="25" t="str">
-        <f>IF(AND(D17&lt;&gt;"", C17&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B17,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D17&lt;&gt;"", C17&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B17,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B17,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15613,7 +16446,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="8"/>
       <c r="E18" s="25" t="str">
-        <f>IF(AND(D18&lt;&gt;"", C18&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B18,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D18&lt;&gt;"", C18&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B18,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B18,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15623,7 +16456,7 @@
       <c r="C19" s="2"/>
       <c r="D19" s="8"/>
       <c r="E19" s="25" t="str">
-        <f>IF(AND(D19&lt;&gt;"", C19&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B19,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D19&lt;&gt;"", C19&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B19,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B19,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15633,7 +16466,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="8"/>
       <c r="E20" s="25" t="str">
-        <f>IF(AND(D20&lt;&gt;"", C20&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B20,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D20&lt;&gt;"", C20&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B20,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B20,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15643,7 +16476,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="8"/>
       <c r="E21" s="25" t="str">
-        <f>IF(AND(D21&lt;&gt;"", C21&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B21,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D21&lt;&gt;"", C21&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B21,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B21,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15653,7 +16486,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="8"/>
       <c r="E22" s="25" t="str">
-        <f>IF(AND(D22&lt;&gt;"", C22&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B22,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D22&lt;&gt;"", C22&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B22,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B22,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15663,7 +16496,7 @@
       <c r="C23" s="2"/>
       <c r="D23" s="8"/>
       <c r="E23" s="25" t="str">
-        <f>IF(AND(D23&lt;&gt;"", C23&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B23,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B23,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D23&lt;&gt;"", C23&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B23,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B23,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15673,7 +16506,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="8"/>
       <c r="E24" s="25" t="str">
-        <f>IF(AND(D24&lt;&gt;"", C24&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B24,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B24,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D24&lt;&gt;"", C24&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B24,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B24,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15683,7 +16516,7 @@
       <c r="C25" s="2"/>
       <c r="D25" s="8"/>
       <c r="E25" s="25" t="str">
-        <f>IF(AND(D25&lt;&gt;"", C25&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B25,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B25,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D25&lt;&gt;"", C25&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B25,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B25,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15693,7 +16526,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="8"/>
       <c r="E26" s="25" t="str">
-        <f>IF(AND(D26&lt;&gt;"", C26&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B26,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B26,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D26&lt;&gt;"", C26&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B26,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B26,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15703,7 +16536,7 @@
       <c r="C27" s="2"/>
       <c r="D27" s="8"/>
       <c r="E27" s="25" t="str">
-        <f>IF(AND(D27&lt;&gt;"", C27&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B27,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B27,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D27&lt;&gt;"", C27&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B27,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B27,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15713,7 +16546,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="8"/>
       <c r="E28" s="25" t="str">
-        <f>IF(AND(D28&lt;&gt;"", C28&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B28,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B28,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D28&lt;&gt;"", C28&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B28,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B28,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15723,7 +16556,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="8"/>
       <c r="E29" s="25" t="str">
-        <f>IF(AND(D29&lt;&gt;"", C29&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B29,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B29,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D29&lt;&gt;"", C29&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B29,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B29,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15733,7 +16566,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="8"/>
       <c r="E30" s="25" t="str">
-        <f>IF(AND(D30&lt;&gt;"", C30&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B30,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B30,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D30&lt;&gt;"", C30&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B30,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B30,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15743,7 +16576,7 @@
       <c r="C31" s="2"/>
       <c r="D31" s="8"/>
       <c r="E31" s="25" t="str">
-        <f>IF(AND(D31&lt;&gt;"", C31&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B31,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B31,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D31&lt;&gt;"", C31&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B31,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B31,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15753,7 +16586,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="8"/>
       <c r="E32" s="25" t="str">
-        <f>IF(AND(D32&lt;&gt;"", C32&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B32,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B32,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D32&lt;&gt;"", C32&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B32,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B32,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15763,7 +16596,7 @@
       <c r="C33" s="2"/>
       <c r="D33" s="8"/>
       <c r="E33" s="25" t="str">
-        <f>IF(AND(D33&lt;&gt;"", C33&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B33,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B33,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D33&lt;&gt;"", C33&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B33,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B33,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15773,7 +16606,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="8"/>
       <c r="E34" s="25" t="str">
-        <f>IF(AND(D34&lt;&gt;"", C34&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B34,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B34,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D34&lt;&gt;"", C34&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B34,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B34,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15783,7 +16616,7 @@
       <c r="C35" s="2"/>
       <c r="D35" s="8"/>
       <c r="E35" s="25" t="str">
-        <f>IF(AND(D35&lt;&gt;"", C35&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B35,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B35,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D35&lt;&gt;"", C35&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B35,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B35,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15793,7 +16626,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="8"/>
       <c r="E36" s="25" t="str">
-        <f>IF(AND(D36&lt;&gt;"", C36&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B36,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B36,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D36&lt;&gt;"", C36&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B36,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B36,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15803,7 +16636,7 @@
       <c r="C37" s="2"/>
       <c r="D37" s="8"/>
       <c r="E37" s="25" t="str">
-        <f>IF(AND(D37&lt;&gt;"", C37&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B37,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B37,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D37&lt;&gt;"", C37&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B37,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B37,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15813,7 +16646,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="8"/>
       <c r="E38" s="25" t="str">
-        <f>IF(AND(D38&lt;&gt;"", C38&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B38,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B38,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D38&lt;&gt;"", C38&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B38,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B38,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15823,7 +16656,7 @@
       <c r="C39" s="2"/>
       <c r="D39" s="8"/>
       <c r="E39" s="25" t="str">
-        <f>IF(AND(D39&lt;&gt;"", C39&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B39,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B39,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D39&lt;&gt;"", C39&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B39,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B39,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15833,7 +16666,7 @@
       <c r="C40" s="2"/>
       <c r="D40" s="8"/>
       <c r="E40" s="25" t="str">
-        <f>IF(AND(D40&lt;&gt;"", C40&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B40,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B40,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D40&lt;&gt;"", C40&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B40,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B40,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15843,7 +16676,7 @@
       <c r="C41" s="2"/>
       <c r="D41" s="8"/>
       <c r="E41" s="25" t="str">
-        <f>IF(AND(D41&lt;&gt;"", C41&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B41,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B41,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D41&lt;&gt;"", C41&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B41,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B41,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15853,7 +16686,7 @@
       <c r="C42" s="2"/>
       <c r="D42" s="8"/>
       <c r="E42" s="25" t="str">
-        <f>IF(AND(D42&lt;&gt;"", C42&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B42,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B42,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D42&lt;&gt;"", C42&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B42,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B42,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15863,7 +16696,7 @@
       <c r="C43" s="2"/>
       <c r="D43" s="8"/>
       <c r="E43" s="25" t="str">
-        <f>IF(AND(D43&lt;&gt;"", C43&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B43,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B43,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D43&lt;&gt;"", C43&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B43,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B43,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15873,7 +16706,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="8"/>
       <c r="E44" s="25" t="str">
-        <f>IF(AND(D44&lt;&gt;"", C44&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B44,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B44,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D44&lt;&gt;"", C44&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B44,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B44,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15883,7 +16716,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="8"/>
       <c r="E45" s="25" t="str">
-        <f>IF(AND(D45&lt;&gt;"", C45&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B45,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B45,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D45&lt;&gt;"", C45&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B45,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B45,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15893,7 +16726,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="8"/>
       <c r="E46" s="25" t="str">
-        <f>IF(AND(D46&lt;&gt;"", C46&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B46,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B46,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D46&lt;&gt;"", C46&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B46,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B46,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15903,7 +16736,7 @@
       <c r="C47" s="2"/>
       <c r="D47" s="8"/>
       <c r="E47" s="25" t="str">
-        <f>IF(AND(D47&lt;&gt;"", C47&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B47,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B47,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D47&lt;&gt;"", C47&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B47,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B47,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15913,7 +16746,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="8"/>
       <c r="E48" s="25" t="str">
-        <f>IF(AND(D48&lt;&gt;"", C48&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B48,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B48,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D48&lt;&gt;"", C48&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B48,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B48,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15923,7 +16756,7 @@
       <c r="C49" s="2"/>
       <c r="D49" s="8"/>
       <c r="E49" s="25" t="str">
-        <f>IF(AND(D49&lt;&gt;"", C49&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B49,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B49,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D49&lt;&gt;"", C49&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B49,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B49,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15933,7 +16766,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="8"/>
       <c r="E50" s="25" t="str">
-        <f>IF(AND(D50&lt;&gt;"", C50&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B50,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B50,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D50&lt;&gt;"", C50&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B50,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B50,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15943,7 +16776,7 @@
       <c r="C51" s="2"/>
       <c r="D51" s="8"/>
       <c r="E51" s="25" t="str">
-        <f>IF(AND(D51&lt;&gt;"", C51&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B51,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B51,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D51&lt;&gt;"", C51&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B51,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B51,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15953,7 +16786,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="8"/>
       <c r="E52" s="25" t="str">
-        <f>IF(AND(D52&lt;&gt;"", C52&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B52,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B52,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D52&lt;&gt;"", C52&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B52,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B52,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15963,7 +16796,7 @@
       <c r="C53" s="2"/>
       <c r="D53" s="8"/>
       <c r="E53" s="25" t="str">
-        <f>IF(AND(D53&lt;&gt;"", C53&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B53,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B53,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D53&lt;&gt;"", C53&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B53,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B53,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15973,7 +16806,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="8"/>
       <c r="E54" s="25" t="str">
-        <f>IF(AND(D54&lt;&gt;"", C54&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B54,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B54,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D54&lt;&gt;"", C54&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B54,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B54,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15983,7 +16816,7 @@
       <c r="C55" s="2"/>
       <c r="D55" s="8"/>
       <c r="E55" s="25" t="str">
-        <f>IF(AND(D55&lt;&gt;"", C55&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B55,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B55,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D55&lt;&gt;"", C55&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B55,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B55,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -15993,7 +16826,7 @@
       <c r="C56" s="2"/>
       <c r="D56" s="8"/>
       <c r="E56" s="25" t="str">
-        <f>IF(AND(D56&lt;&gt;"", C56&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B56,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B56,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D56&lt;&gt;"", C56&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B56,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B56,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16003,7 +16836,7 @@
       <c r="C57" s="2"/>
       <c r="D57" s="8"/>
       <c r="E57" s="25" t="str">
-        <f>IF(AND(D57&lt;&gt;"", C57&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B57,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B57,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D57&lt;&gt;"", C57&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B57,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B57,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16013,7 +16846,7 @@
       <c r="C58" s="2"/>
       <c r="D58" s="8"/>
       <c r="E58" s="25" t="str">
-        <f>IF(AND(D58&lt;&gt;"", C58&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B58,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D58&lt;&gt;"", C58&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B58,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B58,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16023,7 +16856,7 @@
       <c r="C59" s="2"/>
       <c r="D59" s="8"/>
       <c r="E59" s="25" t="str">
-        <f>IF(AND(D59&lt;&gt;"", C59&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B59,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B59,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D59&lt;&gt;"", C59&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B59,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B59,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16033,7 +16866,7 @@
       <c r="C60" s="2"/>
       <c r="D60" s="8"/>
       <c r="E60" s="25" t="str">
-        <f>IF(AND(D60&lt;&gt;"", C60&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B60,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B60,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D60&lt;&gt;"", C60&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B60,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B60,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16043,7 +16876,7 @@
       <c r="C61" s="2"/>
       <c r="D61" s="8"/>
       <c r="E61" s="25" t="str">
-        <f>IF(AND(D61&lt;&gt;"", C61&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B61,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B61,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D61&lt;&gt;"", C61&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B61,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B61,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16053,7 +16886,7 @@
       <c r="C62" s="2"/>
       <c r="D62" s="8"/>
       <c r="E62" s="25" t="str">
-        <f>IF(AND(D62&lt;&gt;"", C62&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B62,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B62,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D62&lt;&gt;"", C62&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B62,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B62,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16063,7 +16896,7 @@
       <c r="C63" s="2"/>
       <c r="D63" s="8"/>
       <c r="E63" s="25" t="str">
-        <f>IF(AND(D63&lt;&gt;"", C63&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B63,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B63,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D63&lt;&gt;"", C63&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B63,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B63,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16073,7 +16906,7 @@
       <c r="C64" s="2"/>
       <c r="D64" s="8"/>
       <c r="E64" s="25" t="str">
-        <f>IF(AND(D64&lt;&gt;"", C64&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B64,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B64,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D64&lt;&gt;"", C64&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B64,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B64,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16083,7 +16916,7 @@
       <c r="C65" s="2"/>
       <c r="D65" s="8"/>
       <c r="E65" s="25" t="str">
-        <f>IF(AND(D65&lt;&gt;"", C65&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B65,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B65,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D65&lt;&gt;"", C65&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B65,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B65,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16093,7 +16926,7 @@
       <c r="C66" s="2"/>
       <c r="D66" s="8"/>
       <c r="E66" s="25" t="str">
-        <f>IF(AND(D66&lt;&gt;"", C66&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B66,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B66,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D66&lt;&gt;"", C66&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B66,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B66,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16103,7 +16936,7 @@
       <c r="C67" s="2"/>
       <c r="D67" s="8"/>
       <c r="E67" s="25" t="str">
-        <f>IF(AND(D67&lt;&gt;"", C67&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B67,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B67,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D67&lt;&gt;"", C67&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B67,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B67,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16113,7 +16946,7 @@
       <c r="C68" s="2"/>
       <c r="D68" s="8"/>
       <c r="E68" s="25" t="str">
-        <f>IF(AND(D68&lt;&gt;"", C68&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B68,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B68,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D68&lt;&gt;"", C68&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B68,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B68,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16123,7 +16956,7 @@
       <c r="C69" s="2"/>
       <c r="D69" s="8"/>
       <c r="E69" s="25" t="str">
-        <f>IF(AND(D69&lt;&gt;"", C69&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B69,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B69,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D69&lt;&gt;"", C69&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B69,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B69,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16133,7 +16966,7 @@
       <c r="C70" s="2"/>
       <c r="D70" s="8"/>
       <c r="E70" s="25" t="str">
-        <f>IF(AND(D70&lt;&gt;"", C70&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B70,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B70,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D70&lt;&gt;"", C70&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B70,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B70,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16143,7 +16976,7 @@
       <c r="C71" s="2"/>
       <c r="D71" s="8"/>
       <c r="E71" s="25" t="str">
-        <f>IF(AND(D71&lt;&gt;"", C71&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B71,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B71,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D71&lt;&gt;"", C71&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B71,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B71,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16153,7 +16986,7 @@
       <c r="C72" s="2"/>
       <c r="D72" s="8"/>
       <c r="E72" s="25" t="str">
-        <f>IF(AND(D72&lt;&gt;"", C72&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B72,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B72,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D72&lt;&gt;"", C72&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B72,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B72,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16163,7 +16996,7 @@
       <c r="C73" s="2"/>
       <c r="D73" s="8"/>
       <c r="E73" s="25" t="str">
-        <f>IF(AND(D73&lt;&gt;"", C73&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B73,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B73,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D73&lt;&gt;"", C73&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B73,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B73,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16173,7 +17006,7 @@
       <c r="C74" s="2"/>
       <c r="D74" s="8"/>
       <c r="E74" s="25" t="str">
-        <f>IF(AND(D74&lt;&gt;"", C74&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B74,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B74,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D74&lt;&gt;"", C74&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B74,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B74,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16183,7 +17016,7 @@
       <c r="C75" s="2"/>
       <c r="D75" s="8"/>
       <c r="E75" s="25" t="str">
-        <f>IF(AND(D75&lt;&gt;"", C75&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B75,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B75,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D75&lt;&gt;"", C75&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B75,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B75,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16193,7 +17026,7 @@
       <c r="C76" s="2"/>
       <c r="D76" s="8"/>
       <c r="E76" s="25" t="str">
-        <f>IF(AND(D76&lt;&gt;"", C76&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B76,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B76,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D76&lt;&gt;"", C76&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B76,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B76,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16203,7 +17036,7 @@
       <c r="C77" s="2"/>
       <c r="D77" s="8"/>
       <c r="E77" s="25" t="str">
-        <f>IF(AND(D77&lt;&gt;"", C77&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B77,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B77,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D77&lt;&gt;"", C77&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B77,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B77,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16213,7 +17046,7 @@
       <c r="C78" s="2"/>
       <c r="D78" s="8"/>
       <c r="E78" s="25" t="str">
-        <f>IF(AND(D78&lt;&gt;"", C78&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B78,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B78,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D78&lt;&gt;"", C78&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B78,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B78,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16223,7 +17056,7 @@
       <c r="C79" s="2"/>
       <c r="D79" s="8"/>
       <c r="E79" s="25" t="str">
-        <f>IF(AND(D79&lt;&gt;"", C79&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B79,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B79,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D79&lt;&gt;"", C79&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B79,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B79,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16233,7 +17066,7 @@
       <c r="C80" s="2"/>
       <c r="D80" s="8"/>
       <c r="E80" s="25" t="str">
-        <f>IF(AND(D80&lt;&gt;"", C80&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B80,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B80,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D80&lt;&gt;"", C80&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B80,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B80,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16243,7 +17076,7 @@
       <c r="C81" s="2"/>
       <c r="D81" s="8"/>
       <c r="E81" s="25" t="str">
-        <f>IF(AND(D81&lt;&gt;"", C81&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B81,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B81,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D81&lt;&gt;"", C81&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B81,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B81,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16253,7 +17086,7 @@
       <c r="C82" s="2"/>
       <c r="D82" s="8"/>
       <c r="E82" s="25" t="str">
-        <f>IF(AND(D82&lt;&gt;"", C82&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B82,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B82,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D82&lt;&gt;"", C82&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B82,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B82,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16263,7 +17096,7 @@
       <c r="C83" s="2"/>
       <c r="D83" s="8"/>
       <c r="E83" s="25" t="str">
-        <f>IF(AND(D83&lt;&gt;"", C83&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B83,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B83,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D83&lt;&gt;"", C83&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B83,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B83,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16273,7 +17106,7 @@
       <c r="C84" s="2"/>
       <c r="D84" s="8"/>
       <c r="E84" s="25" t="str">
-        <f>IF(AND(D84&lt;&gt;"", C84&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$9999,B84,Log!$F$3:$F$9999,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$9999,Log!$A$3:$A$9999,B84,Log!$F$3:$F$9999,"&gt;=50")), "")</f>
+        <f>IF(AND(D84&lt;&gt;"", C84&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B84,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B84,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
         <v/>
       </c>
     </row>
@@ -16287,23 +17120,23 @@
   <sheetPr>
     <tabColor rgb="FFC65911"/>
   </sheetPr>
-  <dimension ref="C18:K26"/>
+  <dimension ref="C19:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-    </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C19" s="26" t="s">
-        <v>43</v>
-      </c>
       <c r="K19" t="s">
         <v>53</v>
       </c>
     </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C23" s="26" t="s">
+        <v>43</v>
+      </c>
       <c r="K23" s="17" t="s">
         <v>38</v>
       </c>
@@ -16325,7 +17158,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K23">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
+++ b/Documentation Data/LCAS Vicon Temperature Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newwb\Documents\brain\professional\university\LCAS\Vicon (EPSURIS) Main\Public Files\Documentation Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1DC83B-A84B-47A7-B756-9B2F8EB23AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8B98E4-BEE5-4C1C-A357-4CBE971CFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1252,8 +1252,8 @@
           <c:h val="0.58522781635054233"/>
         </c:manualLayout>
       </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1270,7 +1270,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2">
                   <a:lumMod val="75000"/>
@@ -1281,23 +1281,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="C65911"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>'Daily Summary'!$B$2:$B$99</c:f>
               <c:numCache>
@@ -1369,10 +1355,13 @@
                 <c:pt idx="21">
                   <c:v>46255</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'Daily Summary'!$C$2:$C$99</c:f>
               <c:numCache>
@@ -1444,9 +1433,12 @@
                 <c:pt idx="21">
                   <c:v>23.5</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1462,11 +1454,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="1072957472"/>
         <c:axId val="1072952192"/>
-      </c:scatterChart>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
@@ -1484,7 +1478,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="00B0F0"/>
               </a:solidFill>
@@ -1493,21 +1487,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="0070C0"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
-          <c:xVal>
+          <c:cat>
             <c:numRef>
               <c:f>'Daily Summary'!$B$2:$B$99</c:f>
               <c:numCache>
@@ -1579,10 +1561,13 @@
                 <c:pt idx="21">
                   <c:v>46255</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46258</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
               <c:f>'Daily Summary'!$E$2:$E$99</c:f>
               <c:numCache>
@@ -1655,7 +1640,7 @@
                   <c:v>18.816666666666677</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>23.766666666666652</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -1881,7 +1866,7 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1897,10 +1882,12 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="1965629424"/>
         <c:axId val="1965623184"/>
-      </c:scatterChart>
-      <c:valAx>
+      </c:lineChart>
+      <c:dateAx>
         <c:axId val="1072957472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -1939,7 +1926,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1960,12 +1947,16 @@
         </c:txPr>
         <c:crossAx val="1072952192"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+      </c:dateAx>
       <c:valAx>
         <c:axId val="1072952192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="26"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1983,9 +1974,9 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -2021,8 +2012,9 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1072957472"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="46228"/>
         <c:crossBetween val="midCat"/>
+        <c:minorUnit val="0.25"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1965623184"/>
@@ -2070,9 +2062,9 @@
         </c:txPr>
         <c:crossAx val="1965629424"/>
         <c:crosses val="max"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
-      <c:valAx>
+      <c:dateAx>
         <c:axId val="1965629424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -2085,8 +2077,10 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1965623184"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2173,267 +2167,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="505666224"/>
-        <c:axId val="512736368"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="505666224"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="512736368"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="512736368"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="505666224"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2989,522 +2723,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3540,42 +2758,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>563880</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F46A80B-2967-17AE-2CEC-2B53FF16C346}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11529,230 +10711,422 @@
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>46258</v>
+      </c>
       <c r="C292" s="9">
         <f>_xlfn.XLOOKUP(Log!A292, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E292" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D292" s="9">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="E292" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H292" s="2" t="str">
+        <v>1.9999999999999929</v>
+      </c>
+      <c r="F292" s="7">
+        <v>27</v>
+      </c>
+      <c r="G292" s="2">
+        <v>30</v>
+      </c>
+      <c r="H292" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A293" s="1">
+        <v>46258</v>
+      </c>
       <c r="C293" s="9">
         <f>_xlfn.XLOOKUP(Log!A293, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E293" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D293" s="9">
+        <v>0.49494212962962963</v>
+      </c>
+      <c r="E293" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H293" s="2" t="str">
+        <v>3.7166666666666348</v>
+      </c>
+      <c r="F293" s="7">
+        <v>32</v>
+      </c>
+      <c r="G293" s="2">
+        <v>33</v>
+      </c>
+      <c r="H293" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>46258</v>
+      </c>
       <c r="C294" s="9">
         <f>_xlfn.XLOOKUP(Log!A294, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E294" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D294" s="9">
+        <v>0.49633101851851852</v>
+      </c>
+      <c r="E294" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H294" s="2" t="str">
+        <v>5.7166666666666277</v>
+      </c>
+      <c r="F294" s="7">
+        <v>35</v>
+      </c>
+      <c r="G294" s="2">
+        <v>38</v>
+      </c>
+      <c r="H294" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A295" s="1">
+        <v>46258</v>
+      </c>
       <c r="C295" s="9">
         <f>_xlfn.XLOOKUP(Log!A295, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E295" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D295" s="9">
+        <v>0.4977314814814815</v>
+      </c>
+      <c r="E295" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H295" s="2" t="str">
+        <v>7.7333333333333165</v>
+      </c>
+      <c r="F295" s="7">
+        <v>38</v>
+      </c>
+      <c r="G295" s="2">
+        <v>41</v>
+      </c>
+      <c r="H295" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>46258</v>
+      </c>
       <c r="C296" s="9">
         <f>_xlfn.XLOOKUP(Log!A296, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E296" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D296" s="9">
+        <v>0.49912037037037038</v>
+      </c>
+      <c r="E296" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H296" s="2" t="str">
+        <v>9.7333333333333094</v>
+      </c>
+      <c r="F296" s="7">
+        <v>41</v>
+      </c>
+      <c r="G296" s="2">
+        <v>42</v>
+      </c>
+      <c r="H296" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>46258</v>
+      </c>
       <c r="C297" s="9">
         <f>_xlfn.XLOOKUP(Log!A297, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E297" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D297" s="9">
+        <v>0.50050925925925926</v>
+      </c>
+      <c r="E297" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H297" s="2" t="str">
+        <v>11.733333333333302</v>
+      </c>
+      <c r="F297" s="7">
+        <v>42</v>
+      </c>
+      <c r="G297" s="2">
+        <v>45</v>
+      </c>
+      <c r="H297" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>46258</v>
+      </c>
       <c r="C298" s="9">
         <f>_xlfn.XLOOKUP(Log!A298, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E298" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D298" s="9">
+        <v>0.50189814814814815</v>
+      </c>
+      <c r="E298" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H298" s="2" t="str">
+        <v>13.733333333333295</v>
+      </c>
+      <c r="F298" s="7">
+        <v>44</v>
+      </c>
+      <c r="G298" s="2">
+        <v>47</v>
+      </c>
+      <c r="H298" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A299" s="1">
+        <v>46258</v>
+      </c>
       <c r="C299" s="9">
         <f>_xlfn.XLOOKUP(Log!A299, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E299" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D299" s="9">
+        <v>0.50328703703703703</v>
+      </c>
+      <c r="E299" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H299" s="2" t="str">
+        <v>15.733333333333288</v>
+      </c>
+      <c r="F299" s="7">
+        <v>45</v>
+      </c>
+      <c r="G299" s="2">
+        <v>49</v>
+      </c>
+      <c r="H299" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A300" s="1">
+        <v>46258</v>
+      </c>
       <c r="C300" s="9">
         <f>_xlfn.XLOOKUP(Log!A300, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E300" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D300" s="9">
+        <v>0.50468749999999996</v>
+      </c>
+      <c r="E300" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H300" s="2" t="str">
+        <v>17.749999999999897</v>
+      </c>
+      <c r="F300" s="7">
+        <v>48</v>
+      </c>
+      <c r="G300" s="2">
+        <v>49</v>
+      </c>
+      <c r="H300" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>46258</v>
+      </c>
       <c r="C301" s="9">
         <f>_xlfn.XLOOKUP(Log!A301, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E301" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D301" s="9">
+        <v>0.50607638888888884</v>
+      </c>
+      <c r="E301" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H301" s="2" t="str">
+        <v>19.74999999999989</v>
+      </c>
+      <c r="F301" s="7">
+        <v>48</v>
+      </c>
+      <c r="G301" s="2">
+        <v>51</v>
+      </c>
+      <c r="H301" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>46258</v>
+      </c>
       <c r="C302" s="9">
         <f>_xlfn.XLOOKUP(Log!A302, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E302" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D302" s="9">
+        <v>0.50747685185185187</v>
+      </c>
+      <c r="E302" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H302" s="2" t="str">
+        <v>21.766666666666659</v>
+      </c>
+      <c r="F302" s="7">
+        <v>49</v>
+      </c>
+      <c r="G302" s="2">
+        <v>52</v>
+      </c>
+      <c r="H302" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>46258</v>
+      </c>
       <c r="C303" s="9">
         <f>_xlfn.XLOOKUP(Log!A303, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E303" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D303" s="9">
+        <v>0.50886574074074076</v>
+      </c>
+      <c r="E303" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H303" s="2" t="str">
+        <v>23.766666666666652</v>
+      </c>
+      <c r="F303" s="7">
+        <v>51</v>
+      </c>
+      <c r="G303" s="2">
+        <v>54</v>
+      </c>
+      <c r="H303" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>46258</v>
+      </c>
       <c r="C304" s="9">
         <f>_xlfn.XLOOKUP(Log!A304, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E304" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D304" s="9">
+        <v>0.51026620370370368</v>
+      </c>
+      <c r="E304" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H304" s="2" t="str">
+        <v>25.78333333333326</v>
+      </c>
+      <c r="F304" s="7">
+        <v>51</v>
+      </c>
+      <c r="G304" s="2">
+        <v>55</v>
+      </c>
+      <c r="H304" s="2">
         <f t="shared" ref="H304:H367" si="10">IF(AND(G304&lt;&gt;"",F304&lt;&gt;""),G304-F304,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="3:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>46258</v>
+      </c>
       <c r="C305" s="9">
         <f>_xlfn.XLOOKUP(Log!A305, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E305" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D305" s="9">
+        <v>0.51165509259259256</v>
+      </c>
+      <c r="E305" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H305" s="2" t="str">
+        <v>27.783333333333253</v>
+      </c>
+      <c r="F305" s="7">
+        <v>52</v>
+      </c>
+      <c r="G305" s="2">
+        <v>55</v>
+      </c>
+      <c r="H305" s="2">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>46258</v>
+      </c>
       <c r="C306" s="9">
         <f>_xlfn.XLOOKUP(Log!A306, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E306" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D306" s="9">
+        <v>0.51304398148148145</v>
+      </c>
+      <c r="E306" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H306" s="2" t="str">
+        <v>29.783333333333246</v>
+      </c>
+      <c r="F306" s="7">
+        <v>54</v>
+      </c>
+      <c r="G306" s="2">
+        <v>55</v>
+      </c>
+      <c r="H306" s="2">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="3:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>46258</v>
+      </c>
       <c r="C307" s="9">
         <f>_xlfn.XLOOKUP(Log!A307, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
-        <v>0</v>
-      </c>
-      <c r="E307" s="6" t="str">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="D307" s="9">
+        <v>0.51444444444444448</v>
+      </c>
+      <c r="E307" s="6">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H307" s="2" t="str">
+        <v>31.800000000000015</v>
+      </c>
+      <c r="F307" s="7">
+        <v>54</v>
+      </c>
+      <c r="G307" s="2">
+        <v>57</v>
+      </c>
+      <c r="H307" s="2">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="3:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C308" s="9">
         <f>_xlfn.XLOOKUP(Log!A308, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11766,7 +11140,7 @@
         <v/>
       </c>
     </row>
-    <row r="309" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C309" s="9">
         <f>_xlfn.XLOOKUP(Log!A309, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11780,7 +11154,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C310" s="9">
         <f>_xlfn.XLOOKUP(Log!A310, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11794,7 +11168,7 @@
         <v/>
       </c>
     </row>
-    <row r="311" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C311" s="9">
         <f>_xlfn.XLOOKUP(Log!A311, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11808,7 +11182,7 @@
         <v/>
       </c>
     </row>
-    <row r="312" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C312" s="9">
         <f>_xlfn.XLOOKUP(Log!A312, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11822,7 +11196,7 @@
         <v/>
       </c>
     </row>
-    <row r="313" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C313" s="9">
         <f>_xlfn.XLOOKUP(Log!A313, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11836,7 +11210,7 @@
         <v/>
       </c>
     </row>
-    <row r="314" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C314" s="9">
         <f>_xlfn.XLOOKUP(Log!A314, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11850,7 +11224,7 @@
         <v/>
       </c>
     </row>
-    <row r="315" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C315" s="9">
         <f>_xlfn.XLOOKUP(Log!A315, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11864,7 +11238,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C316" s="9">
         <f>_xlfn.XLOOKUP(Log!A316, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11878,7 +11252,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C317" s="9">
         <f>_xlfn.XLOOKUP(Log!A317, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11892,7 +11266,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C318" s="9">
         <f>_xlfn.XLOOKUP(Log!A318, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11906,7 +11280,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C319" s="9">
         <f>_xlfn.XLOOKUP(Log!A319, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -11920,7 +11294,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C320" s="9">
         <f>_xlfn.XLOOKUP(Log!A320, 'Daily Summary'!A:A, 'Daily Summary'!D:D, "Not found!")</f>
         <v>0</v>
@@ -15239,7 +14613,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="D3:XFD3 D4:G196 H4:H211 D197:F211 D212:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 I4:XFD32 I33:L40 O33:XFD40 I41:XFD44 J45:XFD45 I46:XFD211 G198:G211 A2:C1048576">
+  <conditionalFormatting sqref="A2:C1048576 D3:XFD3 D4:G196 H4:H211 D197:F211 D212:XFD1048576 A1 I1:XFD1 D2:I2 K2:XFD2 I4:XFD32 I33:L40 O33:XFD40 I41:XFD44 J45:XFD45 I46:XFD211 G198:G211">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(ROW()&gt;2, COLUMN()&lt;8, MOD(ROW(),2)=0)</formula>
     </cfRule>
@@ -15741,11 +15115,21 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="E25" s="25" t="str">
+      <c r="A25" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46258</v>
+      </c>
+      <c r="C25" s="2">
+        <v>23</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0.49236111111111114</v>
+      </c>
+      <c r="E25" s="25">
         <f>IF(AND(D25&lt;&gt;"", C25&lt;&gt;""), IF(COUNTIFS(Log!$A$3:$A$10014,B25,Log!$F$3:$F$10014,"&gt;=50")=0,"–",_xlfn.MINIFS(Log!$E$3:$E$10014,Log!$A$3:$A$10014,B25,Log!$F$3:$F$10014,"&gt;=50")), "")</f>
-        <v/>
+        <v>23.766666666666652</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
